--- a/apps/sushi/templates/Template_for_SushiCredentials_import_singleorg.xlsx
+++ b/apps/sushi/templates/Template_for_SushiCredentials_import_singleorg.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\TMP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\simon\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FABC5173-C0B3-45FA-880B-7EC9F4E79685}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A04D69E-70EA-4605-AA64-B7F164320BE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Explanation" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="165">
   <si>
     <t>title</t>
   </si>
@@ -634,6 +634,9 @@
   <si>
     <t>abc11122ddaasf121213</t>
   </si>
+  <si>
+    <t>Your customer ID that allows access to the SUSHI service of the publisher</t>
+  </si>
 </sst>
 </file>
 
@@ -823,7 +826,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -909,13 +912,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -1224,18 +1224,18 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:Y1000"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="44.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="44.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="31.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.85546875" style="31" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="26.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="25" width="8.7109375" style="26" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="44.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="44.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.88671875" style="30" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="25" width="8.6640625" style="26" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -1274,7 +1274,7 @@
       <c r="X1" s="11"/>
       <c r="Y1" s="11"/>
     </row>
-    <row r="2" spans="1:25" s="1" customFormat="1" ht="90" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:25" s="1" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
         <v>6</v>
       </c>
@@ -1285,7 +1285,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>8</v>
+        <v>164</v>
       </c>
       <c r="E2" s="14" t="s">
         <v>9</v>
@@ -1313,7 +1313,7 @@
       <c r="X2" s="11"/>
       <c r="Y2" s="11"/>
     </row>
-    <row r="3" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11"/>
       <c r="B3" s="11"/>
       <c r="C3" s="11"/>
@@ -1340,7 +1340,7 @@
       <c r="X3" s="11"/>
       <c r="Y3" s="11"/>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
       <c r="D4" s="6"/>
       <c r="G4" s="11"/>
       <c r="H4" s="11"/>
@@ -1362,7 +1362,7 @@
       <c r="X4" s="11"/>
       <c r="Y4" s="11"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
       <c r="D5" s="6"/>
       <c r="G5" s="11"/>
       <c r="H5" s="11"/>
@@ -1384,7 +1384,7 @@
       <c r="X5" s="11"/>
       <c r="Y5" s="11"/>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
       <c r="D6" s="6"/>
       <c r="G6" s="11"/>
       <c r="H6" s="11"/>
@@ -1406,7 +1406,7 @@
       <c r="X6" s="11"/>
       <c r="Y6" s="11"/>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
       <c r="D7" s="6"/>
       <c r="G7" s="11"/>
       <c r="H7" s="11"/>
@@ -1428,7 +1428,7 @@
       <c r="X7" s="11"/>
       <c r="Y7" s="11"/>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A8" s="17" t="s">
         <v>11</v>
       </c>
@@ -1453,7 +1453,7 @@
       <c r="X8" s="11"/>
       <c r="Y8" s="11"/>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
       <c r="D9" s="6"/>
       <c r="G9" s="11"/>
       <c r="H9" s="11"/>
@@ -1475,7 +1475,7 @@
       <c r="X9" s="11"/>
       <c r="Y9" s="11"/>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A10" s="18" t="s">
         <v>12</v>
       </c>
@@ -1500,7 +1500,7 @@
       <c r="X10" s="11"/>
       <c r="Y10" s="11"/>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A11" s="19" t="s">
         <v>13</v>
       </c>
@@ -1525,7 +1525,7 @@
       <c r="X11" s="11"/>
       <c r="Y11" s="11"/>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A12" s="19"/>
       <c r="D12" s="6"/>
       <c r="G12" s="11"/>
@@ -1548,7 +1548,7 @@
       <c r="X12" s="11"/>
       <c r="Y12" s="11"/>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A13" s="19" t="s">
         <v>14</v>
       </c>
@@ -1576,7 +1576,7 @@
       <c r="X13" s="11"/>
       <c r="Y13" s="11"/>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B14" s="21" t="s">
         <v>16</v>
       </c>
@@ -1602,7 +1602,7 @@
       <c r="X14" s="11"/>
       <c r="Y14" s="11"/>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B15" s="22" t="s">
         <v>17</v>
       </c>
@@ -1627,7 +1627,7 @@
       <c r="X15" s="11"/>
       <c r="Y15" s="11"/>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B16" s="23" t="s">
         <v>18</v>
       </c>
@@ -1652,7 +1652,7 @@
       <c r="X16" s="11"/>
       <c r="Y16" s="11"/>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.3">
       <c r="D17" s="6"/>
       <c r="G17" s="11"/>
       <c r="H17" s="11"/>
@@ -1674,7 +1674,7 @@
       <c r="X17" s="11"/>
       <c r="Y17" s="11"/>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A18" s="19" t="s">
         <v>19</v>
       </c>
@@ -1699,7 +1699,7 @@
       <c r="X18" s="11"/>
       <c r="Y18" s="11"/>
     </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A19" s="19" t="s">
         <v>20</v>
       </c>
@@ -1724,7 +1724,7 @@
       <c r="X19" s="11"/>
       <c r="Y19" s="11"/>
     </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A20" s="19" t="s">
         <v>21</v>
       </c>
@@ -1749,7 +1749,7 @@
       <c r="X20" s="11"/>
       <c r="Y20" s="11"/>
     </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:25" x14ac:dyDescent="0.3">
       <c r="D21" s="6"/>
       <c r="G21" s="11"/>
       <c r="H21" s="11"/>
@@ -1771,7 +1771,7 @@
       <c r="X21" s="11"/>
       <c r="Y21" s="11"/>
     </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.3">
       <c r="D22" s="6"/>
       <c r="G22" s="11"/>
       <c r="H22" s="11"/>
@@ -1793,7 +1793,7 @@
       <c r="X22" s="11"/>
       <c r="Y22" s="11"/>
     </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.3">
       <c r="D23" s="6"/>
       <c r="G23" s="11"/>
       <c r="H23" s="11"/>
@@ -1815,7 +1815,7 @@
       <c r="X23" s="11"/>
       <c r="Y23" s="11"/>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.3">
       <c r="D24" s="6"/>
       <c r="G24" s="11"/>
       <c r="H24" s="11"/>
@@ -1837,7 +1837,7 @@
       <c r="X24" s="11"/>
       <c r="Y24" s="11"/>
     </row>
-    <row r="25" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
         <v>0</v>
       </c>
@@ -1876,7 +1876,7 @@
       <c r="X25" s="11"/>
       <c r="Y25" s="11"/>
     </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A26" s="19" t="s">
         <v>160</v>
       </c>
@@ -1909,7 +1909,7 @@
       <c r="X26" s="11"/>
       <c r="Y26" s="11"/>
     </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B27" s="24" t="s">
         <v>24</v>
       </c>
@@ -1939,7 +1939,7 @@
       <c r="X27" s="11"/>
       <c r="Y27" s="11"/>
     </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B28" s="24" t="s">
         <v>25</v>
       </c>
@@ -1964,7 +1964,7 @@
       <c r="X28" s="11"/>
       <c r="Y28" s="11"/>
     </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B29" s="24" t="s">
         <v>26</v>
       </c>
@@ -1989,7 +1989,7 @@
       <c r="X29" s="11"/>
       <c r="Y29" s="11"/>
     </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B30" s="24" t="s">
         <v>27</v>
       </c>
@@ -2014,7 +2014,7 @@
       <c r="X30" s="11"/>
       <c r="Y30" s="11"/>
     </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>161</v>
       </c>
@@ -2050,7 +2050,7 @@
       <c r="X31" s="11"/>
       <c r="Y31" s="11"/>
     </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B32" s="24" t="s">
         <v>29</v>
       </c>
@@ -2075,7 +2075,7 @@
       <c r="X32" s="11"/>
       <c r="Y32" s="11"/>
     </row>
-    <row r="33" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B33" s="24" t="s">
         <v>30</v>
       </c>
@@ -2100,7 +2100,7 @@
       <c r="X33" s="11"/>
       <c r="Y33" s="11"/>
     </row>
-    <row r="34" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B34" s="24" t="s">
         <v>31</v>
       </c>
@@ -2125,7 +2125,7 @@
       <c r="X34" s="11"/>
       <c r="Y34" s="11"/>
     </row>
-    <row r="35" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B35" s="24" t="s">
         <v>32</v>
       </c>
@@ -2150,7 +2150,7 @@
       <c r="X35" s="11"/>
       <c r="Y35" s="11"/>
     </row>
-    <row r="36" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B36" s="24" t="s">
         <v>33</v>
       </c>
@@ -2175,7 +2175,7 @@
       <c r="X36" s="11"/>
       <c r="Y36" s="11"/>
     </row>
-    <row r="37" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B37" s="24" t="s">
         <v>34</v>
       </c>
@@ -2200,7 +2200,7 @@
       <c r="X37" s="11"/>
       <c r="Y37" s="11"/>
     </row>
-    <row r="38" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B38" s="24" t="s">
         <v>35</v>
       </c>
@@ -2225,7 +2225,7 @@
       <c r="X38" s="11"/>
       <c r="Y38" s="11"/>
     </row>
-    <row r="39" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B39" s="24" t="s">
         <v>36</v>
       </c>
@@ -2250,7 +2250,7 @@
       <c r="X39" s="11"/>
       <c r="Y39" s="11"/>
     </row>
-    <row r="40" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B40" s="24" t="s">
         <v>37</v>
       </c>
@@ -2275,7 +2275,7 @@
       <c r="X40" s="11"/>
       <c r="Y40" s="11"/>
     </row>
-    <row r="41" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B41" s="24" t="s">
         <v>38</v>
       </c>
@@ -2300,7 +2300,7 @@
       <c r="X41" s="11"/>
       <c r="Y41" s="11"/>
     </row>
-    <row r="42" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B42" s="24" t="s">
         <v>39</v>
       </c>
@@ -2325,7 +2325,7 @@
       <c r="X42" s="11"/>
       <c r="Y42" s="11"/>
     </row>
-    <row r="43" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B43" s="24" t="s">
         <v>40</v>
       </c>
@@ -2350,7 +2350,7 @@
       <c r="X43" s="11"/>
       <c r="Y43" s="11"/>
     </row>
-    <row r="44" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A44" s="19" t="s">
         <v>41</v>
       </c>
@@ -2383,7 +2383,7 @@
       <c r="X44" s="11"/>
       <c r="Y44" s="11"/>
     </row>
-    <row r="45" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B45" s="24" t="s">
         <v>44</v>
       </c>
@@ -2408,7 +2408,7 @@
       <c r="X45" s="11"/>
       <c r="Y45" s="11"/>
     </row>
-    <row r="46" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B46" s="24" t="s">
         <v>45</v>
       </c>
@@ -2433,7 +2433,7 @@
       <c r="X46" s="11"/>
       <c r="Y46" s="11"/>
     </row>
-    <row r="47" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B47" s="24" t="s">
         <v>46</v>
       </c>
@@ -2458,7 +2458,7 @@
       <c r="X47" s="11"/>
       <c r="Y47" s="11"/>
     </row>
-    <row r="48" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B48" s="24" t="s">
         <v>47</v>
       </c>
@@ -2483,7 +2483,7 @@
       <c r="X48" s="11"/>
       <c r="Y48" s="11"/>
     </row>
-    <row r="49" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B49" s="24" t="s">
         <v>48</v>
       </c>
@@ -2508,7 +2508,7 @@
       <c r="X49" s="11"/>
       <c r="Y49" s="11"/>
     </row>
-    <row r="50" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B50" s="24" t="s">
         <v>49</v>
       </c>
@@ -2533,7 +2533,7 @@
       <c r="X50" s="11"/>
       <c r="Y50" s="11"/>
     </row>
-    <row r="51" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B51" s="24" t="s">
         <v>50</v>
       </c>
@@ -2558,7 +2558,7 @@
       <c r="X51" s="11"/>
       <c r="Y51" s="11"/>
     </row>
-    <row r="52" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B52" s="24" t="s">
         <v>51</v>
       </c>
@@ -2583,14 +2583,14 @@
       <c r="X52" s="11"/>
       <c r="Y52" s="11"/>
     </row>
-    <row r="53" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B53" s="24" t="s">
         <v>52</v>
       </c>
       <c r="C53" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="D53" s="30" t="s">
+      <c r="D53" s="19" t="s">
         <v>54</v>
       </c>
       <c r="G53" s="11"/>
@@ -2613,7 +2613,7 @@
       <c r="X53" s="11"/>
       <c r="Y53" s="11"/>
     </row>
-    <row r="54" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B54" s="24" t="s">
         <v>55</v>
       </c>
@@ -2638,7 +2638,7 @@
       <c r="X54" s="11"/>
       <c r="Y54" s="11"/>
     </row>
-    <row r="55" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B55" s="24" t="s">
         <v>56</v>
       </c>
@@ -2663,7 +2663,7 @@
       <c r="X55" s="11"/>
       <c r="Y55" s="11"/>
     </row>
-    <row r="56" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B56" s="24" t="s">
         <v>57</v>
       </c>
@@ -2688,7 +2688,7 @@
       <c r="X56" s="11"/>
       <c r="Y56" s="11"/>
     </row>
-    <row r="57" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B57" s="24" t="s">
         <v>58</v>
       </c>
@@ -2713,7 +2713,7 @@
       <c r="X57" s="11"/>
       <c r="Y57" s="11"/>
     </row>
-    <row r="58" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B58" s="24" t="s">
         <v>59</v>
       </c>
@@ -2738,7 +2738,7 @@
       <c r="X58" s="11"/>
       <c r="Y58" s="11"/>
     </row>
-    <row r="59" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B59" s="24" t="s">
         <v>60</v>
       </c>
@@ -2763,7 +2763,7 @@
       <c r="X59" s="11"/>
       <c r="Y59" s="11"/>
     </row>
-    <row r="60" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B60" s="24" t="s">
         <v>61</v>
       </c>
@@ -2788,7 +2788,7 @@
       <c r="X60" s="11"/>
       <c r="Y60" s="11"/>
     </row>
-    <row r="61" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B61" s="24" t="s">
         <v>62</v>
       </c>
@@ -2813,7 +2813,7 @@
       <c r="X61" s="11"/>
       <c r="Y61" s="11"/>
     </row>
-    <row r="62" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B62" s="24" t="s">
         <v>63</v>
       </c>
@@ -2838,7 +2838,7 @@
       <c r="X62" s="11"/>
       <c r="Y62" s="11"/>
     </row>
-    <row r="63" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B63" s="24" t="s">
         <v>64</v>
       </c>
@@ -2863,7 +2863,7 @@
       <c r="X63" s="11"/>
       <c r="Y63" s="11"/>
     </row>
-    <row r="64" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B64" s="24" t="s">
         <v>65</v>
       </c>
@@ -2888,7 +2888,7 @@
       <c r="X64" s="11"/>
       <c r="Y64" s="11"/>
     </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B65" s="24" t="s">
         <v>66</v>
       </c>
@@ -2913,7 +2913,7 @@
       <c r="X65" s="11"/>
       <c r="Y65" s="11"/>
     </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B66" s="24" t="s">
         <v>67</v>
       </c>
@@ -2938,7 +2938,7 @@
       <c r="X66" s="11"/>
       <c r="Y66" s="11"/>
     </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B67" s="24" t="s">
         <v>68</v>
       </c>
@@ -2963,7 +2963,7 @@
       <c r="X67" s="11"/>
       <c r="Y67" s="11"/>
     </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B68" s="24" t="s">
         <v>69</v>
       </c>
@@ -2988,7 +2988,7 @@
       <c r="X68" s="11"/>
       <c r="Y68" s="11"/>
     </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B69" s="24" t="s">
         <v>70</v>
       </c>
@@ -3013,7 +3013,7 @@
       <c r="X69" s="11"/>
       <c r="Y69" s="11"/>
     </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B70" s="24" t="s">
         <v>71</v>
       </c>
@@ -3038,7 +3038,7 @@
       <c r="X70" s="11"/>
       <c r="Y70" s="11"/>
     </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B71" s="24" t="s">
         <v>72</v>
       </c>
@@ -3063,7 +3063,7 @@
       <c r="X71" s="11"/>
       <c r="Y71" s="11"/>
     </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B72" s="24" t="s">
         <v>73</v>
       </c>
@@ -3088,7 +3088,7 @@
       <c r="X72" s="11"/>
       <c r="Y72" s="11"/>
     </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B73" s="24" t="s">
         <v>74</v>
       </c>
@@ -3113,7 +3113,7 @@
       <c r="X73" s="11"/>
       <c r="Y73" s="11"/>
     </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B74" s="24" t="s">
         <v>75</v>
       </c>
@@ -3138,7 +3138,7 @@
       <c r="X74" s="11"/>
       <c r="Y74" s="11"/>
     </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B75" s="24" t="s">
         <v>76</v>
       </c>
@@ -3163,7 +3163,7 @@
       <c r="X75" s="11"/>
       <c r="Y75" s="11"/>
     </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B76" s="24" t="s">
         <v>77</v>
       </c>
@@ -3188,7 +3188,7 @@
       <c r="X76" s="11"/>
       <c r="Y76" s="11"/>
     </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B77" s="24" t="s">
         <v>78</v>
       </c>
@@ -3213,7 +3213,7 @@
       <c r="X77" s="11"/>
       <c r="Y77" s="11"/>
     </row>
-    <row r="78" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B78" s="24" t="s">
         <v>79</v>
       </c>
@@ -3238,7 +3238,7 @@
       <c r="X78" s="11"/>
       <c r="Y78" s="11"/>
     </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B79" s="24" t="s">
         <v>80</v>
       </c>
@@ -3263,7 +3263,7 @@
       <c r="X79" s="11"/>
       <c r="Y79" s="11"/>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B80" s="24" t="s">
         <v>81</v>
       </c>
@@ -3288,7 +3288,7 @@
       <c r="X80" s="11"/>
       <c r="Y80" s="11"/>
     </row>
-    <row r="81" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B81" s="24" t="s">
         <v>82</v>
       </c>
@@ -3313,7 +3313,7 @@
       <c r="X81" s="11"/>
       <c r="Y81" s="11"/>
     </row>
-    <row r="82" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B82" s="24" t="s">
         <v>83</v>
       </c>
@@ -3338,7 +3338,7 @@
       <c r="X82" s="11"/>
       <c r="Y82" s="11"/>
     </row>
-    <row r="83" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B83" s="24" t="s">
         <v>84</v>
       </c>
@@ -3363,7 +3363,7 @@
       <c r="X83" s="11"/>
       <c r="Y83" s="11"/>
     </row>
-    <row r="84" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B84" s="24" t="s">
         <v>85</v>
       </c>
@@ -3388,7 +3388,7 @@
       <c r="X84" s="11"/>
       <c r="Y84" s="11"/>
     </row>
-    <row r="85" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B85" s="24" t="s">
         <v>86</v>
       </c>
@@ -3413,7 +3413,7 @@
       <c r="X85" s="11"/>
       <c r="Y85" s="11"/>
     </row>
-    <row r="86" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B86" s="24" t="s">
         <v>87</v>
       </c>
@@ -3438,7 +3438,7 @@
       <c r="X86" s="11"/>
       <c r="Y86" s="11"/>
     </row>
-    <row r="87" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B87" s="24" t="s">
         <v>88</v>
       </c>
@@ -3463,7 +3463,7 @@
       <c r="X87" s="11"/>
       <c r="Y87" s="11"/>
     </row>
-    <row r="88" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B88" s="24" t="s">
         <v>89</v>
       </c>
@@ -3488,7 +3488,7 @@
       <c r="X88" s="11"/>
       <c r="Y88" s="11"/>
     </row>
-    <row r="89" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B89" s="24" t="s">
         <v>90</v>
       </c>
@@ -3513,7 +3513,7 @@
       <c r="X89" s="11"/>
       <c r="Y89" s="11"/>
     </row>
-    <row r="90" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B90" s="24" t="s">
         <v>91</v>
       </c>
@@ -3538,7 +3538,7 @@
       <c r="X90" s="11"/>
       <c r="Y90" s="11"/>
     </row>
-    <row r="91" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B91" s="24" t="s">
         <v>92</v>
       </c>
@@ -3563,7 +3563,7 @@
       <c r="X91" s="11"/>
       <c r="Y91" s="11"/>
     </row>
-    <row r="92" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B92" s="24" t="s">
         <v>93</v>
       </c>
@@ -3588,7 +3588,7 @@
       <c r="X92" s="11"/>
       <c r="Y92" s="11"/>
     </row>
-    <row r="93" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B93" s="24" t="s">
         <v>94</v>
       </c>
@@ -3613,7 +3613,7 @@
       <c r="X93" s="11"/>
       <c r="Y93" s="11"/>
     </row>
-    <row r="94" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B94" s="24" t="s">
         <v>95</v>
       </c>
@@ -3638,7 +3638,7 @@
       <c r="X94" s="11"/>
       <c r="Y94" s="11"/>
     </row>
-    <row r="95" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B95" s="24" t="s">
         <v>96</v>
       </c>
@@ -3663,7 +3663,7 @@
       <c r="X95" s="11"/>
       <c r="Y95" s="11"/>
     </row>
-    <row r="96" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B96" s="24" t="s">
         <v>97</v>
       </c>
@@ -3688,7 +3688,7 @@
       <c r="X96" s="11"/>
       <c r="Y96" s="11"/>
     </row>
-    <row r="97" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B97" s="24" t="s">
         <v>98</v>
       </c>
@@ -3713,7 +3713,7 @@
       <c r="X97" s="11"/>
       <c r="Y97" s="11"/>
     </row>
-    <row r="98" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B98" s="24" t="s">
         <v>99</v>
       </c>
@@ -3738,7 +3738,7 @@
       <c r="X98" s="11"/>
       <c r="Y98" s="11"/>
     </row>
-    <row r="99" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B99" s="24" t="s">
         <v>100</v>
       </c>
@@ -3763,7 +3763,7 @@
       <c r="X99" s="11"/>
       <c r="Y99" s="11"/>
     </row>
-    <row r="100" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B100" s="24" t="s">
         <v>101</v>
       </c>
@@ -3788,7 +3788,7 @@
       <c r="X100" s="11"/>
       <c r="Y100" s="11"/>
     </row>
-    <row r="101" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B101" s="24" t="s">
         <v>102</v>
       </c>
@@ -3813,7 +3813,7 @@
       <c r="X101" s="11"/>
       <c r="Y101" s="11"/>
     </row>
-    <row r="102" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B102" s="24" t="s">
         <v>103</v>
       </c>
@@ -3838,7 +3838,7 @@
       <c r="X102" s="11"/>
       <c r="Y102" s="11"/>
     </row>
-    <row r="103" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B103" s="24" t="s">
         <v>104</v>
       </c>
@@ -3863,7 +3863,7 @@
       <c r="X103" s="11"/>
       <c r="Y103" s="11"/>
     </row>
-    <row r="104" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B104" s="24" t="s">
         <v>105</v>
       </c>
@@ -3888,7 +3888,7 @@
       <c r="X104" s="11"/>
       <c r="Y104" s="11"/>
     </row>
-    <row r="105" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B105" s="24" t="s">
         <v>106</v>
       </c>
@@ -3913,7 +3913,7 @@
       <c r="X105" s="11"/>
       <c r="Y105" s="11"/>
     </row>
-    <row r="106" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B106" s="24" t="s">
         <v>107</v>
       </c>
@@ -3938,7 +3938,7 @@
       <c r="X106" s="11"/>
       <c r="Y106" s="11"/>
     </row>
-    <row r="107" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B107" s="24" t="s">
         <v>108</v>
       </c>
@@ -3963,7 +3963,7 @@
       <c r="X107" s="11"/>
       <c r="Y107" s="11"/>
     </row>
-    <row r="108" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B108" s="24" t="s">
         <v>109</v>
       </c>
@@ -3988,7 +3988,7 @@
       <c r="X108" s="11"/>
       <c r="Y108" s="11"/>
     </row>
-    <row r="109" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B109" s="24" t="s">
         <v>110</v>
       </c>
@@ -4013,7 +4013,7 @@
       <c r="X109" s="11"/>
       <c r="Y109" s="11"/>
     </row>
-    <row r="110" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B110" s="24" t="s">
         <v>111</v>
       </c>
@@ -4038,7 +4038,7 @@
       <c r="X110" s="11"/>
       <c r="Y110" s="11"/>
     </row>
-    <row r="111" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="111" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B111" s="24" t="s">
         <v>112</v>
       </c>
@@ -4063,7 +4063,7 @@
       <c r="X111" s="11"/>
       <c r="Y111" s="11"/>
     </row>
-    <row r="112" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B112" s="24" t="s">
         <v>113</v>
       </c>
@@ -4088,7 +4088,7 @@
       <c r="X112" s="11"/>
       <c r="Y112" s="11"/>
     </row>
-    <row r="113" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="113" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B113" s="24" t="s">
         <v>114</v>
       </c>
@@ -4113,7 +4113,7 @@
       <c r="X113" s="11"/>
       <c r="Y113" s="11"/>
     </row>
-    <row r="114" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="114" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B114" s="24" t="s">
         <v>115</v>
       </c>
@@ -4138,7 +4138,7 @@
       <c r="X114" s="11"/>
       <c r="Y114" s="11"/>
     </row>
-    <row r="115" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B115" s="24" t="s">
         <v>116</v>
       </c>
@@ -4163,7 +4163,7 @@
       <c r="X115" s="11"/>
       <c r="Y115" s="11"/>
     </row>
-    <row r="116" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="116" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B116" s="24" t="s">
         <v>117</v>
       </c>
@@ -4188,7 +4188,7 @@
       <c r="X116" s="11"/>
       <c r="Y116" s="11"/>
     </row>
-    <row r="117" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="117" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B117" s="24" t="s">
         <v>118</v>
       </c>
@@ -4213,7 +4213,7 @@
       <c r="X117" s="11"/>
       <c r="Y117" s="11"/>
     </row>
-    <row r="118" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="118" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B118" s="24" t="s">
         <v>119</v>
       </c>
@@ -4238,7 +4238,7 @@
       <c r="X118" s="11"/>
       <c r="Y118" s="11"/>
     </row>
-    <row r="119" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="119" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B119" s="24" t="s">
         <v>120</v>
       </c>
@@ -4263,7 +4263,7 @@
       <c r="X119" s="11"/>
       <c r="Y119" s="11"/>
     </row>
-    <row r="120" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="120" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B120" s="24" t="s">
         <v>121</v>
       </c>
@@ -4288,7 +4288,7 @@
       <c r="X120" s="11"/>
       <c r="Y120" s="11"/>
     </row>
-    <row r="121" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="121" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B121" s="24" t="s">
         <v>122</v>
       </c>
@@ -4313,7 +4313,7 @@
       <c r="X121" s="11"/>
       <c r="Y121" s="11"/>
     </row>
-    <row r="122" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="122" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B122" s="24" t="s">
         <v>123</v>
       </c>
@@ -4338,7 +4338,7 @@
       <c r="X122" s="11"/>
       <c r="Y122" s="11"/>
     </row>
-    <row r="123" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="123" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B123" s="24" t="s">
         <v>124</v>
       </c>
@@ -4363,7 +4363,7 @@
       <c r="X123" s="11"/>
       <c r="Y123" s="11"/>
     </row>
-    <row r="124" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="124" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B124" s="24" t="s">
         <v>125</v>
       </c>
@@ -4388,7 +4388,7 @@
       <c r="X124" s="11"/>
       <c r="Y124" s="11"/>
     </row>
-    <row r="125" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="125" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B125" s="24" t="s">
         <v>126</v>
       </c>
@@ -4413,7 +4413,7 @@
       <c r="X125" s="11"/>
       <c r="Y125" s="11"/>
     </row>
-    <row r="126" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="126" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B126" s="24" t="s">
         <v>127</v>
       </c>
@@ -4438,7 +4438,7 @@
       <c r="X126" s="11"/>
       <c r="Y126" s="11"/>
     </row>
-    <row r="127" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B127" s="24" t="s">
         <v>128</v>
       </c>
@@ -4463,7 +4463,7 @@
       <c r="X127" s="11"/>
       <c r="Y127" s="11"/>
     </row>
-    <row r="128" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="128" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B128" s="24" t="s">
         <v>129</v>
       </c>
@@ -4488,7 +4488,7 @@
       <c r="X128" s="11"/>
       <c r="Y128" s="11"/>
     </row>
-    <row r="129" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="129" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B129" s="24" t="s">
         <v>130</v>
       </c>
@@ -4513,7 +4513,7 @@
       <c r="X129" s="11"/>
       <c r="Y129" s="11"/>
     </row>
-    <row r="130" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="130" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B130" s="24" t="s">
         <v>131</v>
       </c>
@@ -4538,7 +4538,7 @@
       <c r="X130" s="11"/>
       <c r="Y130" s="11"/>
     </row>
-    <row r="131" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="131" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B131" s="24" t="s">
         <v>132</v>
       </c>
@@ -4563,7 +4563,7 @@
       <c r="X131" s="11"/>
       <c r="Y131" s="11"/>
     </row>
-    <row r="132" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="132" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B132" s="24" t="s">
         <v>133</v>
       </c>
@@ -4588,7 +4588,7 @@
       <c r="X132" s="11"/>
       <c r="Y132" s="11"/>
     </row>
-    <row r="133" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="133" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B133" s="24" t="s">
         <v>134</v>
       </c>
@@ -4613,7 +4613,7 @@
       <c r="X133" s="11"/>
       <c r="Y133" s="11"/>
     </row>
-    <row r="134" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="134" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B134" s="24" t="s">
         <v>135</v>
       </c>
@@ -4638,7 +4638,7 @@
       <c r="X134" s="11"/>
       <c r="Y134" s="11"/>
     </row>
-    <row r="135" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="135" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B135" s="24" t="s">
         <v>136</v>
       </c>
@@ -4663,7 +4663,7 @@
       <c r="X135" s="11"/>
       <c r="Y135" s="11"/>
     </row>
-    <row r="136" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="136" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B136" s="24" t="s">
         <v>137</v>
       </c>
@@ -4688,7 +4688,7 @@
       <c r="X136" s="11"/>
       <c r="Y136" s="11"/>
     </row>
-    <row r="137" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="137" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B137" s="24" t="s">
         <v>138</v>
       </c>
@@ -4713,7 +4713,7 @@
       <c r="X137" s="11"/>
       <c r="Y137" s="11"/>
     </row>
-    <row r="138" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="138" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B138" s="24" t="s">
         <v>139</v>
       </c>
@@ -4738,14 +4738,14 @@
       <c r="X138" s="11"/>
       <c r="Y138" s="11"/>
     </row>
-    <row r="139" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="139" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B139" s="24" t="s">
         <v>140</v>
       </c>
       <c r="C139" s="19" t="s">
         <v>141</v>
       </c>
-      <c r="D139" s="30" t="s">
+      <c r="D139" s="19" t="s">
         <v>142</v>
       </c>
       <c r="E139" s="19" t="s">
@@ -4774,7 +4774,7 @@
       <c r="X139" s="11"/>
       <c r="Y139" s="11"/>
     </row>
-    <row r="140" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="140" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B140" s="24" t="s">
         <v>144</v>
       </c>
@@ -4799,7 +4799,7 @@
       <c r="X140" s="11"/>
       <c r="Y140" s="11"/>
     </row>
-    <row r="141" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="141" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B141" s="24" t="s">
         <v>145</v>
       </c>
@@ -4824,7 +4824,7 @@
       <c r="X141" s="11"/>
       <c r="Y141" s="11"/>
     </row>
-    <row r="142" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="142" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B142" s="24" t="s">
         <v>146</v>
       </c>
@@ -4849,7 +4849,7 @@
       <c r="X142" s="11"/>
       <c r="Y142" s="11"/>
     </row>
-    <row r="143" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="143" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B143" s="24" t="s">
         <v>147</v>
       </c>
@@ -4874,7 +4874,7 @@
       <c r="X143" s="11"/>
       <c r="Y143" s="11"/>
     </row>
-    <row r="144" spans="2:25" x14ac:dyDescent="0.25">
+    <row r="144" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B144" s="24" t="s">
         <v>148</v>
       </c>
@@ -4899,7 +4899,7 @@
       <c r="X144" s="11"/>
       <c r="Y144" s="11"/>
     </row>
-    <row r="145" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B145" s="24" t="s">
         <v>149</v>
       </c>
@@ -4924,7 +4924,7 @@
       <c r="X145" s="11"/>
       <c r="Y145" s="11"/>
     </row>
-    <row r="146" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B146" s="24" t="s">
         <v>150</v>
       </c>
@@ -4949,7 +4949,7 @@
       <c r="X146" s="11"/>
       <c r="Y146" s="11"/>
     </row>
-    <row r="147" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B147" s="24" t="s">
         <v>151</v>
       </c>
@@ -4974,7 +4974,7 @@
       <c r="X147" s="11"/>
       <c r="Y147" s="11"/>
     </row>
-    <row r="148" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B148" s="24" t="s">
         <v>152</v>
       </c>
@@ -4999,7 +4999,7 @@
       <c r="X148" s="11"/>
       <c r="Y148" s="11"/>
     </row>
-    <row r="149" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B149" s="24" t="s">
         <v>153</v>
       </c>
@@ -5024,7 +5024,7 @@
       <c r="X149" s="11"/>
       <c r="Y149" s="11"/>
     </row>
-    <row r="150" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A150" s="19" t="s">
         <v>154</v>
       </c>
@@ -5060,7 +5060,7 @@
       <c r="X150" s="11"/>
       <c r="Y150" s="11"/>
     </row>
-    <row r="151" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B151" s="24" t="s">
         <v>156</v>
       </c>
@@ -5085,7 +5085,7 @@
       <c r="X151" s="11"/>
       <c r="Y151" s="11"/>
     </row>
-    <row r="152" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B152" s="24" t="s">
         <v>157</v>
       </c>
@@ -5110,7 +5110,7 @@
       <c r="X152" s="11"/>
       <c r="Y152" s="11"/>
     </row>
-    <row r="153" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B153" s="24" t="s">
         <v>158</v>
       </c>
@@ -5135,7 +5135,7 @@
       <c r="X153" s="11"/>
       <c r="Y153" s="11"/>
     </row>
-    <row r="154" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B154" s="24" t="s">
         <v>159</v>
       </c>
@@ -5160,7 +5160,7 @@
       <c r="X154" s="11"/>
       <c r="Y154" s="11"/>
     </row>
-    <row r="155" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:25" x14ac:dyDescent="0.3">
       <c r="D155" s="29"/>
       <c r="G155" s="11"/>
       <c r="H155" s="11"/>
@@ -5182,7 +5182,7 @@
       <c r="X155" s="11"/>
       <c r="Y155" s="11"/>
     </row>
-    <row r="156" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:25" x14ac:dyDescent="0.3">
       <c r="D156" s="29"/>
       <c r="G156" s="11"/>
       <c r="H156" s="11"/>
@@ -5204,7 +5204,7 @@
       <c r="X156" s="11"/>
       <c r="Y156" s="11"/>
     </row>
-    <row r="157" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:25" x14ac:dyDescent="0.3">
       <c r="D157" s="29"/>
       <c r="G157" s="11"/>
       <c r="H157" s="11"/>
@@ -5226,7 +5226,7 @@
       <c r="X157" s="11"/>
       <c r="Y157" s="11"/>
     </row>
-    <row r="158" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:25" x14ac:dyDescent="0.3">
       <c r="D158" s="29"/>
       <c r="G158" s="11"/>
       <c r="H158" s="11"/>
@@ -5248,7 +5248,7 @@
       <c r="X158" s="11"/>
       <c r="Y158" s="11"/>
     </row>
-    <row r="159" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:25" x14ac:dyDescent="0.3">
       <c r="D159" s="29"/>
       <c r="G159" s="11"/>
       <c r="H159" s="11"/>
@@ -5270,7 +5270,7 @@
       <c r="X159" s="11"/>
       <c r="Y159" s="11"/>
     </row>
-    <row r="160" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:25" x14ac:dyDescent="0.3">
       <c r="D160" s="29"/>
       <c r="G160" s="11"/>
       <c r="H160" s="11"/>
@@ -5292,7 +5292,7 @@
       <c r="X160" s="11"/>
       <c r="Y160" s="11"/>
     </row>
-    <row r="161" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="161" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D161" s="29"/>
       <c r="G161" s="11"/>
       <c r="H161" s="11"/>
@@ -5314,7 +5314,7 @@
       <c r="X161" s="11"/>
       <c r="Y161" s="11"/>
     </row>
-    <row r="162" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="162" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D162" s="29"/>
       <c r="G162" s="11"/>
       <c r="H162" s="11"/>
@@ -5336,7 +5336,7 @@
       <c r="X162" s="11"/>
       <c r="Y162" s="11"/>
     </row>
-    <row r="163" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="163" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D163" s="29"/>
       <c r="G163" s="11"/>
       <c r="H163" s="11"/>
@@ -5358,7 +5358,7 @@
       <c r="X163" s="11"/>
       <c r="Y163" s="11"/>
     </row>
-    <row r="164" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="164" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D164" s="29"/>
       <c r="G164" s="11"/>
       <c r="H164" s="11"/>
@@ -5380,7 +5380,7 @@
       <c r="X164" s="11"/>
       <c r="Y164" s="11"/>
     </row>
-    <row r="165" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="165" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D165" s="29"/>
       <c r="G165" s="11"/>
       <c r="H165" s="11"/>
@@ -5402,7 +5402,7 @@
       <c r="X165" s="11"/>
       <c r="Y165" s="11"/>
     </row>
-    <row r="166" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="166" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D166" s="29"/>
       <c r="G166" s="11"/>
       <c r="H166" s="11"/>
@@ -5424,7 +5424,7 @@
       <c r="X166" s="11"/>
       <c r="Y166" s="11"/>
     </row>
-    <row r="167" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="167" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D167" s="29"/>
       <c r="G167" s="11"/>
       <c r="H167" s="11"/>
@@ -5446,7 +5446,7 @@
       <c r="X167" s="11"/>
       <c r="Y167" s="11"/>
     </row>
-    <row r="168" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="168" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D168" s="29"/>
       <c r="G168" s="11"/>
       <c r="H168" s="11"/>
@@ -5468,7 +5468,7 @@
       <c r="X168" s="11"/>
       <c r="Y168" s="11"/>
     </row>
-    <row r="169" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="169" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D169" s="29"/>
       <c r="G169" s="11"/>
       <c r="H169" s="11"/>
@@ -5490,7 +5490,7 @@
       <c r="X169" s="11"/>
       <c r="Y169" s="11"/>
     </row>
-    <row r="170" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="170" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D170" s="29"/>
       <c r="G170" s="11"/>
       <c r="H170" s="11"/>
@@ -5512,7 +5512,7 @@
       <c r="X170" s="11"/>
       <c r="Y170" s="11"/>
     </row>
-    <row r="171" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="171" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D171" s="29"/>
       <c r="G171" s="11"/>
       <c r="H171" s="11"/>
@@ -5534,7 +5534,7 @@
       <c r="X171" s="11"/>
       <c r="Y171" s="11"/>
     </row>
-    <row r="172" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="172" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D172" s="29"/>
       <c r="G172" s="11"/>
       <c r="H172" s="11"/>
@@ -5556,7 +5556,7 @@
       <c r="X172" s="11"/>
       <c r="Y172" s="11"/>
     </row>
-    <row r="173" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="173" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D173" s="29"/>
       <c r="G173" s="11"/>
       <c r="H173" s="11"/>
@@ -5578,7 +5578,7 @@
       <c r="X173" s="11"/>
       <c r="Y173" s="11"/>
     </row>
-    <row r="174" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="174" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D174" s="29"/>
       <c r="G174" s="11"/>
       <c r="H174" s="11"/>
@@ -5600,7 +5600,7 @@
       <c r="X174" s="11"/>
       <c r="Y174" s="11"/>
     </row>
-    <row r="175" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="175" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D175" s="29"/>
       <c r="G175" s="11"/>
       <c r="H175" s="11"/>
@@ -5622,7 +5622,7 @@
       <c r="X175" s="11"/>
       <c r="Y175" s="11"/>
     </row>
-    <row r="176" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="176" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D176" s="29"/>
       <c r="G176" s="11"/>
       <c r="H176" s="11"/>
@@ -5644,7 +5644,7 @@
       <c r="X176" s="11"/>
       <c r="Y176" s="11"/>
     </row>
-    <row r="177" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="177" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D177" s="29"/>
       <c r="G177" s="11"/>
       <c r="H177" s="11"/>
@@ -5666,7 +5666,7 @@
       <c r="X177" s="11"/>
       <c r="Y177" s="11"/>
     </row>
-    <row r="178" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="178" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D178" s="29"/>
       <c r="G178" s="11"/>
       <c r="H178" s="11"/>
@@ -5688,7 +5688,7 @@
       <c r="X178" s="11"/>
       <c r="Y178" s="11"/>
     </row>
-    <row r="179" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="179" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D179" s="29"/>
       <c r="G179" s="11"/>
       <c r="H179" s="11"/>
@@ -5710,7 +5710,7 @@
       <c r="X179" s="11"/>
       <c r="Y179" s="11"/>
     </row>
-    <row r="180" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="180" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D180" s="29"/>
       <c r="G180" s="11"/>
       <c r="H180" s="11"/>
@@ -5732,7 +5732,7 @@
       <c r="X180" s="11"/>
       <c r="Y180" s="11"/>
     </row>
-    <row r="181" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="181" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D181" s="29"/>
       <c r="G181" s="11"/>
       <c r="H181" s="11"/>
@@ -5754,7 +5754,7 @@
       <c r="X181" s="11"/>
       <c r="Y181" s="11"/>
     </row>
-    <row r="182" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="182" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D182" s="29"/>
       <c r="G182" s="11"/>
       <c r="H182" s="11"/>
@@ -5776,7 +5776,7 @@
       <c r="X182" s="11"/>
       <c r="Y182" s="11"/>
     </row>
-    <row r="183" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="183" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D183" s="29"/>
       <c r="G183" s="11"/>
       <c r="H183" s="11"/>
@@ -5798,7 +5798,7 @@
       <c r="X183" s="11"/>
       <c r="Y183" s="11"/>
     </row>
-    <row r="184" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="184" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D184" s="29"/>
       <c r="G184" s="11"/>
       <c r="H184" s="11"/>
@@ -5820,7 +5820,7 @@
       <c r="X184" s="11"/>
       <c r="Y184" s="11"/>
     </row>
-    <row r="185" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="185" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D185" s="29"/>
       <c r="G185" s="11"/>
       <c r="H185" s="11"/>
@@ -5842,7 +5842,7 @@
       <c r="X185" s="11"/>
       <c r="Y185" s="11"/>
     </row>
-    <row r="186" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="186" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D186" s="29"/>
       <c r="G186" s="11"/>
       <c r="H186" s="11"/>
@@ -5864,7 +5864,7 @@
       <c r="X186" s="11"/>
       <c r="Y186" s="11"/>
     </row>
-    <row r="187" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="187" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D187" s="29"/>
       <c r="G187" s="11"/>
       <c r="H187" s="11"/>
@@ -5886,7 +5886,7 @@
       <c r="X187" s="11"/>
       <c r="Y187" s="11"/>
     </row>
-    <row r="188" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="188" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D188" s="29"/>
       <c r="G188" s="11"/>
       <c r="H188" s="11"/>
@@ -5908,7 +5908,7 @@
       <c r="X188" s="11"/>
       <c r="Y188" s="11"/>
     </row>
-    <row r="189" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="189" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D189" s="29"/>
       <c r="G189" s="11"/>
       <c r="H189" s="11"/>
@@ -5930,7 +5930,7 @@
       <c r="X189" s="11"/>
       <c r="Y189" s="11"/>
     </row>
-    <row r="190" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="190" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D190" s="29"/>
       <c r="G190" s="11"/>
       <c r="H190" s="11"/>
@@ -5952,7 +5952,7 @@
       <c r="X190" s="11"/>
       <c r="Y190" s="11"/>
     </row>
-    <row r="191" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="191" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D191" s="29"/>
       <c r="G191" s="11"/>
       <c r="H191" s="11"/>
@@ -5974,7 +5974,7 @@
       <c r="X191" s="11"/>
       <c r="Y191" s="11"/>
     </row>
-    <row r="192" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="192" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D192" s="29"/>
       <c r="G192" s="11"/>
       <c r="H192" s="11"/>
@@ -5996,7 +5996,7 @@
       <c r="X192" s="11"/>
       <c r="Y192" s="11"/>
     </row>
-    <row r="193" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="193" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D193" s="29"/>
       <c r="G193" s="11"/>
       <c r="H193" s="11"/>
@@ -6018,7 +6018,7 @@
       <c r="X193" s="11"/>
       <c r="Y193" s="11"/>
     </row>
-    <row r="194" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="194" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D194" s="29"/>
       <c r="G194" s="11"/>
       <c r="H194" s="11"/>
@@ -6040,7 +6040,7 @@
       <c r="X194" s="11"/>
       <c r="Y194" s="11"/>
     </row>
-    <row r="195" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="195" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D195" s="29"/>
       <c r="G195" s="11"/>
       <c r="H195" s="11"/>
@@ -6062,7 +6062,7 @@
       <c r="X195" s="11"/>
       <c r="Y195" s="11"/>
     </row>
-    <row r="196" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="196" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D196" s="29"/>
       <c r="G196" s="11"/>
       <c r="H196" s="11"/>
@@ -6084,7 +6084,7 @@
       <c r="X196" s="11"/>
       <c r="Y196" s="11"/>
     </row>
-    <row r="197" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="197" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D197" s="29"/>
       <c r="G197" s="11"/>
       <c r="H197" s="11"/>
@@ -6106,7 +6106,7 @@
       <c r="X197" s="11"/>
       <c r="Y197" s="11"/>
     </row>
-    <row r="198" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="198" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D198" s="29"/>
       <c r="G198" s="11"/>
       <c r="H198" s="11"/>
@@ -6128,7 +6128,7 @@
       <c r="X198" s="11"/>
       <c r="Y198" s="11"/>
     </row>
-    <row r="199" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="199" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D199" s="29"/>
       <c r="G199" s="11"/>
       <c r="H199" s="11"/>
@@ -6150,7 +6150,7 @@
       <c r="X199" s="11"/>
       <c r="Y199" s="11"/>
     </row>
-    <row r="200" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="200" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D200" s="29"/>
       <c r="G200" s="11"/>
       <c r="H200" s="11"/>
@@ -6172,7 +6172,7 @@
       <c r="X200" s="11"/>
       <c r="Y200" s="11"/>
     </row>
-    <row r="201" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="201" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D201" s="29"/>
       <c r="G201" s="11"/>
       <c r="H201" s="11"/>
@@ -6194,7 +6194,7 @@
       <c r="X201" s="11"/>
       <c r="Y201" s="11"/>
     </row>
-    <row r="202" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="202" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D202" s="29"/>
       <c r="G202" s="11"/>
       <c r="H202" s="11"/>
@@ -6216,7 +6216,7 @@
       <c r="X202" s="11"/>
       <c r="Y202" s="11"/>
     </row>
-    <row r="203" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="203" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D203" s="29"/>
       <c r="G203" s="11"/>
       <c r="H203" s="11"/>
@@ -6238,7 +6238,7 @@
       <c r="X203" s="11"/>
       <c r="Y203" s="11"/>
     </row>
-    <row r="204" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="204" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D204" s="29"/>
       <c r="G204" s="11"/>
       <c r="H204" s="11"/>
@@ -6260,7 +6260,7 @@
       <c r="X204" s="11"/>
       <c r="Y204" s="11"/>
     </row>
-    <row r="205" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="205" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D205" s="29"/>
       <c r="G205" s="11"/>
       <c r="H205" s="11"/>
@@ -6282,7 +6282,7 @@
       <c r="X205" s="11"/>
       <c r="Y205" s="11"/>
     </row>
-    <row r="206" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="206" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D206" s="29"/>
       <c r="G206" s="11"/>
       <c r="H206" s="11"/>
@@ -6304,7 +6304,7 @@
       <c r="X206" s="11"/>
       <c r="Y206" s="11"/>
     </row>
-    <row r="207" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="207" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D207" s="29"/>
       <c r="G207" s="11"/>
       <c r="H207" s="11"/>
@@ -6326,7 +6326,7 @@
       <c r="X207" s="11"/>
       <c r="Y207" s="11"/>
     </row>
-    <row r="208" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="208" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D208" s="29"/>
       <c r="G208" s="11"/>
       <c r="H208" s="11"/>
@@ -6348,7 +6348,7 @@
       <c r="X208" s="11"/>
       <c r="Y208" s="11"/>
     </row>
-    <row r="209" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="209" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D209" s="29"/>
       <c r="G209" s="11"/>
       <c r="H209" s="11"/>
@@ -6370,7 +6370,7 @@
       <c r="X209" s="11"/>
       <c r="Y209" s="11"/>
     </row>
-    <row r="210" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="210" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D210" s="29"/>
       <c r="G210" s="11"/>
       <c r="H210" s="11"/>
@@ -6392,7 +6392,7 @@
       <c r="X210" s="11"/>
       <c r="Y210" s="11"/>
     </row>
-    <row r="211" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="211" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D211" s="29"/>
       <c r="G211" s="11"/>
       <c r="H211" s="11"/>
@@ -6414,7 +6414,7 @@
       <c r="X211" s="11"/>
       <c r="Y211" s="11"/>
     </row>
-    <row r="212" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="212" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D212" s="29"/>
       <c r="G212" s="11"/>
       <c r="H212" s="11"/>
@@ -6436,7 +6436,7 @@
       <c r="X212" s="11"/>
       <c r="Y212" s="11"/>
     </row>
-    <row r="213" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="213" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D213" s="29"/>
       <c r="G213" s="11"/>
       <c r="H213" s="11"/>
@@ -6458,7 +6458,7 @@
       <c r="X213" s="11"/>
       <c r="Y213" s="11"/>
     </row>
-    <row r="214" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="214" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D214" s="29"/>
       <c r="G214" s="11"/>
       <c r="H214" s="11"/>
@@ -6480,7 +6480,7 @@
       <c r="X214" s="11"/>
       <c r="Y214" s="11"/>
     </row>
-    <row r="215" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="215" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D215" s="29"/>
       <c r="G215" s="11"/>
       <c r="H215" s="11"/>
@@ -6502,7 +6502,7 @@
       <c r="X215" s="11"/>
       <c r="Y215" s="11"/>
     </row>
-    <row r="216" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="216" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D216" s="29"/>
       <c r="G216" s="11"/>
       <c r="H216" s="11"/>
@@ -6524,7 +6524,7 @@
       <c r="X216" s="11"/>
       <c r="Y216" s="11"/>
     </row>
-    <row r="217" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="217" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D217" s="29"/>
       <c r="G217" s="11"/>
       <c r="H217" s="11"/>
@@ -6546,7 +6546,7 @@
       <c r="X217" s="11"/>
       <c r="Y217" s="11"/>
     </row>
-    <row r="218" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="218" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D218" s="29"/>
       <c r="G218" s="11"/>
       <c r="H218" s="11"/>
@@ -6568,7 +6568,7 @@
       <c r="X218" s="11"/>
       <c r="Y218" s="11"/>
     </row>
-    <row r="219" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="219" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D219" s="29"/>
       <c r="G219" s="11"/>
       <c r="H219" s="11"/>
@@ -6590,7 +6590,7 @@
       <c r="X219" s="11"/>
       <c r="Y219" s="11"/>
     </row>
-    <row r="220" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="220" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D220" s="29"/>
       <c r="G220" s="11"/>
       <c r="H220" s="11"/>
@@ -6612,7 +6612,7 @@
       <c r="X220" s="11"/>
       <c r="Y220" s="11"/>
     </row>
-    <row r="221" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="221" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D221" s="29"/>
       <c r="G221" s="11"/>
       <c r="H221" s="11"/>
@@ -6634,7 +6634,7 @@
       <c r="X221" s="11"/>
       <c r="Y221" s="11"/>
     </row>
-    <row r="222" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="222" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D222" s="29"/>
       <c r="G222" s="11"/>
       <c r="H222" s="11"/>
@@ -6656,7 +6656,7 @@
       <c r="X222" s="11"/>
       <c r="Y222" s="11"/>
     </row>
-    <row r="223" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="223" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D223" s="29"/>
       <c r="G223" s="11"/>
       <c r="H223" s="11"/>
@@ -6678,7 +6678,7 @@
       <c r="X223" s="11"/>
       <c r="Y223" s="11"/>
     </row>
-    <row r="224" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="224" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D224" s="29"/>
       <c r="G224" s="11"/>
       <c r="H224" s="11"/>
@@ -6700,7 +6700,7 @@
       <c r="X224" s="11"/>
       <c r="Y224" s="11"/>
     </row>
-    <row r="225" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="225" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D225" s="29"/>
       <c r="G225" s="11"/>
       <c r="H225" s="11"/>
@@ -6722,7 +6722,7 @@
       <c r="X225" s="11"/>
       <c r="Y225" s="11"/>
     </row>
-    <row r="226" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="226" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D226" s="29"/>
       <c r="G226" s="11"/>
       <c r="H226" s="11"/>
@@ -6744,7 +6744,7 @@
       <c r="X226" s="11"/>
       <c r="Y226" s="11"/>
     </row>
-    <row r="227" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="227" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D227" s="29"/>
       <c r="G227" s="11"/>
       <c r="H227" s="11"/>
@@ -6766,7 +6766,7 @@
       <c r="X227" s="11"/>
       <c r="Y227" s="11"/>
     </row>
-    <row r="228" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="228" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D228" s="29"/>
       <c r="G228" s="11"/>
       <c r="H228" s="11"/>
@@ -6788,7 +6788,7 @@
       <c r="X228" s="11"/>
       <c r="Y228" s="11"/>
     </row>
-    <row r="229" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="229" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D229" s="29"/>
       <c r="G229" s="11"/>
       <c r="H229" s="11"/>
@@ -6810,7 +6810,7 @@
       <c r="X229" s="11"/>
       <c r="Y229" s="11"/>
     </row>
-    <row r="230" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="230" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D230" s="29"/>
       <c r="G230" s="11"/>
       <c r="H230" s="11"/>
@@ -6832,7 +6832,7 @@
       <c r="X230" s="11"/>
       <c r="Y230" s="11"/>
     </row>
-    <row r="231" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="231" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D231" s="29"/>
       <c r="G231" s="11"/>
       <c r="H231" s="11"/>
@@ -6854,7 +6854,7 @@
       <c r="X231" s="11"/>
       <c r="Y231" s="11"/>
     </row>
-    <row r="232" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="232" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D232" s="29"/>
       <c r="G232" s="11"/>
       <c r="H232" s="11"/>
@@ -6876,7 +6876,7 @@
       <c r="X232" s="11"/>
       <c r="Y232" s="11"/>
     </row>
-    <row r="233" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="233" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D233" s="29"/>
       <c r="G233" s="11"/>
       <c r="H233" s="11"/>
@@ -6898,7 +6898,7 @@
       <c r="X233" s="11"/>
       <c r="Y233" s="11"/>
     </row>
-    <row r="234" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="234" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D234" s="29"/>
       <c r="G234" s="11"/>
       <c r="H234" s="11"/>
@@ -6920,7 +6920,7 @@
       <c r="X234" s="11"/>
       <c r="Y234" s="11"/>
     </row>
-    <row r="235" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="235" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D235" s="29"/>
       <c r="G235" s="11"/>
       <c r="H235" s="11"/>
@@ -6942,7 +6942,7 @@
       <c r="X235" s="11"/>
       <c r="Y235" s="11"/>
     </row>
-    <row r="236" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="236" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D236" s="29"/>
       <c r="G236" s="11"/>
       <c r="H236" s="11"/>
@@ -6964,7 +6964,7 @@
       <c r="X236" s="11"/>
       <c r="Y236" s="11"/>
     </row>
-    <row r="237" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="237" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D237" s="29"/>
       <c r="G237" s="11"/>
       <c r="H237" s="11"/>
@@ -6986,7 +6986,7 @@
       <c r="X237" s="11"/>
       <c r="Y237" s="11"/>
     </row>
-    <row r="238" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="238" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D238" s="29"/>
       <c r="G238" s="11"/>
       <c r="H238" s="11"/>
@@ -7008,7 +7008,7 @@
       <c r="X238" s="11"/>
       <c r="Y238" s="11"/>
     </row>
-    <row r="239" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="239" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D239" s="29"/>
       <c r="G239" s="11"/>
       <c r="H239" s="11"/>
@@ -7030,7 +7030,7 @@
       <c r="X239" s="11"/>
       <c r="Y239" s="11"/>
     </row>
-    <row r="240" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="240" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D240" s="29"/>
       <c r="G240" s="11"/>
       <c r="H240" s="11"/>
@@ -7052,7 +7052,7 @@
       <c r="X240" s="11"/>
       <c r="Y240" s="11"/>
     </row>
-    <row r="241" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="241" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D241" s="29"/>
       <c r="G241" s="11"/>
       <c r="H241" s="11"/>
@@ -7074,7 +7074,7 @@
       <c r="X241" s="11"/>
       <c r="Y241" s="11"/>
     </row>
-    <row r="242" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="242" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D242" s="29"/>
       <c r="G242" s="11"/>
       <c r="H242" s="11"/>
@@ -7096,7 +7096,7 @@
       <c r="X242" s="11"/>
       <c r="Y242" s="11"/>
     </row>
-    <row r="243" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="243" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D243" s="29"/>
       <c r="G243" s="11"/>
       <c r="H243" s="11"/>
@@ -7118,7 +7118,7 @@
       <c r="X243" s="11"/>
       <c r="Y243" s="11"/>
     </row>
-    <row r="244" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="244" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D244" s="29"/>
       <c r="G244" s="11"/>
       <c r="H244" s="11"/>
@@ -7140,7 +7140,7 @@
       <c r="X244" s="11"/>
       <c r="Y244" s="11"/>
     </row>
-    <row r="245" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="245" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D245" s="29"/>
       <c r="G245" s="11"/>
       <c r="H245" s="11"/>
@@ -7162,7 +7162,7 @@
       <c r="X245" s="11"/>
       <c r="Y245" s="11"/>
     </row>
-    <row r="246" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="246" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D246" s="29"/>
       <c r="G246" s="11"/>
       <c r="H246" s="11"/>
@@ -7184,7 +7184,7 @@
       <c r="X246" s="11"/>
       <c r="Y246" s="11"/>
     </row>
-    <row r="247" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="247" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D247" s="29"/>
       <c r="G247" s="11"/>
       <c r="H247" s="11"/>
@@ -7206,7 +7206,7 @@
       <c r="X247" s="11"/>
       <c r="Y247" s="11"/>
     </row>
-    <row r="248" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="248" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D248" s="29"/>
       <c r="G248" s="11"/>
       <c r="H248" s="11"/>
@@ -7228,7 +7228,7 @@
       <c r="X248" s="11"/>
       <c r="Y248" s="11"/>
     </row>
-    <row r="249" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="249" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D249" s="29"/>
       <c r="G249" s="11"/>
       <c r="H249" s="11"/>
@@ -7250,7 +7250,7 @@
       <c r="X249" s="11"/>
       <c r="Y249" s="11"/>
     </row>
-    <row r="250" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="250" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D250" s="29"/>
       <c r="G250" s="11"/>
       <c r="H250" s="11"/>
@@ -7272,7 +7272,7 @@
       <c r="X250" s="11"/>
       <c r="Y250" s="11"/>
     </row>
-    <row r="251" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="251" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D251" s="29"/>
       <c r="G251" s="11"/>
       <c r="H251" s="11"/>
@@ -7294,7 +7294,7 @@
       <c r="X251" s="11"/>
       <c r="Y251" s="11"/>
     </row>
-    <row r="252" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="252" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D252" s="29"/>
       <c r="G252" s="11"/>
       <c r="H252" s="11"/>
@@ -7316,7 +7316,7 @@
       <c r="X252" s="11"/>
       <c r="Y252" s="11"/>
     </row>
-    <row r="253" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="253" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D253" s="29"/>
       <c r="G253" s="11"/>
       <c r="H253" s="11"/>
@@ -7338,7 +7338,7 @@
       <c r="X253" s="11"/>
       <c r="Y253" s="11"/>
     </row>
-    <row r="254" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="254" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D254" s="29"/>
       <c r="G254" s="11"/>
       <c r="H254" s="11"/>
@@ -7360,7 +7360,7 @@
       <c r="X254" s="11"/>
       <c r="Y254" s="11"/>
     </row>
-    <row r="255" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="255" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D255" s="29"/>
       <c r="G255" s="11"/>
       <c r="H255" s="11"/>
@@ -7382,7 +7382,7 @@
       <c r="X255" s="11"/>
       <c r="Y255" s="11"/>
     </row>
-    <row r="256" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="256" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D256" s="29"/>
       <c r="G256" s="11"/>
       <c r="H256" s="11"/>
@@ -7404,7 +7404,7 @@
       <c r="X256" s="11"/>
       <c r="Y256" s="11"/>
     </row>
-    <row r="257" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="257" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D257" s="29"/>
       <c r="G257" s="11"/>
       <c r="H257" s="11"/>
@@ -7426,7 +7426,7 @@
       <c r="X257" s="11"/>
       <c r="Y257" s="11"/>
     </row>
-    <row r="258" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="258" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D258" s="29"/>
       <c r="G258" s="11"/>
       <c r="H258" s="11"/>
@@ -7448,7 +7448,7 @@
       <c r="X258" s="11"/>
       <c r="Y258" s="11"/>
     </row>
-    <row r="259" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="259" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D259" s="29"/>
       <c r="G259" s="11"/>
       <c r="H259" s="11"/>
@@ -7470,7 +7470,7 @@
       <c r="X259" s="11"/>
       <c r="Y259" s="11"/>
     </row>
-    <row r="260" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="260" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D260" s="29"/>
       <c r="G260" s="11"/>
       <c r="H260" s="11"/>
@@ -7492,7 +7492,7 @@
       <c r="X260" s="11"/>
       <c r="Y260" s="11"/>
     </row>
-    <row r="261" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="261" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D261" s="29"/>
       <c r="G261" s="11"/>
       <c r="H261" s="11"/>
@@ -7514,7 +7514,7 @@
       <c r="X261" s="11"/>
       <c r="Y261" s="11"/>
     </row>
-    <row r="262" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="262" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D262" s="29"/>
       <c r="G262" s="11"/>
       <c r="H262" s="11"/>
@@ -7536,7 +7536,7 @@
       <c r="X262" s="11"/>
       <c r="Y262" s="11"/>
     </row>
-    <row r="263" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="263" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D263" s="29"/>
       <c r="G263" s="11"/>
       <c r="H263" s="11"/>
@@ -7558,7 +7558,7 @@
       <c r="X263" s="11"/>
       <c r="Y263" s="11"/>
     </row>
-    <row r="264" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="264" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D264" s="29"/>
       <c r="G264" s="11"/>
       <c r="H264" s="11"/>
@@ -7580,7 +7580,7 @@
       <c r="X264" s="11"/>
       <c r="Y264" s="11"/>
     </row>
-    <row r="265" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="265" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D265" s="29"/>
       <c r="G265" s="11"/>
       <c r="H265" s="11"/>
@@ -7602,7 +7602,7 @@
       <c r="X265" s="11"/>
       <c r="Y265" s="11"/>
     </row>
-    <row r="266" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="266" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D266" s="29"/>
       <c r="G266" s="11"/>
       <c r="H266" s="11"/>
@@ -7624,7 +7624,7 @@
       <c r="X266" s="11"/>
       <c r="Y266" s="11"/>
     </row>
-    <row r="267" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="267" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D267" s="29"/>
       <c r="G267" s="11"/>
       <c r="H267" s="11"/>
@@ -7646,7 +7646,7 @@
       <c r="X267" s="11"/>
       <c r="Y267" s="11"/>
     </row>
-    <row r="268" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="268" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D268" s="29"/>
       <c r="G268" s="11"/>
       <c r="H268" s="11"/>
@@ -7668,7 +7668,7 @@
       <c r="X268" s="11"/>
       <c r="Y268" s="11"/>
     </row>
-    <row r="269" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="269" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D269" s="29"/>
       <c r="G269" s="11"/>
       <c r="H269" s="11"/>
@@ -7690,7 +7690,7 @@
       <c r="X269" s="11"/>
       <c r="Y269" s="11"/>
     </row>
-    <row r="270" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="270" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D270" s="29"/>
       <c r="G270" s="11"/>
       <c r="H270" s="11"/>
@@ -7712,7 +7712,7 @@
       <c r="X270" s="11"/>
       <c r="Y270" s="11"/>
     </row>
-    <row r="271" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="271" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D271" s="29"/>
       <c r="G271" s="11"/>
       <c r="H271" s="11"/>
@@ -7734,7 +7734,7 @@
       <c r="X271" s="11"/>
       <c r="Y271" s="11"/>
     </row>
-    <row r="272" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="272" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D272" s="29"/>
       <c r="G272" s="11"/>
       <c r="H272" s="11"/>
@@ -7756,7 +7756,7 @@
       <c r="X272" s="11"/>
       <c r="Y272" s="11"/>
     </row>
-    <row r="273" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="273" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D273" s="29"/>
       <c r="G273" s="11"/>
       <c r="H273" s="11"/>
@@ -7778,7 +7778,7 @@
       <c r="X273" s="11"/>
       <c r="Y273" s="11"/>
     </row>
-    <row r="274" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="274" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D274" s="29"/>
       <c r="G274" s="11"/>
       <c r="H274" s="11"/>
@@ -7800,7 +7800,7 @@
       <c r="X274" s="11"/>
       <c r="Y274" s="11"/>
     </row>
-    <row r="275" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="275" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D275" s="29"/>
       <c r="G275" s="11"/>
       <c r="H275" s="11"/>
@@ -7822,7 +7822,7 @@
       <c r="X275" s="11"/>
       <c r="Y275" s="11"/>
     </row>
-    <row r="276" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="276" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D276" s="29"/>
       <c r="G276" s="11"/>
       <c r="H276" s="11"/>
@@ -7844,7 +7844,7 @@
       <c r="X276" s="11"/>
       <c r="Y276" s="11"/>
     </row>
-    <row r="277" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="277" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D277" s="29"/>
       <c r="G277" s="11"/>
       <c r="H277" s="11"/>
@@ -7866,7 +7866,7 @@
       <c r="X277" s="11"/>
       <c r="Y277" s="11"/>
     </row>
-    <row r="278" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="278" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D278" s="29"/>
       <c r="G278" s="11"/>
       <c r="H278" s="11"/>
@@ -7888,7 +7888,7 @@
       <c r="X278" s="11"/>
       <c r="Y278" s="11"/>
     </row>
-    <row r="279" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="279" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D279" s="29"/>
       <c r="G279" s="11"/>
       <c r="H279" s="11"/>
@@ -7910,7 +7910,7 @@
       <c r="X279" s="11"/>
       <c r="Y279" s="11"/>
     </row>
-    <row r="280" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="280" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D280" s="29"/>
       <c r="G280" s="11"/>
       <c r="H280" s="11"/>
@@ -7932,7 +7932,7 @@
       <c r="X280" s="11"/>
       <c r="Y280" s="11"/>
     </row>
-    <row r="281" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="281" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D281" s="29"/>
       <c r="G281" s="11"/>
       <c r="H281" s="11"/>
@@ -7954,7 +7954,7 @@
       <c r="X281" s="11"/>
       <c r="Y281" s="11"/>
     </row>
-    <row r="282" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="282" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D282" s="29"/>
       <c r="G282" s="11"/>
       <c r="H282" s="11"/>
@@ -7976,7 +7976,7 @@
       <c r="X282" s="11"/>
       <c r="Y282" s="11"/>
     </row>
-    <row r="283" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="283" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D283" s="29"/>
       <c r="G283" s="11"/>
       <c r="H283" s="11"/>
@@ -7998,7 +7998,7 @@
       <c r="X283" s="11"/>
       <c r="Y283" s="11"/>
     </row>
-    <row r="284" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="284" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D284" s="29"/>
       <c r="G284" s="11"/>
       <c r="H284" s="11"/>
@@ -8020,7 +8020,7 @@
       <c r="X284" s="11"/>
       <c r="Y284" s="11"/>
     </row>
-    <row r="285" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="285" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D285" s="29"/>
       <c r="G285" s="11"/>
       <c r="H285" s="11"/>
@@ -8042,7 +8042,7 @@
       <c r="X285" s="11"/>
       <c r="Y285" s="11"/>
     </row>
-    <row r="286" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="286" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D286" s="29"/>
       <c r="G286" s="11"/>
       <c r="H286" s="11"/>
@@ -8064,7 +8064,7 @@
       <c r="X286" s="11"/>
       <c r="Y286" s="11"/>
     </row>
-    <row r="287" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="287" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D287" s="29"/>
       <c r="G287" s="11"/>
       <c r="H287" s="11"/>
@@ -8086,7 +8086,7 @@
       <c r="X287" s="11"/>
       <c r="Y287" s="11"/>
     </row>
-    <row r="288" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="288" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D288" s="29"/>
       <c r="G288" s="11"/>
       <c r="H288" s="11"/>
@@ -8108,7 +8108,7 @@
       <c r="X288" s="11"/>
       <c r="Y288" s="11"/>
     </row>
-    <row r="289" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="289" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D289" s="29"/>
       <c r="G289" s="11"/>
       <c r="H289" s="11"/>
@@ -8130,7 +8130,7 @@
       <c r="X289" s="11"/>
       <c r="Y289" s="11"/>
     </row>
-    <row r="290" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="290" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D290" s="29"/>
       <c r="G290" s="11"/>
       <c r="H290" s="11"/>
@@ -8152,7 +8152,7 @@
       <c r="X290" s="11"/>
       <c r="Y290" s="11"/>
     </row>
-    <row r="291" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="291" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D291" s="29"/>
       <c r="G291" s="11"/>
       <c r="H291" s="11"/>
@@ -8174,7 +8174,7 @@
       <c r="X291" s="11"/>
       <c r="Y291" s="11"/>
     </row>
-    <row r="292" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="292" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D292" s="29"/>
       <c r="G292" s="11"/>
       <c r="H292" s="11"/>
@@ -8196,7 +8196,7 @@
       <c r="X292" s="11"/>
       <c r="Y292" s="11"/>
     </row>
-    <row r="293" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="293" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D293" s="29"/>
       <c r="G293" s="11"/>
       <c r="H293" s="11"/>
@@ -8218,7 +8218,7 @@
       <c r="X293" s="11"/>
       <c r="Y293" s="11"/>
     </row>
-    <row r="294" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="294" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D294" s="29"/>
       <c r="G294" s="11"/>
       <c r="H294" s="11"/>
@@ -8240,7 +8240,7 @@
       <c r="X294" s="11"/>
       <c r="Y294" s="11"/>
     </row>
-    <row r="295" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="295" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D295" s="29"/>
       <c r="G295" s="11"/>
       <c r="H295" s="11"/>
@@ -8262,7 +8262,7 @@
       <c r="X295" s="11"/>
       <c r="Y295" s="11"/>
     </row>
-    <row r="296" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="296" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D296" s="29"/>
       <c r="G296" s="11"/>
       <c r="H296" s="11"/>
@@ -8284,7 +8284,7 @@
       <c r="X296" s="11"/>
       <c r="Y296" s="11"/>
     </row>
-    <row r="297" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="297" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D297" s="29"/>
       <c r="G297" s="11"/>
       <c r="H297" s="11"/>
@@ -8306,7 +8306,7 @@
       <c r="X297" s="11"/>
       <c r="Y297" s="11"/>
     </row>
-    <row r="298" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="298" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D298" s="29"/>
       <c r="G298" s="11"/>
       <c r="H298" s="11"/>
@@ -8328,7 +8328,7 @@
       <c r="X298" s="11"/>
       <c r="Y298" s="11"/>
     </row>
-    <row r="299" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="299" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D299" s="29"/>
       <c r="G299" s="11"/>
       <c r="H299" s="11"/>
@@ -8350,7 +8350,7 @@
       <c r="X299" s="11"/>
       <c r="Y299" s="11"/>
     </row>
-    <row r="300" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="300" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D300" s="29"/>
       <c r="G300" s="11"/>
       <c r="H300" s="11"/>
@@ -8372,7 +8372,7 @@
       <c r="X300" s="11"/>
       <c r="Y300" s="11"/>
     </row>
-    <row r="301" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="301" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D301" s="29"/>
       <c r="G301" s="11"/>
       <c r="H301" s="11"/>
@@ -8394,7 +8394,7 @@
       <c r="X301" s="11"/>
       <c r="Y301" s="11"/>
     </row>
-    <row r="302" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="302" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D302" s="29"/>
       <c r="G302" s="11"/>
       <c r="H302" s="11"/>
@@ -8416,7 +8416,7 @@
       <c r="X302" s="11"/>
       <c r="Y302" s="11"/>
     </row>
-    <row r="303" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="303" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D303" s="29"/>
       <c r="G303" s="11"/>
       <c r="H303" s="11"/>
@@ -8438,7 +8438,7 @@
       <c r="X303" s="11"/>
       <c r="Y303" s="11"/>
     </row>
-    <row r="304" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="304" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D304" s="29"/>
       <c r="G304" s="11"/>
       <c r="H304" s="11"/>
@@ -8460,7 +8460,7 @@
       <c r="X304" s="11"/>
       <c r="Y304" s="11"/>
     </row>
-    <row r="305" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="305" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D305" s="29"/>
       <c r="G305" s="11"/>
       <c r="H305" s="11"/>
@@ -8482,7 +8482,7 @@
       <c r="X305" s="11"/>
       <c r="Y305" s="11"/>
     </row>
-    <row r="306" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="306" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D306" s="29"/>
       <c r="G306" s="11"/>
       <c r="H306" s="11"/>
@@ -8504,7 +8504,7 @@
       <c r="X306" s="11"/>
       <c r="Y306" s="11"/>
     </row>
-    <row r="307" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="307" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D307" s="29"/>
       <c r="G307" s="11"/>
       <c r="H307" s="11"/>
@@ -8526,7 +8526,7 @@
       <c r="X307" s="11"/>
       <c r="Y307" s="11"/>
     </row>
-    <row r="308" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="308" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D308" s="29"/>
       <c r="G308" s="11"/>
       <c r="H308" s="11"/>
@@ -8548,7 +8548,7 @@
       <c r="X308" s="11"/>
       <c r="Y308" s="11"/>
     </row>
-    <row r="309" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="309" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D309" s="29"/>
       <c r="G309" s="11"/>
       <c r="H309" s="11"/>
@@ -8570,7 +8570,7 @@
       <c r="X309" s="11"/>
       <c r="Y309" s="11"/>
     </row>
-    <row r="310" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="310" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D310" s="29"/>
       <c r="G310" s="11"/>
       <c r="H310" s="11"/>
@@ -8592,7 +8592,7 @@
       <c r="X310" s="11"/>
       <c r="Y310" s="11"/>
     </row>
-    <row r="311" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="311" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D311" s="29"/>
       <c r="G311" s="11"/>
       <c r="H311" s="11"/>
@@ -8614,7 +8614,7 @@
       <c r="X311" s="11"/>
       <c r="Y311" s="11"/>
     </row>
-    <row r="312" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="312" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D312" s="29"/>
       <c r="G312" s="11"/>
       <c r="H312" s="11"/>
@@ -8636,7 +8636,7 @@
       <c r="X312" s="11"/>
       <c r="Y312" s="11"/>
     </row>
-    <row r="313" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="313" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D313" s="29"/>
       <c r="G313" s="11"/>
       <c r="H313" s="11"/>
@@ -8658,7 +8658,7 @@
       <c r="X313" s="11"/>
       <c r="Y313" s="11"/>
     </row>
-    <row r="314" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="314" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D314" s="29"/>
       <c r="G314" s="11"/>
       <c r="H314" s="11"/>
@@ -8680,7 +8680,7 @@
       <c r="X314" s="11"/>
       <c r="Y314" s="11"/>
     </row>
-    <row r="315" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="315" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D315" s="29"/>
       <c r="G315" s="11"/>
       <c r="H315" s="11"/>
@@ -8702,7 +8702,7 @@
       <c r="X315" s="11"/>
       <c r="Y315" s="11"/>
     </row>
-    <row r="316" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="316" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D316" s="29"/>
       <c r="G316" s="11"/>
       <c r="H316" s="11"/>
@@ -8724,7 +8724,7 @@
       <c r="X316" s="11"/>
       <c r="Y316" s="11"/>
     </row>
-    <row r="317" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="317" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D317" s="29"/>
       <c r="G317" s="11"/>
       <c r="H317" s="11"/>
@@ -8746,7 +8746,7 @@
       <c r="X317" s="11"/>
       <c r="Y317" s="11"/>
     </row>
-    <row r="318" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="318" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D318" s="29"/>
       <c r="G318" s="11"/>
       <c r="H318" s="11"/>
@@ -8768,7 +8768,7 @@
       <c r="X318" s="11"/>
       <c r="Y318" s="11"/>
     </row>
-    <row r="319" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="319" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D319" s="29"/>
       <c r="G319" s="11"/>
       <c r="H319" s="11"/>
@@ -8790,7 +8790,7 @@
       <c r="X319" s="11"/>
       <c r="Y319" s="11"/>
     </row>
-    <row r="320" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="320" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D320" s="29"/>
       <c r="G320" s="11"/>
       <c r="H320" s="11"/>
@@ -8812,7 +8812,7 @@
       <c r="X320" s="11"/>
       <c r="Y320" s="11"/>
     </row>
-    <row r="321" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="321" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D321" s="29"/>
       <c r="G321" s="11"/>
       <c r="H321" s="11"/>
@@ -8834,7 +8834,7 @@
       <c r="X321" s="11"/>
       <c r="Y321" s="11"/>
     </row>
-    <row r="322" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="322" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D322" s="29"/>
       <c r="G322" s="11"/>
       <c r="H322" s="11"/>
@@ -8856,7 +8856,7 @@
       <c r="X322" s="11"/>
       <c r="Y322" s="11"/>
     </row>
-    <row r="323" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="323" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D323" s="29"/>
       <c r="G323" s="11"/>
       <c r="H323" s="11"/>
@@ -8878,7 +8878,7 @@
       <c r="X323" s="11"/>
       <c r="Y323" s="11"/>
     </row>
-    <row r="324" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="324" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D324" s="29"/>
       <c r="G324" s="11"/>
       <c r="H324" s="11"/>
@@ -8900,7 +8900,7 @@
       <c r="X324" s="11"/>
       <c r="Y324" s="11"/>
     </row>
-    <row r="325" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="325" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D325" s="29"/>
       <c r="G325" s="11"/>
       <c r="H325" s="11"/>
@@ -8922,7 +8922,7 @@
       <c r="X325" s="11"/>
       <c r="Y325" s="11"/>
     </row>
-    <row r="326" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="326" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D326" s="29"/>
       <c r="G326" s="11"/>
       <c r="H326" s="11"/>
@@ -8944,7 +8944,7 @@
       <c r="X326" s="11"/>
       <c r="Y326" s="11"/>
     </row>
-    <row r="327" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="327" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D327" s="29"/>
       <c r="G327" s="11"/>
       <c r="H327" s="11"/>
@@ -8966,7 +8966,7 @@
       <c r="X327" s="11"/>
       <c r="Y327" s="11"/>
     </row>
-    <row r="328" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="328" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D328" s="29"/>
       <c r="G328" s="11"/>
       <c r="H328" s="11"/>
@@ -8988,7 +8988,7 @@
       <c r="X328" s="11"/>
       <c r="Y328" s="11"/>
     </row>
-    <row r="329" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="329" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D329" s="29"/>
       <c r="G329" s="11"/>
       <c r="H329" s="11"/>
@@ -9010,7 +9010,7 @@
       <c r="X329" s="11"/>
       <c r="Y329" s="11"/>
     </row>
-    <row r="330" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="330" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D330" s="29"/>
       <c r="G330" s="11"/>
       <c r="H330" s="11"/>
@@ -9032,7 +9032,7 @@
       <c r="X330" s="11"/>
       <c r="Y330" s="11"/>
     </row>
-    <row r="331" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="331" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D331" s="29"/>
       <c r="G331" s="11"/>
       <c r="H331" s="11"/>
@@ -9054,7 +9054,7 @@
       <c r="X331" s="11"/>
       <c r="Y331" s="11"/>
     </row>
-    <row r="332" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="332" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D332" s="29"/>
       <c r="G332" s="11"/>
       <c r="H332" s="11"/>
@@ -9076,7 +9076,7 @@
       <c r="X332" s="11"/>
       <c r="Y332" s="11"/>
     </row>
-    <row r="333" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="333" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D333" s="29"/>
       <c r="G333" s="11"/>
       <c r="H333" s="11"/>
@@ -9098,7 +9098,7 @@
       <c r="X333" s="11"/>
       <c r="Y333" s="11"/>
     </row>
-    <row r="334" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="334" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D334" s="29"/>
       <c r="G334" s="11"/>
       <c r="H334" s="11"/>
@@ -9120,7 +9120,7 @@
       <c r="X334" s="11"/>
       <c r="Y334" s="11"/>
     </row>
-    <row r="335" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="335" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D335" s="29"/>
       <c r="G335" s="11"/>
       <c r="H335" s="11"/>
@@ -9142,7 +9142,7 @@
       <c r="X335" s="11"/>
       <c r="Y335" s="11"/>
     </row>
-    <row r="336" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="336" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D336" s="29"/>
       <c r="G336" s="11"/>
       <c r="H336" s="11"/>
@@ -9164,7 +9164,7 @@
       <c r="X336" s="11"/>
       <c r="Y336" s="11"/>
     </row>
-    <row r="337" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="337" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D337" s="29"/>
       <c r="G337" s="11"/>
       <c r="H337" s="11"/>
@@ -9186,7 +9186,7 @@
       <c r="X337" s="11"/>
       <c r="Y337" s="11"/>
     </row>
-    <row r="338" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="338" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D338" s="29"/>
       <c r="G338" s="11"/>
       <c r="H338" s="11"/>
@@ -9208,7 +9208,7 @@
       <c r="X338" s="11"/>
       <c r="Y338" s="11"/>
     </row>
-    <row r="339" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="339" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D339" s="29"/>
       <c r="G339" s="11"/>
       <c r="H339" s="11"/>
@@ -9230,7 +9230,7 @@
       <c r="X339" s="11"/>
       <c r="Y339" s="11"/>
     </row>
-    <row r="340" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="340" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D340" s="29"/>
       <c r="G340" s="11"/>
       <c r="H340" s="11"/>
@@ -9252,7 +9252,7 @@
       <c r="X340" s="11"/>
       <c r="Y340" s="11"/>
     </row>
-    <row r="341" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="341" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D341" s="29"/>
       <c r="G341" s="11"/>
       <c r="H341" s="11"/>
@@ -9274,7 +9274,7 @@
       <c r="X341" s="11"/>
       <c r="Y341" s="11"/>
     </row>
-    <row r="342" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="342" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D342" s="29"/>
       <c r="G342" s="11"/>
       <c r="H342" s="11"/>
@@ -9296,7 +9296,7 @@
       <c r="X342" s="11"/>
       <c r="Y342" s="11"/>
     </row>
-    <row r="343" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="343" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D343" s="29"/>
       <c r="G343" s="11"/>
       <c r="H343" s="11"/>
@@ -9318,7 +9318,7 @@
       <c r="X343" s="11"/>
       <c r="Y343" s="11"/>
     </row>
-    <row r="344" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="344" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D344" s="29"/>
       <c r="G344" s="11"/>
       <c r="H344" s="11"/>
@@ -9340,7 +9340,7 @@
       <c r="X344" s="11"/>
       <c r="Y344" s="11"/>
     </row>
-    <row r="345" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="345" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D345" s="29"/>
       <c r="G345" s="11"/>
       <c r="H345" s="11"/>
@@ -9362,7 +9362,7 @@
       <c r="X345" s="11"/>
       <c r="Y345" s="11"/>
     </row>
-    <row r="346" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="346" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D346" s="29"/>
       <c r="G346" s="11"/>
       <c r="H346" s="11"/>
@@ -9384,7 +9384,7 @@
       <c r="X346" s="11"/>
       <c r="Y346" s="11"/>
     </row>
-    <row r="347" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="347" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D347" s="29"/>
       <c r="G347" s="11"/>
       <c r="H347" s="11"/>
@@ -9406,7 +9406,7 @@
       <c r="X347" s="11"/>
       <c r="Y347" s="11"/>
     </row>
-    <row r="348" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="348" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D348" s="29"/>
       <c r="G348" s="11"/>
       <c r="H348" s="11"/>
@@ -9428,7 +9428,7 @@
       <c r="X348" s="11"/>
       <c r="Y348" s="11"/>
     </row>
-    <row r="349" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="349" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D349" s="29"/>
       <c r="G349" s="11"/>
       <c r="H349" s="11"/>
@@ -9450,7 +9450,7 @@
       <c r="X349" s="11"/>
       <c r="Y349" s="11"/>
     </row>
-    <row r="350" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="350" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D350" s="29"/>
       <c r="G350" s="11"/>
       <c r="H350" s="11"/>
@@ -9472,7 +9472,7 @@
       <c r="X350" s="11"/>
       <c r="Y350" s="11"/>
     </row>
-    <row r="351" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="351" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D351" s="29"/>
       <c r="G351" s="11"/>
       <c r="H351" s="11"/>
@@ -9494,7 +9494,7 @@
       <c r="X351" s="11"/>
       <c r="Y351" s="11"/>
     </row>
-    <row r="352" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="352" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D352" s="29"/>
       <c r="G352" s="11"/>
       <c r="H352" s="11"/>
@@ -9516,7 +9516,7 @@
       <c r="X352" s="11"/>
       <c r="Y352" s="11"/>
     </row>
-    <row r="353" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="353" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D353" s="29"/>
       <c r="G353" s="11"/>
       <c r="H353" s="11"/>
@@ -9538,7 +9538,7 @@
       <c r="X353" s="11"/>
       <c r="Y353" s="11"/>
     </row>
-    <row r="354" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="354" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D354" s="29"/>
       <c r="G354" s="11"/>
       <c r="H354" s="11"/>
@@ -9560,7 +9560,7 @@
       <c r="X354" s="11"/>
       <c r="Y354" s="11"/>
     </row>
-    <row r="355" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="355" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D355" s="29"/>
       <c r="G355" s="11"/>
       <c r="H355" s="11"/>
@@ -9582,7 +9582,7 @@
       <c r="X355" s="11"/>
       <c r="Y355" s="11"/>
     </row>
-    <row r="356" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="356" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D356" s="29"/>
       <c r="G356" s="11"/>
       <c r="H356" s="11"/>
@@ -9604,7 +9604,7 @@
       <c r="X356" s="11"/>
       <c r="Y356" s="11"/>
     </row>
-    <row r="357" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="357" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D357" s="29"/>
       <c r="G357" s="11"/>
       <c r="H357" s="11"/>
@@ -9626,7 +9626,7 @@
       <c r="X357" s="11"/>
       <c r="Y357" s="11"/>
     </row>
-    <row r="358" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="358" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D358" s="29"/>
       <c r="G358" s="11"/>
       <c r="H358" s="11"/>
@@ -9648,7 +9648,7 @@
       <c r="X358" s="11"/>
       <c r="Y358" s="11"/>
     </row>
-    <row r="359" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="359" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D359" s="29"/>
       <c r="G359" s="11"/>
       <c r="H359" s="11"/>
@@ -9670,7 +9670,7 @@
       <c r="X359" s="11"/>
       <c r="Y359" s="11"/>
     </row>
-    <row r="360" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="360" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D360" s="29"/>
       <c r="G360" s="11"/>
       <c r="H360" s="11"/>
@@ -9692,7 +9692,7 @@
       <c r="X360" s="11"/>
       <c r="Y360" s="11"/>
     </row>
-    <row r="361" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="361" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D361" s="29"/>
       <c r="G361" s="11"/>
       <c r="H361" s="11"/>
@@ -9714,7 +9714,7 @@
       <c r="X361" s="11"/>
       <c r="Y361" s="11"/>
     </row>
-    <row r="362" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="362" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D362" s="29"/>
       <c r="G362" s="11"/>
       <c r="H362" s="11"/>
@@ -9736,7 +9736,7 @@
       <c r="X362" s="11"/>
       <c r="Y362" s="11"/>
     </row>
-    <row r="363" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="363" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D363" s="29"/>
       <c r="G363" s="11"/>
       <c r="H363" s="11"/>
@@ -9758,7 +9758,7 @@
       <c r="X363" s="11"/>
       <c r="Y363" s="11"/>
     </row>
-    <row r="364" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="364" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D364" s="29"/>
       <c r="G364" s="11"/>
       <c r="H364" s="11"/>
@@ -9780,7 +9780,7 @@
       <c r="X364" s="11"/>
       <c r="Y364" s="11"/>
     </row>
-    <row r="365" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="365" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D365" s="29"/>
       <c r="G365" s="11"/>
       <c r="H365" s="11"/>
@@ -9802,7 +9802,7 @@
       <c r="X365" s="11"/>
       <c r="Y365" s="11"/>
     </row>
-    <row r="366" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="366" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D366" s="29"/>
       <c r="G366" s="11"/>
       <c r="H366" s="11"/>
@@ -9824,7 +9824,7 @@
       <c r="X366" s="11"/>
       <c r="Y366" s="11"/>
     </row>
-    <row r="367" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="367" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D367" s="29"/>
       <c r="G367" s="11"/>
       <c r="H367" s="11"/>
@@ -9846,7 +9846,7 @@
       <c r="X367" s="11"/>
       <c r="Y367" s="11"/>
     </row>
-    <row r="368" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="368" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D368" s="29"/>
       <c r="G368" s="11"/>
       <c r="H368" s="11"/>
@@ -9868,7 +9868,7 @@
       <c r="X368" s="11"/>
       <c r="Y368" s="11"/>
     </row>
-    <row r="369" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="369" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D369" s="29"/>
       <c r="G369" s="11"/>
       <c r="H369" s="11"/>
@@ -9890,7 +9890,7 @@
       <c r="X369" s="11"/>
       <c r="Y369" s="11"/>
     </row>
-    <row r="370" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="370" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D370" s="29"/>
       <c r="G370" s="11"/>
       <c r="H370" s="11"/>
@@ -9912,7 +9912,7 @@
       <c r="X370" s="11"/>
       <c r="Y370" s="11"/>
     </row>
-    <row r="371" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="371" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D371" s="29"/>
       <c r="G371" s="11"/>
       <c r="H371" s="11"/>
@@ -9934,7 +9934,7 @@
       <c r="X371" s="11"/>
       <c r="Y371" s="11"/>
     </row>
-    <row r="372" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="372" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D372" s="29"/>
       <c r="G372" s="11"/>
       <c r="H372" s="11"/>
@@ -9956,7 +9956,7 @@
       <c r="X372" s="11"/>
       <c r="Y372" s="11"/>
     </row>
-    <row r="373" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="373" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D373" s="29"/>
       <c r="G373" s="11"/>
       <c r="H373" s="11"/>
@@ -9978,7 +9978,7 @@
       <c r="X373" s="11"/>
       <c r="Y373" s="11"/>
     </row>
-    <row r="374" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="374" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D374" s="29"/>
       <c r="G374" s="11"/>
       <c r="H374" s="11"/>
@@ -10000,7 +10000,7 @@
       <c r="X374" s="11"/>
       <c r="Y374" s="11"/>
     </row>
-    <row r="375" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="375" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D375" s="29"/>
       <c r="G375" s="11"/>
       <c r="H375" s="11"/>
@@ -10022,7 +10022,7 @@
       <c r="X375" s="11"/>
       <c r="Y375" s="11"/>
     </row>
-    <row r="376" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="376" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D376" s="29"/>
       <c r="G376" s="11"/>
       <c r="H376" s="11"/>
@@ -10044,7 +10044,7 @@
       <c r="X376" s="11"/>
       <c r="Y376" s="11"/>
     </row>
-    <row r="377" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="377" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D377" s="29"/>
       <c r="G377" s="11"/>
       <c r="H377" s="11"/>
@@ -10066,7 +10066,7 @@
       <c r="X377" s="11"/>
       <c r="Y377" s="11"/>
     </row>
-    <row r="378" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="378" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D378" s="29"/>
       <c r="G378" s="11"/>
       <c r="H378" s="11"/>
@@ -10088,7 +10088,7 @@
       <c r="X378" s="11"/>
       <c r="Y378" s="11"/>
     </row>
-    <row r="379" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="379" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D379" s="29"/>
       <c r="G379" s="11"/>
       <c r="H379" s="11"/>
@@ -10110,7 +10110,7 @@
       <c r="X379" s="11"/>
       <c r="Y379" s="11"/>
     </row>
-    <row r="380" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="380" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D380" s="29"/>
       <c r="G380" s="11"/>
       <c r="H380" s="11"/>
@@ -10132,7 +10132,7 @@
       <c r="X380" s="11"/>
       <c r="Y380" s="11"/>
     </row>
-    <row r="381" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="381" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D381" s="29"/>
       <c r="G381" s="11"/>
       <c r="H381" s="11"/>
@@ -10154,7 +10154,7 @@
       <c r="X381" s="11"/>
       <c r="Y381" s="11"/>
     </row>
-    <row r="382" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="382" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D382" s="29"/>
       <c r="G382" s="11"/>
       <c r="H382" s="11"/>
@@ -10176,7 +10176,7 @@
       <c r="X382" s="11"/>
       <c r="Y382" s="11"/>
     </row>
-    <row r="383" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="383" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D383" s="29"/>
       <c r="G383" s="11"/>
       <c r="H383" s="11"/>
@@ -10198,7 +10198,7 @@
       <c r="X383" s="11"/>
       <c r="Y383" s="11"/>
     </row>
-    <row r="384" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="384" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D384" s="29"/>
       <c r="G384" s="11"/>
       <c r="H384" s="11"/>
@@ -10220,7 +10220,7 @@
       <c r="X384" s="11"/>
       <c r="Y384" s="11"/>
     </row>
-    <row r="385" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="385" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D385" s="29"/>
       <c r="G385" s="11"/>
       <c r="H385" s="11"/>
@@ -10242,7 +10242,7 @@
       <c r="X385" s="11"/>
       <c r="Y385" s="11"/>
     </row>
-    <row r="386" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="386" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D386" s="29"/>
       <c r="G386" s="11"/>
       <c r="H386" s="11"/>
@@ -10264,7 +10264,7 @@
       <c r="X386" s="11"/>
       <c r="Y386" s="11"/>
     </row>
-    <row r="387" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="387" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D387" s="29"/>
       <c r="G387" s="11"/>
       <c r="H387" s="11"/>
@@ -10286,7 +10286,7 @@
       <c r="X387" s="11"/>
       <c r="Y387" s="11"/>
     </row>
-    <row r="388" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="388" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D388" s="29"/>
       <c r="G388" s="11"/>
       <c r="H388" s="11"/>
@@ -10308,7 +10308,7 @@
       <c r="X388" s="11"/>
       <c r="Y388" s="11"/>
     </row>
-    <row r="389" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="389" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D389" s="29"/>
       <c r="G389" s="11"/>
       <c r="H389" s="11"/>
@@ -10330,7 +10330,7 @@
       <c r="X389" s="11"/>
       <c r="Y389" s="11"/>
     </row>
-    <row r="390" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="390" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D390" s="29"/>
       <c r="G390" s="11"/>
       <c r="H390" s="11"/>
@@ -10352,7 +10352,7 @@
       <c r="X390" s="11"/>
       <c r="Y390" s="11"/>
     </row>
-    <row r="391" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="391" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D391" s="29"/>
       <c r="G391" s="11"/>
       <c r="H391" s="11"/>
@@ -10374,7 +10374,7 @@
       <c r="X391" s="11"/>
       <c r="Y391" s="11"/>
     </row>
-    <row r="392" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="392" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D392" s="29"/>
       <c r="G392" s="11"/>
       <c r="H392" s="11"/>
@@ -10396,7 +10396,7 @@
       <c r="X392" s="11"/>
       <c r="Y392" s="11"/>
     </row>
-    <row r="393" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="393" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D393" s="29"/>
       <c r="G393" s="11"/>
       <c r="H393" s="11"/>
@@ -10418,7 +10418,7 @@
       <c r="X393" s="11"/>
       <c r="Y393" s="11"/>
     </row>
-    <row r="394" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="394" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D394" s="29"/>
       <c r="G394" s="11"/>
       <c r="H394" s="11"/>
@@ -10440,7 +10440,7 @@
       <c r="X394" s="11"/>
       <c r="Y394" s="11"/>
     </row>
-    <row r="395" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="395" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D395" s="29"/>
       <c r="G395" s="11"/>
       <c r="H395" s="11"/>
@@ -10462,7 +10462,7 @@
       <c r="X395" s="11"/>
       <c r="Y395" s="11"/>
     </row>
-    <row r="396" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="396" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D396" s="29"/>
       <c r="G396" s="11"/>
       <c r="H396" s="11"/>
@@ -10484,7 +10484,7 @@
       <c r="X396" s="11"/>
       <c r="Y396" s="11"/>
     </row>
-    <row r="397" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="397" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D397" s="29"/>
       <c r="G397" s="11"/>
       <c r="H397" s="11"/>
@@ -10506,7 +10506,7 @@
       <c r="X397" s="11"/>
       <c r="Y397" s="11"/>
     </row>
-    <row r="398" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="398" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D398" s="29"/>
       <c r="G398" s="11"/>
       <c r="H398" s="11"/>
@@ -10528,7 +10528,7 @@
       <c r="X398" s="11"/>
       <c r="Y398" s="11"/>
     </row>
-    <row r="399" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="399" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D399" s="29"/>
       <c r="G399" s="11"/>
       <c r="H399" s="11"/>
@@ -10550,7 +10550,7 @@
       <c r="X399" s="11"/>
       <c r="Y399" s="11"/>
     </row>
-    <row r="400" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="400" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D400" s="29"/>
       <c r="G400" s="11"/>
       <c r="H400" s="11"/>
@@ -10572,7 +10572,7 @@
       <c r="X400" s="11"/>
       <c r="Y400" s="11"/>
     </row>
-    <row r="401" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="401" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D401" s="29"/>
       <c r="G401" s="11"/>
       <c r="H401" s="11"/>
@@ -10594,7 +10594,7 @@
       <c r="X401" s="11"/>
       <c r="Y401" s="11"/>
     </row>
-    <row r="402" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="402" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D402" s="29"/>
       <c r="G402" s="11"/>
       <c r="H402" s="11"/>
@@ -10616,7 +10616,7 @@
       <c r="X402" s="11"/>
       <c r="Y402" s="11"/>
     </row>
-    <row r="403" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="403" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D403" s="29"/>
       <c r="G403" s="11"/>
       <c r="H403" s="11"/>
@@ -10638,7 +10638,7 @@
       <c r="X403" s="11"/>
       <c r="Y403" s="11"/>
     </row>
-    <row r="404" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="404" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D404" s="29"/>
       <c r="G404" s="11"/>
       <c r="H404" s="11"/>
@@ -10660,7 +10660,7 @@
       <c r="X404" s="11"/>
       <c r="Y404" s="11"/>
     </row>
-    <row r="405" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="405" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D405" s="29"/>
       <c r="G405" s="11"/>
       <c r="H405" s="11"/>
@@ -10682,7 +10682,7 @@
       <c r="X405" s="11"/>
       <c r="Y405" s="11"/>
     </row>
-    <row r="406" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="406" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D406" s="29"/>
       <c r="G406" s="11"/>
       <c r="H406" s="11"/>
@@ -10704,7 +10704,7 @@
       <c r="X406" s="11"/>
       <c r="Y406" s="11"/>
     </row>
-    <row r="407" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="407" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D407" s="29"/>
       <c r="G407" s="11"/>
       <c r="H407" s="11"/>
@@ -10726,7 +10726,7 @@
       <c r="X407" s="11"/>
       <c r="Y407" s="11"/>
     </row>
-    <row r="408" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="408" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D408" s="29"/>
       <c r="G408" s="11"/>
       <c r="H408" s="11"/>
@@ -10748,7 +10748,7 @@
       <c r="X408" s="11"/>
       <c r="Y408" s="11"/>
     </row>
-    <row r="409" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="409" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D409" s="29"/>
       <c r="G409" s="11"/>
       <c r="H409" s="11"/>
@@ -10770,7 +10770,7 @@
       <c r="X409" s="11"/>
       <c r="Y409" s="11"/>
     </row>
-    <row r="410" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="410" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D410" s="29"/>
       <c r="G410" s="11"/>
       <c r="H410" s="11"/>
@@ -10792,7 +10792,7 @@
       <c r="X410" s="11"/>
       <c r="Y410" s="11"/>
     </row>
-    <row r="411" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="411" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D411" s="29"/>
       <c r="G411" s="11"/>
       <c r="H411" s="11"/>
@@ -10814,7 +10814,7 @@
       <c r="X411" s="11"/>
       <c r="Y411" s="11"/>
     </row>
-    <row r="412" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="412" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D412" s="29"/>
       <c r="G412" s="11"/>
       <c r="H412" s="11"/>
@@ -10836,7 +10836,7 @@
       <c r="X412" s="11"/>
       <c r="Y412" s="11"/>
     </row>
-    <row r="413" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="413" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D413" s="29"/>
       <c r="G413" s="11"/>
       <c r="H413" s="11"/>
@@ -10858,7 +10858,7 @@
       <c r="X413" s="11"/>
       <c r="Y413" s="11"/>
     </row>
-    <row r="414" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="414" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D414" s="29"/>
       <c r="G414" s="11"/>
       <c r="H414" s="11"/>
@@ -10880,7 +10880,7 @@
       <c r="X414" s="11"/>
       <c r="Y414" s="11"/>
     </row>
-    <row r="415" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="415" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D415" s="29"/>
       <c r="G415" s="11"/>
       <c r="H415" s="11"/>
@@ -10902,7 +10902,7 @@
       <c r="X415" s="11"/>
       <c r="Y415" s="11"/>
     </row>
-    <row r="416" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="416" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D416" s="29"/>
       <c r="G416" s="11"/>
       <c r="H416" s="11"/>
@@ -10924,7 +10924,7 @@
       <c r="X416" s="11"/>
       <c r="Y416" s="11"/>
     </row>
-    <row r="417" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="417" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D417" s="29"/>
       <c r="G417" s="11"/>
       <c r="H417" s="11"/>
@@ -10946,7 +10946,7 @@
       <c r="X417" s="11"/>
       <c r="Y417" s="11"/>
     </row>
-    <row r="418" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="418" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D418" s="29"/>
       <c r="G418" s="11"/>
       <c r="H418" s="11"/>
@@ -10968,7 +10968,7 @@
       <c r="X418" s="11"/>
       <c r="Y418" s="11"/>
     </row>
-    <row r="419" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="419" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D419" s="29"/>
       <c r="G419" s="11"/>
       <c r="H419" s="11"/>
@@ -10990,7 +10990,7 @@
       <c r="X419" s="11"/>
       <c r="Y419" s="11"/>
     </row>
-    <row r="420" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="420" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D420" s="29"/>
       <c r="G420" s="11"/>
       <c r="H420" s="11"/>
@@ -11012,7 +11012,7 @@
       <c r="X420" s="11"/>
       <c r="Y420" s="11"/>
     </row>
-    <row r="421" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="421" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D421" s="29"/>
       <c r="G421" s="11"/>
       <c r="H421" s="11"/>
@@ -11034,7 +11034,7 @@
       <c r="X421" s="11"/>
       <c r="Y421" s="11"/>
     </row>
-    <row r="422" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="422" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D422" s="29"/>
       <c r="G422" s="11"/>
       <c r="H422" s="11"/>
@@ -11056,7 +11056,7 @@
       <c r="X422" s="11"/>
       <c r="Y422" s="11"/>
     </row>
-    <row r="423" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="423" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D423" s="29"/>
       <c r="G423" s="11"/>
       <c r="H423" s="11"/>
@@ -11078,7 +11078,7 @@
       <c r="X423" s="11"/>
       <c r="Y423" s="11"/>
     </row>
-    <row r="424" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="424" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D424" s="29"/>
       <c r="G424" s="11"/>
       <c r="H424" s="11"/>
@@ -11100,7 +11100,7 @@
       <c r="X424" s="11"/>
       <c r="Y424" s="11"/>
     </row>
-    <row r="425" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="425" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D425" s="29"/>
       <c r="G425" s="11"/>
       <c r="H425" s="11"/>
@@ -11122,7 +11122,7 @@
       <c r="X425" s="11"/>
       <c r="Y425" s="11"/>
     </row>
-    <row r="426" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="426" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D426" s="29"/>
       <c r="G426" s="11"/>
       <c r="H426" s="11"/>
@@ -11144,7 +11144,7 @@
       <c r="X426" s="11"/>
       <c r="Y426" s="11"/>
     </row>
-    <row r="427" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="427" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D427" s="29"/>
       <c r="G427" s="11"/>
       <c r="H427" s="11"/>
@@ -11166,7 +11166,7 @@
       <c r="X427" s="11"/>
       <c r="Y427" s="11"/>
     </row>
-    <row r="428" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="428" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D428" s="29"/>
       <c r="G428" s="11"/>
       <c r="H428" s="11"/>
@@ -11188,7 +11188,7 @@
       <c r="X428" s="11"/>
       <c r="Y428" s="11"/>
     </row>
-    <row r="429" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="429" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D429" s="29"/>
       <c r="G429" s="11"/>
       <c r="H429" s="11"/>
@@ -11210,7 +11210,7 @@
       <c r="X429" s="11"/>
       <c r="Y429" s="11"/>
     </row>
-    <row r="430" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="430" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D430" s="29"/>
       <c r="G430" s="11"/>
       <c r="H430" s="11"/>
@@ -11232,7 +11232,7 @@
       <c r="X430" s="11"/>
       <c r="Y430" s="11"/>
     </row>
-    <row r="431" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="431" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D431" s="29"/>
       <c r="G431" s="11"/>
       <c r="H431" s="11"/>
@@ -11254,7 +11254,7 @@
       <c r="X431" s="11"/>
       <c r="Y431" s="11"/>
     </row>
-    <row r="432" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="432" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D432" s="29"/>
       <c r="G432" s="11"/>
       <c r="H432" s="11"/>
@@ -11276,7 +11276,7 @@
       <c r="X432" s="11"/>
       <c r="Y432" s="11"/>
     </row>
-    <row r="433" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="433" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D433" s="29"/>
       <c r="G433" s="11"/>
       <c r="H433" s="11"/>
@@ -11298,7 +11298,7 @@
       <c r="X433" s="11"/>
       <c r="Y433" s="11"/>
     </row>
-    <row r="434" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="434" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D434" s="29"/>
       <c r="G434" s="11"/>
       <c r="H434" s="11"/>
@@ -11320,7 +11320,7 @@
       <c r="X434" s="11"/>
       <c r="Y434" s="11"/>
     </row>
-    <row r="435" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="435" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D435" s="29"/>
       <c r="G435" s="11"/>
       <c r="H435" s="11"/>
@@ -11342,7 +11342,7 @@
       <c r="X435" s="11"/>
       <c r="Y435" s="11"/>
     </row>
-    <row r="436" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="436" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D436" s="29"/>
       <c r="G436" s="11"/>
       <c r="H436" s="11"/>
@@ -11364,7 +11364,7 @@
       <c r="X436" s="11"/>
       <c r="Y436" s="11"/>
     </row>
-    <row r="437" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="437" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D437" s="29"/>
       <c r="G437" s="11"/>
       <c r="H437" s="11"/>
@@ -11386,7 +11386,7 @@
       <c r="X437" s="11"/>
       <c r="Y437" s="11"/>
     </row>
-    <row r="438" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="438" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D438" s="29"/>
       <c r="G438" s="11"/>
       <c r="H438" s="11"/>
@@ -11408,7 +11408,7 @@
       <c r="X438" s="11"/>
       <c r="Y438" s="11"/>
     </row>
-    <row r="439" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="439" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D439" s="29"/>
       <c r="G439" s="11"/>
       <c r="H439" s="11"/>
@@ -11430,7 +11430,7 @@
       <c r="X439" s="11"/>
       <c r="Y439" s="11"/>
     </row>
-    <row r="440" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="440" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D440" s="29"/>
       <c r="G440" s="11"/>
       <c r="H440" s="11"/>
@@ -11452,7 +11452,7 @@
       <c r="X440" s="11"/>
       <c r="Y440" s="11"/>
     </row>
-    <row r="441" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="441" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D441" s="29"/>
       <c r="G441" s="11"/>
       <c r="H441" s="11"/>
@@ -11474,7 +11474,7 @@
       <c r="X441" s="11"/>
       <c r="Y441" s="11"/>
     </row>
-    <row r="442" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="442" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D442" s="29"/>
       <c r="G442" s="11"/>
       <c r="H442" s="11"/>
@@ -11496,7 +11496,7 @@
       <c r="X442" s="11"/>
       <c r="Y442" s="11"/>
     </row>
-    <row r="443" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="443" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D443" s="29"/>
       <c r="G443" s="11"/>
       <c r="H443" s="11"/>
@@ -11518,7 +11518,7 @@
       <c r="X443" s="11"/>
       <c r="Y443" s="11"/>
     </row>
-    <row r="444" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="444" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D444" s="29"/>
       <c r="G444" s="11"/>
       <c r="H444" s="11"/>
@@ -11540,7 +11540,7 @@
       <c r="X444" s="11"/>
       <c r="Y444" s="11"/>
     </row>
-    <row r="445" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="445" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D445" s="29"/>
       <c r="G445" s="11"/>
       <c r="H445" s="11"/>
@@ -11562,7 +11562,7 @@
       <c r="X445" s="11"/>
       <c r="Y445" s="11"/>
     </row>
-    <row r="446" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="446" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D446" s="29"/>
       <c r="G446" s="11"/>
       <c r="H446" s="11"/>
@@ -11584,7 +11584,7 @@
       <c r="X446" s="11"/>
       <c r="Y446" s="11"/>
     </row>
-    <row r="447" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="447" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D447" s="29"/>
       <c r="G447" s="11"/>
       <c r="H447" s="11"/>
@@ -11606,7 +11606,7 @@
       <c r="X447" s="11"/>
       <c r="Y447" s="11"/>
     </row>
-    <row r="448" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="448" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D448" s="29"/>
       <c r="G448" s="11"/>
       <c r="H448" s="11"/>
@@ -11628,7 +11628,7 @@
       <c r="X448" s="11"/>
       <c r="Y448" s="11"/>
     </row>
-    <row r="449" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="449" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D449" s="29"/>
       <c r="G449" s="11"/>
       <c r="H449" s="11"/>
@@ -11650,7 +11650,7 @@
       <c r="X449" s="11"/>
       <c r="Y449" s="11"/>
     </row>
-    <row r="450" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="450" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D450" s="29"/>
       <c r="G450" s="11"/>
       <c r="H450" s="11"/>
@@ -11672,7 +11672,7 @@
       <c r="X450" s="11"/>
       <c r="Y450" s="11"/>
     </row>
-    <row r="451" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="451" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D451" s="29"/>
       <c r="G451" s="11"/>
       <c r="H451" s="11"/>
@@ -11694,7 +11694,7 @@
       <c r="X451" s="11"/>
       <c r="Y451" s="11"/>
     </row>
-    <row r="452" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="452" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D452" s="29"/>
       <c r="G452" s="11"/>
       <c r="H452" s="11"/>
@@ -11716,7 +11716,7 @@
       <c r="X452" s="11"/>
       <c r="Y452" s="11"/>
     </row>
-    <row r="453" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="453" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D453" s="29"/>
       <c r="G453" s="11"/>
       <c r="H453" s="11"/>
@@ -11738,7 +11738,7 @@
       <c r="X453" s="11"/>
       <c r="Y453" s="11"/>
     </row>
-    <row r="454" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="454" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D454" s="29"/>
       <c r="G454" s="11"/>
       <c r="H454" s="11"/>
@@ -11760,7 +11760,7 @@
       <c r="X454" s="11"/>
       <c r="Y454" s="11"/>
     </row>
-    <row r="455" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="455" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D455" s="29"/>
       <c r="G455" s="11"/>
       <c r="H455" s="11"/>
@@ -11782,7 +11782,7 @@
       <c r="X455" s="11"/>
       <c r="Y455" s="11"/>
     </row>
-    <row r="456" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="456" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D456" s="29"/>
       <c r="G456" s="11"/>
       <c r="H456" s="11"/>
@@ -11804,7 +11804,7 @@
       <c r="X456" s="11"/>
       <c r="Y456" s="11"/>
     </row>
-    <row r="457" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="457" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D457" s="29"/>
       <c r="G457" s="11"/>
       <c r="H457" s="11"/>
@@ -11826,7 +11826,7 @@
       <c r="X457" s="11"/>
       <c r="Y457" s="11"/>
     </row>
-    <row r="458" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="458" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D458" s="29"/>
       <c r="G458" s="11"/>
       <c r="H458" s="11"/>
@@ -11848,7 +11848,7 @@
       <c r="X458" s="11"/>
       <c r="Y458" s="11"/>
     </row>
-    <row r="459" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="459" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D459" s="29"/>
       <c r="G459" s="11"/>
       <c r="H459" s="11"/>
@@ -11870,7 +11870,7 @@
       <c r="X459" s="11"/>
       <c r="Y459" s="11"/>
     </row>
-    <row r="460" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="460" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D460" s="29"/>
       <c r="G460" s="11"/>
       <c r="H460" s="11"/>
@@ -11892,7 +11892,7 @@
       <c r="X460" s="11"/>
       <c r="Y460" s="11"/>
     </row>
-    <row r="461" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="461" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D461" s="29"/>
       <c r="G461" s="11"/>
       <c r="H461" s="11"/>
@@ -11914,7 +11914,7 @@
       <c r="X461" s="11"/>
       <c r="Y461" s="11"/>
     </row>
-    <row r="462" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="462" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D462" s="29"/>
       <c r="G462" s="11"/>
       <c r="H462" s="11"/>
@@ -11936,7 +11936,7 @@
       <c r="X462" s="11"/>
       <c r="Y462" s="11"/>
     </row>
-    <row r="463" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="463" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D463" s="29"/>
       <c r="G463" s="11"/>
       <c r="H463" s="11"/>
@@ -11958,7 +11958,7 @@
       <c r="X463" s="11"/>
       <c r="Y463" s="11"/>
     </row>
-    <row r="464" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="464" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D464" s="29"/>
       <c r="G464" s="11"/>
       <c r="H464" s="11"/>
@@ -11980,7 +11980,7 @@
       <c r="X464" s="11"/>
       <c r="Y464" s="11"/>
     </row>
-    <row r="465" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="465" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D465" s="29"/>
       <c r="G465" s="11"/>
       <c r="H465" s="11"/>
@@ -12002,7 +12002,7 @@
       <c r="X465" s="11"/>
       <c r="Y465" s="11"/>
     </row>
-    <row r="466" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="466" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D466" s="29"/>
       <c r="G466" s="11"/>
       <c r="H466" s="11"/>
@@ -12024,7 +12024,7 @@
       <c r="X466" s="11"/>
       <c r="Y466" s="11"/>
     </row>
-    <row r="467" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="467" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D467" s="29"/>
       <c r="G467" s="11"/>
       <c r="H467" s="11"/>
@@ -12046,7 +12046,7 @@
       <c r="X467" s="11"/>
       <c r="Y467" s="11"/>
     </row>
-    <row r="468" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="468" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D468" s="29"/>
       <c r="G468" s="11"/>
       <c r="H468" s="11"/>
@@ -12068,7 +12068,7 @@
       <c r="X468" s="11"/>
       <c r="Y468" s="11"/>
     </row>
-    <row r="469" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="469" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D469" s="29"/>
       <c r="G469" s="11"/>
       <c r="H469" s="11"/>
@@ -12090,7 +12090,7 @@
       <c r="X469" s="11"/>
       <c r="Y469" s="11"/>
     </row>
-    <row r="470" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="470" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D470" s="29"/>
       <c r="G470" s="11"/>
       <c r="H470" s="11"/>
@@ -12112,7 +12112,7 @@
       <c r="X470" s="11"/>
       <c r="Y470" s="11"/>
     </row>
-    <row r="471" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="471" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D471" s="29"/>
       <c r="G471" s="11"/>
       <c r="H471" s="11"/>
@@ -12134,7 +12134,7 @@
       <c r="X471" s="11"/>
       <c r="Y471" s="11"/>
     </row>
-    <row r="472" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="472" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D472" s="29"/>
       <c r="G472" s="11"/>
       <c r="H472" s="11"/>
@@ -12156,7 +12156,7 @@
       <c r="X472" s="11"/>
       <c r="Y472" s="11"/>
     </row>
-    <row r="473" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="473" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D473" s="29"/>
       <c r="G473" s="11"/>
       <c r="H473" s="11"/>
@@ -12178,7 +12178,7 @@
       <c r="X473" s="11"/>
       <c r="Y473" s="11"/>
     </row>
-    <row r="474" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="474" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D474" s="29"/>
       <c r="G474" s="11"/>
       <c r="H474" s="11"/>
@@ -12200,7 +12200,7 @@
       <c r="X474" s="11"/>
       <c r="Y474" s="11"/>
     </row>
-    <row r="475" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="475" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D475" s="29"/>
       <c r="G475" s="11"/>
       <c r="H475" s="11"/>
@@ -12222,7 +12222,7 @@
       <c r="X475" s="11"/>
       <c r="Y475" s="11"/>
     </row>
-    <row r="476" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="476" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D476" s="29"/>
       <c r="G476" s="11"/>
       <c r="H476" s="11"/>
@@ -12244,7 +12244,7 @@
       <c r="X476" s="11"/>
       <c r="Y476" s="11"/>
     </row>
-    <row r="477" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="477" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D477" s="29"/>
       <c r="G477" s="11"/>
       <c r="H477" s="11"/>
@@ -12266,7 +12266,7 @@
       <c r="X477" s="11"/>
       <c r="Y477" s="11"/>
     </row>
-    <row r="478" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="478" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D478" s="29"/>
       <c r="G478" s="11"/>
       <c r="H478" s="11"/>
@@ -12288,7 +12288,7 @@
       <c r="X478" s="11"/>
       <c r="Y478" s="11"/>
     </row>
-    <row r="479" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="479" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D479" s="29"/>
       <c r="G479" s="11"/>
       <c r="H479" s="11"/>
@@ -12310,7 +12310,7 @@
       <c r="X479" s="11"/>
       <c r="Y479" s="11"/>
     </row>
-    <row r="480" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="480" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D480" s="29"/>
       <c r="G480" s="11"/>
       <c r="H480" s="11"/>
@@ -12332,7 +12332,7 @@
       <c r="X480" s="11"/>
       <c r="Y480" s="11"/>
     </row>
-    <row r="481" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="481" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D481" s="29"/>
       <c r="G481" s="11"/>
       <c r="H481" s="11"/>
@@ -12354,7 +12354,7 @@
       <c r="X481" s="11"/>
       <c r="Y481" s="11"/>
     </row>
-    <row r="482" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="482" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D482" s="29"/>
       <c r="G482" s="11"/>
       <c r="H482" s="11"/>
@@ -12376,7 +12376,7 @@
       <c r="X482" s="11"/>
       <c r="Y482" s="11"/>
     </row>
-    <row r="483" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="483" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D483" s="29"/>
       <c r="G483" s="11"/>
       <c r="H483" s="11"/>
@@ -12398,7 +12398,7 @@
       <c r="X483" s="11"/>
       <c r="Y483" s="11"/>
     </row>
-    <row r="484" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="484" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D484" s="29"/>
       <c r="G484" s="11"/>
       <c r="H484" s="11"/>
@@ -12420,7 +12420,7 @@
       <c r="X484" s="11"/>
       <c r="Y484" s="11"/>
     </row>
-    <row r="485" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="485" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D485" s="29"/>
       <c r="G485" s="11"/>
       <c r="H485" s="11"/>
@@ -12442,7 +12442,7 @@
       <c r="X485" s="11"/>
       <c r="Y485" s="11"/>
     </row>
-    <row r="486" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="486" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D486" s="29"/>
       <c r="G486" s="11"/>
       <c r="H486" s="11"/>
@@ -12464,7 +12464,7 @@
       <c r="X486" s="11"/>
       <c r="Y486" s="11"/>
     </row>
-    <row r="487" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="487" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D487" s="29"/>
       <c r="G487" s="11"/>
       <c r="H487" s="11"/>
@@ -12486,7 +12486,7 @@
       <c r="X487" s="11"/>
       <c r="Y487" s="11"/>
     </row>
-    <row r="488" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="488" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D488" s="29"/>
       <c r="G488" s="11"/>
       <c r="H488" s="11"/>
@@ -12508,7 +12508,7 @@
       <c r="X488" s="11"/>
       <c r="Y488" s="11"/>
     </row>
-    <row r="489" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="489" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D489" s="29"/>
       <c r="G489" s="11"/>
       <c r="H489" s="11"/>
@@ -12530,7 +12530,7 @@
       <c r="X489" s="11"/>
       <c r="Y489" s="11"/>
     </row>
-    <row r="490" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="490" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D490" s="29"/>
       <c r="G490" s="11"/>
       <c r="H490" s="11"/>
@@ -12552,7 +12552,7 @@
       <c r="X490" s="11"/>
       <c r="Y490" s="11"/>
     </row>
-    <row r="491" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="491" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D491" s="29"/>
       <c r="G491" s="11"/>
       <c r="H491" s="11"/>
@@ -12574,7 +12574,7 @@
       <c r="X491" s="11"/>
       <c r="Y491" s="11"/>
     </row>
-    <row r="492" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="492" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D492" s="29"/>
       <c r="G492" s="11"/>
       <c r="H492" s="11"/>
@@ -12596,7 +12596,7 @@
       <c r="X492" s="11"/>
       <c r="Y492" s="11"/>
     </row>
-    <row r="493" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="493" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D493" s="29"/>
       <c r="G493" s="11"/>
       <c r="H493" s="11"/>
@@ -12618,7 +12618,7 @@
       <c r="X493" s="11"/>
       <c r="Y493" s="11"/>
     </row>
-    <row r="494" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="494" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D494" s="29"/>
       <c r="G494" s="11"/>
       <c r="H494" s="11"/>
@@ -12640,7 +12640,7 @@
       <c r="X494" s="11"/>
       <c r="Y494" s="11"/>
     </row>
-    <row r="495" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="495" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D495" s="29"/>
       <c r="G495" s="11"/>
       <c r="H495" s="11"/>
@@ -12662,7 +12662,7 @@
       <c r="X495" s="11"/>
       <c r="Y495" s="11"/>
     </row>
-    <row r="496" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="496" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D496" s="29"/>
       <c r="G496" s="11"/>
       <c r="H496" s="11"/>
@@ -12684,7 +12684,7 @@
       <c r="X496" s="11"/>
       <c r="Y496" s="11"/>
     </row>
-    <row r="497" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="497" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D497" s="29"/>
       <c r="G497" s="11"/>
       <c r="H497" s="11"/>
@@ -12706,7 +12706,7 @@
       <c r="X497" s="11"/>
       <c r="Y497" s="11"/>
     </row>
-    <row r="498" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="498" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D498" s="29"/>
       <c r="G498" s="11"/>
       <c r="H498" s="11"/>
@@ -12728,7 +12728,7 @@
       <c r="X498" s="11"/>
       <c r="Y498" s="11"/>
     </row>
-    <row r="499" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="499" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D499" s="29"/>
       <c r="G499" s="11"/>
       <c r="H499" s="11"/>
@@ -12750,7 +12750,7 @@
       <c r="X499" s="11"/>
       <c r="Y499" s="11"/>
     </row>
-    <row r="500" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="500" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D500" s="29"/>
       <c r="G500" s="11"/>
       <c r="H500" s="11"/>
@@ -12772,7 +12772,7 @@
       <c r="X500" s="11"/>
       <c r="Y500" s="11"/>
     </row>
-    <row r="501" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="501" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D501" s="29"/>
       <c r="G501" s="11"/>
       <c r="H501" s="11"/>
@@ -12794,7 +12794,7 @@
       <c r="X501" s="11"/>
       <c r="Y501" s="11"/>
     </row>
-    <row r="502" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="502" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D502" s="29"/>
       <c r="G502" s="11"/>
       <c r="H502" s="11"/>
@@ -12816,7 +12816,7 @@
       <c r="X502" s="11"/>
       <c r="Y502" s="11"/>
     </row>
-    <row r="503" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="503" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D503" s="29"/>
       <c r="G503" s="11"/>
       <c r="H503" s="11"/>
@@ -12838,7 +12838,7 @@
       <c r="X503" s="11"/>
       <c r="Y503" s="11"/>
     </row>
-    <row r="504" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="504" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D504" s="29"/>
       <c r="G504" s="11"/>
       <c r="H504" s="11"/>
@@ -12860,7 +12860,7 @@
       <c r="X504" s="11"/>
       <c r="Y504" s="11"/>
     </row>
-    <row r="505" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="505" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D505" s="29"/>
       <c r="G505" s="11"/>
       <c r="H505" s="11"/>
@@ -12882,7 +12882,7 @@
       <c r="X505" s="11"/>
       <c r="Y505" s="11"/>
     </row>
-    <row r="506" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="506" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D506" s="29"/>
       <c r="G506" s="11"/>
       <c r="H506" s="11"/>
@@ -12904,7 +12904,7 @@
       <c r="X506" s="11"/>
       <c r="Y506" s="11"/>
     </row>
-    <row r="507" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="507" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D507" s="29"/>
       <c r="G507" s="11"/>
       <c r="H507" s="11"/>
@@ -12926,7 +12926,7 @@
       <c r="X507" s="11"/>
       <c r="Y507" s="11"/>
     </row>
-    <row r="508" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="508" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D508" s="29"/>
       <c r="G508" s="11"/>
       <c r="H508" s="11"/>
@@ -12948,7 +12948,7 @@
       <c r="X508" s="11"/>
       <c r="Y508" s="11"/>
     </row>
-    <row r="509" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="509" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D509" s="29"/>
       <c r="G509" s="11"/>
       <c r="H509" s="11"/>
@@ -12970,7 +12970,7 @@
       <c r="X509" s="11"/>
       <c r="Y509" s="11"/>
     </row>
-    <row r="510" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="510" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D510" s="29"/>
       <c r="G510" s="11"/>
       <c r="H510" s="11"/>
@@ -12992,7 +12992,7 @@
       <c r="X510" s="11"/>
       <c r="Y510" s="11"/>
     </row>
-    <row r="511" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="511" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D511" s="29"/>
       <c r="G511" s="11"/>
       <c r="H511" s="11"/>
@@ -13014,7 +13014,7 @@
       <c r="X511" s="11"/>
       <c r="Y511" s="11"/>
     </row>
-    <row r="512" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="512" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D512" s="29"/>
       <c r="G512" s="11"/>
       <c r="H512" s="11"/>
@@ -13036,7 +13036,7 @@
       <c r="X512" s="11"/>
       <c r="Y512" s="11"/>
     </row>
-    <row r="513" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="513" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D513" s="29"/>
       <c r="G513" s="11"/>
       <c r="H513" s="11"/>
@@ -13058,7 +13058,7 @@
       <c r="X513" s="11"/>
       <c r="Y513" s="11"/>
     </row>
-    <row r="514" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="514" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D514" s="29"/>
       <c r="G514" s="11"/>
       <c r="H514" s="11"/>
@@ -13080,7 +13080,7 @@
       <c r="X514" s="11"/>
       <c r="Y514" s="11"/>
     </row>
-    <row r="515" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="515" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D515" s="29"/>
       <c r="G515" s="11"/>
       <c r="H515" s="11"/>
@@ -13102,7 +13102,7 @@
       <c r="X515" s="11"/>
       <c r="Y515" s="11"/>
     </row>
-    <row r="516" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="516" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D516" s="29"/>
       <c r="G516" s="11"/>
       <c r="H516" s="11"/>
@@ -13124,7 +13124,7 @@
       <c r="X516" s="11"/>
       <c r="Y516" s="11"/>
     </row>
-    <row r="517" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="517" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D517" s="29"/>
       <c r="G517" s="11"/>
       <c r="H517" s="11"/>
@@ -13146,7 +13146,7 @@
       <c r="X517" s="11"/>
       <c r="Y517" s="11"/>
     </row>
-    <row r="518" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="518" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D518" s="29"/>
       <c r="G518" s="11"/>
       <c r="H518" s="11"/>
@@ -13168,7 +13168,7 @@
       <c r="X518" s="11"/>
       <c r="Y518" s="11"/>
     </row>
-    <row r="519" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="519" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D519" s="29"/>
       <c r="G519" s="11"/>
       <c r="H519" s="11"/>
@@ -13190,7 +13190,7 @@
       <c r="X519" s="11"/>
       <c r="Y519" s="11"/>
     </row>
-    <row r="520" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="520" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D520" s="29"/>
       <c r="G520" s="11"/>
       <c r="H520" s="11"/>
@@ -13212,7 +13212,7 @@
       <c r="X520" s="11"/>
       <c r="Y520" s="11"/>
     </row>
-    <row r="521" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="521" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D521" s="29"/>
       <c r="G521" s="11"/>
       <c r="H521" s="11"/>
@@ -13234,7 +13234,7 @@
       <c r="X521" s="11"/>
       <c r="Y521" s="11"/>
     </row>
-    <row r="522" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="522" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D522" s="29"/>
       <c r="G522" s="11"/>
       <c r="H522" s="11"/>
@@ -13256,7 +13256,7 @@
       <c r="X522" s="11"/>
       <c r="Y522" s="11"/>
     </row>
-    <row r="523" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="523" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D523" s="29"/>
       <c r="G523" s="11"/>
       <c r="H523" s="11"/>
@@ -13278,7 +13278,7 @@
       <c r="X523" s="11"/>
       <c r="Y523" s="11"/>
     </row>
-    <row r="524" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="524" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D524" s="29"/>
       <c r="G524" s="11"/>
       <c r="H524" s="11"/>
@@ -13300,7 +13300,7 @@
       <c r="X524" s="11"/>
       <c r="Y524" s="11"/>
     </row>
-    <row r="525" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="525" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D525" s="29"/>
       <c r="G525" s="11"/>
       <c r="H525" s="11"/>
@@ -13322,7 +13322,7 @@
       <c r="X525" s="11"/>
       <c r="Y525" s="11"/>
     </row>
-    <row r="526" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="526" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D526" s="29"/>
       <c r="G526" s="11"/>
       <c r="H526" s="11"/>
@@ -13344,7 +13344,7 @@
       <c r="X526" s="11"/>
       <c r="Y526" s="11"/>
     </row>
-    <row r="527" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="527" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D527" s="29"/>
       <c r="G527" s="11"/>
       <c r="H527" s="11"/>
@@ -13366,7 +13366,7 @@
       <c r="X527" s="11"/>
       <c r="Y527" s="11"/>
     </row>
-    <row r="528" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="528" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D528" s="29"/>
       <c r="G528" s="11"/>
       <c r="H528" s="11"/>
@@ -13388,7 +13388,7 @@
       <c r="X528" s="11"/>
       <c r="Y528" s="11"/>
     </row>
-    <row r="529" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="529" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D529" s="29"/>
       <c r="G529" s="11"/>
       <c r="H529" s="11"/>
@@ -13410,7 +13410,7 @@
       <c r="X529" s="11"/>
       <c r="Y529" s="11"/>
     </row>
-    <row r="530" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="530" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D530" s="29"/>
       <c r="G530" s="11"/>
       <c r="H530" s="11"/>
@@ -13432,7 +13432,7 @@
       <c r="X530" s="11"/>
       <c r="Y530" s="11"/>
     </row>
-    <row r="531" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="531" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D531" s="29"/>
       <c r="G531" s="11"/>
       <c r="H531" s="11"/>
@@ -13454,7 +13454,7 @@
       <c r="X531" s="11"/>
       <c r="Y531" s="11"/>
     </row>
-    <row r="532" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="532" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D532" s="29"/>
       <c r="G532" s="11"/>
       <c r="H532" s="11"/>
@@ -13476,7 +13476,7 @@
       <c r="X532" s="11"/>
       <c r="Y532" s="11"/>
     </row>
-    <row r="533" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="533" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D533" s="29"/>
       <c r="G533" s="11"/>
       <c r="H533" s="11"/>
@@ -13498,7 +13498,7 @@
       <c r="X533" s="11"/>
       <c r="Y533" s="11"/>
     </row>
-    <row r="534" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="534" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D534" s="29"/>
       <c r="G534" s="11"/>
       <c r="H534" s="11"/>
@@ -13520,7 +13520,7 @@
       <c r="X534" s="11"/>
       <c r="Y534" s="11"/>
     </row>
-    <row r="535" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="535" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D535" s="29"/>
       <c r="G535" s="11"/>
       <c r="H535" s="11"/>
@@ -13542,7 +13542,7 @@
       <c r="X535" s="11"/>
       <c r="Y535" s="11"/>
     </row>
-    <row r="536" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="536" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D536" s="29"/>
       <c r="G536" s="11"/>
       <c r="H536" s="11"/>
@@ -13564,7 +13564,7 @@
       <c r="X536" s="11"/>
       <c r="Y536" s="11"/>
     </row>
-    <row r="537" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="537" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D537" s="29"/>
       <c r="G537" s="11"/>
       <c r="H537" s="11"/>
@@ -13586,7 +13586,7 @@
       <c r="X537" s="11"/>
       <c r="Y537" s="11"/>
     </row>
-    <row r="538" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="538" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D538" s="29"/>
       <c r="G538" s="11"/>
       <c r="H538" s="11"/>
@@ -13608,7 +13608,7 @@
       <c r="X538" s="11"/>
       <c r="Y538" s="11"/>
     </row>
-    <row r="539" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="539" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D539" s="29"/>
       <c r="G539" s="11"/>
       <c r="H539" s="11"/>
@@ -13630,7 +13630,7 @@
       <c r="X539" s="11"/>
       <c r="Y539" s="11"/>
     </row>
-    <row r="540" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="540" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D540" s="29"/>
       <c r="G540" s="11"/>
       <c r="H540" s="11"/>
@@ -13652,7 +13652,7 @@
       <c r="X540" s="11"/>
       <c r="Y540" s="11"/>
     </row>
-    <row r="541" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="541" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D541" s="29"/>
       <c r="G541" s="11"/>
       <c r="H541" s="11"/>
@@ -13674,7 +13674,7 @@
       <c r="X541" s="11"/>
       <c r="Y541" s="11"/>
     </row>
-    <row r="542" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="542" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D542" s="29"/>
       <c r="G542" s="11"/>
       <c r="H542" s="11"/>
@@ -13696,7 +13696,7 @@
       <c r="X542" s="11"/>
       <c r="Y542" s="11"/>
     </row>
-    <row r="543" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="543" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D543" s="29"/>
       <c r="G543" s="11"/>
       <c r="H543" s="11"/>
@@ -13718,7 +13718,7 @@
       <c r="X543" s="11"/>
       <c r="Y543" s="11"/>
     </row>
-    <row r="544" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="544" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D544" s="29"/>
       <c r="G544" s="11"/>
       <c r="H544" s="11"/>
@@ -13740,7 +13740,7 @@
       <c r="X544" s="11"/>
       <c r="Y544" s="11"/>
     </row>
-    <row r="545" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="545" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D545" s="29"/>
       <c r="G545" s="11"/>
       <c r="H545" s="11"/>
@@ -13762,7 +13762,7 @@
       <c r="X545" s="11"/>
       <c r="Y545" s="11"/>
     </row>
-    <row r="546" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="546" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D546" s="29"/>
       <c r="G546" s="11"/>
       <c r="H546" s="11"/>
@@ -13784,7 +13784,7 @@
       <c r="X546" s="11"/>
       <c r="Y546" s="11"/>
     </row>
-    <row r="547" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="547" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D547" s="29"/>
       <c r="G547" s="11"/>
       <c r="H547" s="11"/>
@@ -13806,7 +13806,7 @@
       <c r="X547" s="11"/>
       <c r="Y547" s="11"/>
     </row>
-    <row r="548" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="548" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D548" s="29"/>
       <c r="G548" s="11"/>
       <c r="H548" s="11"/>
@@ -13828,7 +13828,7 @@
       <c r="X548" s="11"/>
       <c r="Y548" s="11"/>
     </row>
-    <row r="549" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="549" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D549" s="29"/>
       <c r="G549" s="11"/>
       <c r="H549" s="11"/>
@@ -13850,7 +13850,7 @@
       <c r="X549" s="11"/>
       <c r="Y549" s="11"/>
     </row>
-    <row r="550" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="550" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D550" s="29"/>
       <c r="G550" s="11"/>
       <c r="H550" s="11"/>
@@ -13872,7 +13872,7 @@
       <c r="X550" s="11"/>
       <c r="Y550" s="11"/>
     </row>
-    <row r="551" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="551" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D551" s="29"/>
       <c r="G551" s="11"/>
       <c r="H551" s="11"/>
@@ -13894,7 +13894,7 @@
       <c r="X551" s="11"/>
       <c r="Y551" s="11"/>
     </row>
-    <row r="552" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="552" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D552" s="29"/>
       <c r="G552" s="11"/>
       <c r="H552" s="11"/>
@@ -13916,7 +13916,7 @@
       <c r="X552" s="11"/>
       <c r="Y552" s="11"/>
     </row>
-    <row r="553" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="553" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D553" s="29"/>
       <c r="G553" s="11"/>
       <c r="H553" s="11"/>
@@ -13938,7 +13938,7 @@
       <c r="X553" s="11"/>
       <c r="Y553" s="11"/>
     </row>
-    <row r="554" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="554" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D554" s="29"/>
       <c r="G554" s="11"/>
       <c r="H554" s="11"/>
@@ -13960,7 +13960,7 @@
       <c r="X554" s="11"/>
       <c r="Y554" s="11"/>
     </row>
-    <row r="555" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="555" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D555" s="29"/>
       <c r="G555" s="11"/>
       <c r="H555" s="11"/>
@@ -13982,7 +13982,7 @@
       <c r="X555" s="11"/>
       <c r="Y555" s="11"/>
     </row>
-    <row r="556" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="556" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D556" s="29"/>
       <c r="G556" s="11"/>
       <c r="H556" s="11"/>
@@ -14004,7 +14004,7 @@
       <c r="X556" s="11"/>
       <c r="Y556" s="11"/>
     </row>
-    <row r="557" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="557" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D557" s="29"/>
       <c r="G557" s="11"/>
       <c r="H557" s="11"/>
@@ -14026,7 +14026,7 @@
       <c r="X557" s="11"/>
       <c r="Y557" s="11"/>
     </row>
-    <row r="558" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="558" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D558" s="29"/>
       <c r="G558" s="11"/>
       <c r="H558" s="11"/>
@@ -14048,7 +14048,7 @@
       <c r="X558" s="11"/>
       <c r="Y558" s="11"/>
     </row>
-    <row r="559" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="559" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D559" s="29"/>
       <c r="G559" s="11"/>
       <c r="H559" s="11"/>
@@ -14070,7 +14070,7 @@
       <c r="X559" s="11"/>
       <c r="Y559" s="11"/>
     </row>
-    <row r="560" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="560" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D560" s="29"/>
       <c r="G560" s="11"/>
       <c r="H560" s="11"/>
@@ -14092,7 +14092,7 @@
       <c r="X560" s="11"/>
       <c r="Y560" s="11"/>
     </row>
-    <row r="561" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="561" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D561" s="29"/>
       <c r="G561" s="11"/>
       <c r="H561" s="11"/>
@@ -14114,7 +14114,7 @@
       <c r="X561" s="11"/>
       <c r="Y561" s="11"/>
     </row>
-    <row r="562" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="562" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D562" s="29"/>
       <c r="G562" s="11"/>
       <c r="H562" s="11"/>
@@ -14136,7 +14136,7 @@
       <c r="X562" s="11"/>
       <c r="Y562" s="11"/>
     </row>
-    <row r="563" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="563" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D563" s="29"/>
       <c r="G563" s="11"/>
       <c r="H563" s="11"/>
@@ -14158,7 +14158,7 @@
       <c r="X563" s="11"/>
       <c r="Y563" s="11"/>
     </row>
-    <row r="564" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="564" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D564" s="29"/>
       <c r="G564" s="11"/>
       <c r="H564" s="11"/>
@@ -14180,7 +14180,7 @@
       <c r="X564" s="11"/>
       <c r="Y564" s="11"/>
     </row>
-    <row r="565" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="565" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D565" s="29"/>
       <c r="G565" s="11"/>
       <c r="H565" s="11"/>
@@ -14202,7 +14202,7 @@
       <c r="X565" s="11"/>
       <c r="Y565" s="11"/>
     </row>
-    <row r="566" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="566" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D566" s="29"/>
       <c r="G566" s="11"/>
       <c r="H566" s="11"/>
@@ -14224,7 +14224,7 @@
       <c r="X566" s="11"/>
       <c r="Y566" s="11"/>
     </row>
-    <row r="567" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="567" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D567" s="29"/>
       <c r="G567" s="11"/>
       <c r="H567" s="11"/>
@@ -14246,7 +14246,7 @@
       <c r="X567" s="11"/>
       <c r="Y567" s="11"/>
     </row>
-    <row r="568" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="568" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D568" s="29"/>
       <c r="G568" s="11"/>
       <c r="H568" s="11"/>
@@ -14268,7 +14268,7 @@
       <c r="X568" s="11"/>
       <c r="Y568" s="11"/>
     </row>
-    <row r="569" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="569" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D569" s="29"/>
       <c r="G569" s="11"/>
       <c r="H569" s="11"/>
@@ -14290,7 +14290,7 @@
       <c r="X569" s="11"/>
       <c r="Y569" s="11"/>
     </row>
-    <row r="570" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="570" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D570" s="29"/>
       <c r="G570" s="11"/>
       <c r="H570" s="11"/>
@@ -14312,7 +14312,7 @@
       <c r="X570" s="11"/>
       <c r="Y570" s="11"/>
     </row>
-    <row r="571" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="571" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D571" s="29"/>
       <c r="G571" s="11"/>
       <c r="H571" s="11"/>
@@ -14334,7 +14334,7 @@
       <c r="X571" s="11"/>
       <c r="Y571" s="11"/>
     </row>
-    <row r="572" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="572" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D572" s="29"/>
       <c r="G572" s="11"/>
       <c r="H572" s="11"/>
@@ -14356,7 +14356,7 @@
       <c r="X572" s="11"/>
       <c r="Y572" s="11"/>
     </row>
-    <row r="573" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="573" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D573" s="29"/>
       <c r="G573" s="11"/>
       <c r="H573" s="11"/>
@@ -14378,7 +14378,7 @@
       <c r="X573" s="11"/>
       <c r="Y573" s="11"/>
     </row>
-    <row r="574" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="574" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D574" s="29"/>
       <c r="G574" s="11"/>
       <c r="H574" s="11"/>
@@ -14400,7 +14400,7 @@
       <c r="X574" s="11"/>
       <c r="Y574" s="11"/>
     </row>
-    <row r="575" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="575" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D575" s="29"/>
       <c r="G575" s="11"/>
       <c r="H575" s="11"/>
@@ -14422,7 +14422,7 @@
       <c r="X575" s="11"/>
       <c r="Y575" s="11"/>
     </row>
-    <row r="576" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="576" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D576" s="29"/>
       <c r="G576" s="11"/>
       <c r="H576" s="11"/>
@@ -14444,7 +14444,7 @@
       <c r="X576" s="11"/>
       <c r="Y576" s="11"/>
     </row>
-    <row r="577" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="577" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D577" s="29"/>
       <c r="G577" s="11"/>
       <c r="H577" s="11"/>
@@ -14466,7 +14466,7 @@
       <c r="X577" s="11"/>
       <c r="Y577" s="11"/>
     </row>
-    <row r="578" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="578" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D578" s="29"/>
       <c r="G578" s="11"/>
       <c r="H578" s="11"/>
@@ -14488,7 +14488,7 @@
       <c r="X578" s="11"/>
       <c r="Y578" s="11"/>
     </row>
-    <row r="579" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="579" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D579" s="29"/>
       <c r="G579" s="11"/>
       <c r="H579" s="11"/>
@@ -14510,7 +14510,7 @@
       <c r="X579" s="11"/>
       <c r="Y579" s="11"/>
     </row>
-    <row r="580" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="580" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D580" s="29"/>
       <c r="G580" s="11"/>
       <c r="H580" s="11"/>
@@ -14532,7 +14532,7 @@
       <c r="X580" s="11"/>
       <c r="Y580" s="11"/>
     </row>
-    <row r="581" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="581" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D581" s="29"/>
       <c r="G581" s="11"/>
       <c r="H581" s="11"/>
@@ -14554,7 +14554,7 @@
       <c r="X581" s="11"/>
       <c r="Y581" s="11"/>
     </row>
-    <row r="582" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="582" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D582" s="29"/>
       <c r="G582" s="11"/>
       <c r="H582" s="11"/>
@@ -14576,7 +14576,7 @@
       <c r="X582" s="11"/>
       <c r="Y582" s="11"/>
     </row>
-    <row r="583" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="583" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D583" s="29"/>
       <c r="G583" s="11"/>
       <c r="H583" s="11"/>
@@ -14598,7 +14598,7 @@
       <c r="X583" s="11"/>
       <c r="Y583" s="11"/>
     </row>
-    <row r="584" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="584" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D584" s="29"/>
       <c r="G584" s="11"/>
       <c r="H584" s="11"/>
@@ -14620,7 +14620,7 @@
       <c r="X584" s="11"/>
       <c r="Y584" s="11"/>
     </row>
-    <row r="585" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="585" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D585" s="29"/>
       <c r="G585" s="11"/>
       <c r="H585" s="11"/>
@@ -14642,7 +14642,7 @@
       <c r="X585" s="11"/>
       <c r="Y585" s="11"/>
     </row>
-    <row r="586" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="586" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D586" s="29"/>
       <c r="G586" s="11"/>
       <c r="H586" s="11"/>
@@ -14664,7 +14664,7 @@
       <c r="X586" s="11"/>
       <c r="Y586" s="11"/>
     </row>
-    <row r="587" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="587" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D587" s="29"/>
       <c r="G587" s="11"/>
       <c r="H587" s="11"/>
@@ -14686,7 +14686,7 @@
       <c r="X587" s="11"/>
       <c r="Y587" s="11"/>
     </row>
-    <row r="588" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="588" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D588" s="29"/>
       <c r="G588" s="11"/>
       <c r="H588" s="11"/>
@@ -14708,7 +14708,7 @@
       <c r="X588" s="11"/>
       <c r="Y588" s="11"/>
     </row>
-    <row r="589" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="589" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D589" s="29"/>
       <c r="G589" s="11"/>
       <c r="H589" s="11"/>
@@ -14730,7 +14730,7 @@
       <c r="X589" s="11"/>
       <c r="Y589" s="11"/>
     </row>
-    <row r="590" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="590" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D590" s="29"/>
       <c r="G590" s="11"/>
       <c r="H590" s="11"/>
@@ -14752,7 +14752,7 @@
       <c r="X590" s="11"/>
       <c r="Y590" s="11"/>
     </row>
-    <row r="591" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="591" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D591" s="29"/>
       <c r="G591" s="11"/>
       <c r="H591" s="11"/>
@@ -14774,7 +14774,7 @@
       <c r="X591" s="11"/>
       <c r="Y591" s="11"/>
     </row>
-    <row r="592" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="592" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D592" s="29"/>
       <c r="G592" s="11"/>
       <c r="H592" s="11"/>
@@ -14796,7 +14796,7 @@
       <c r="X592" s="11"/>
       <c r="Y592" s="11"/>
     </row>
-    <row r="593" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="593" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D593" s="29"/>
       <c r="G593" s="11"/>
       <c r="H593" s="11"/>
@@ -14818,7 +14818,7 @@
       <c r="X593" s="11"/>
       <c r="Y593" s="11"/>
     </row>
-    <row r="594" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="594" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D594" s="29"/>
       <c r="G594" s="11"/>
       <c r="H594" s="11"/>
@@ -14840,7 +14840,7 @@
       <c r="X594" s="11"/>
       <c r="Y594" s="11"/>
     </row>
-    <row r="595" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="595" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D595" s="29"/>
       <c r="G595" s="11"/>
       <c r="H595" s="11"/>
@@ -14862,7 +14862,7 @@
       <c r="X595" s="11"/>
       <c r="Y595" s="11"/>
     </row>
-    <row r="596" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="596" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D596" s="29"/>
       <c r="G596" s="11"/>
       <c r="H596" s="11"/>
@@ -14884,7 +14884,7 @@
       <c r="X596" s="11"/>
       <c r="Y596" s="11"/>
     </row>
-    <row r="597" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="597" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D597" s="29"/>
       <c r="G597" s="11"/>
       <c r="H597" s="11"/>
@@ -14906,7 +14906,7 @@
       <c r="X597" s="11"/>
       <c r="Y597" s="11"/>
     </row>
-    <row r="598" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="598" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D598" s="29"/>
       <c r="G598" s="11"/>
       <c r="H598" s="11"/>
@@ -14928,7 +14928,7 @@
       <c r="X598" s="11"/>
       <c r="Y598" s="11"/>
     </row>
-    <row r="599" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="599" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D599" s="29"/>
       <c r="G599" s="11"/>
       <c r="H599" s="11"/>
@@ -14950,7 +14950,7 @@
       <c r="X599" s="11"/>
       <c r="Y599" s="11"/>
     </row>
-    <row r="600" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="600" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D600" s="29"/>
       <c r="G600" s="11"/>
       <c r="H600" s="11"/>
@@ -14972,7 +14972,7 @@
       <c r="X600" s="11"/>
       <c r="Y600" s="11"/>
     </row>
-    <row r="601" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="601" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D601" s="29"/>
       <c r="G601" s="11"/>
       <c r="H601" s="11"/>
@@ -14994,7 +14994,7 @@
       <c r="X601" s="11"/>
       <c r="Y601" s="11"/>
     </row>
-    <row r="602" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="602" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D602" s="29"/>
       <c r="G602" s="11"/>
       <c r="H602" s="11"/>
@@ -15016,7 +15016,7 @@
       <c r="X602" s="11"/>
       <c r="Y602" s="11"/>
     </row>
-    <row r="603" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="603" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D603" s="29"/>
       <c r="G603" s="11"/>
       <c r="H603" s="11"/>
@@ -15038,7 +15038,7 @@
       <c r="X603" s="11"/>
       <c r="Y603" s="11"/>
     </row>
-    <row r="604" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="604" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D604" s="29"/>
       <c r="G604" s="11"/>
       <c r="H604" s="11"/>
@@ -15060,7 +15060,7 @@
       <c r="X604" s="11"/>
       <c r="Y604" s="11"/>
     </row>
-    <row r="605" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="605" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D605" s="29"/>
       <c r="G605" s="11"/>
       <c r="H605" s="11"/>
@@ -15082,7 +15082,7 @@
       <c r="X605" s="11"/>
       <c r="Y605" s="11"/>
     </row>
-    <row r="606" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="606" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D606" s="29"/>
       <c r="G606" s="11"/>
       <c r="H606" s="11"/>
@@ -15104,7 +15104,7 @@
       <c r="X606" s="11"/>
       <c r="Y606" s="11"/>
     </row>
-    <row r="607" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="607" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D607" s="29"/>
       <c r="G607" s="11"/>
       <c r="H607" s="11"/>
@@ -15126,7 +15126,7 @@
       <c r="X607" s="11"/>
       <c r="Y607" s="11"/>
     </row>
-    <row r="608" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="608" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D608" s="29"/>
       <c r="G608" s="11"/>
       <c r="H608" s="11"/>
@@ -15148,7 +15148,7 @@
       <c r="X608" s="11"/>
       <c r="Y608" s="11"/>
     </row>
-    <row r="609" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="609" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D609" s="29"/>
       <c r="G609" s="11"/>
       <c r="H609" s="11"/>
@@ -15170,7 +15170,7 @@
       <c r="X609" s="11"/>
       <c r="Y609" s="11"/>
     </row>
-    <row r="610" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="610" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D610" s="29"/>
       <c r="G610" s="11"/>
       <c r="H610" s="11"/>
@@ -15192,7 +15192,7 @@
       <c r="X610" s="11"/>
       <c r="Y610" s="11"/>
     </row>
-    <row r="611" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="611" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D611" s="29"/>
       <c r="G611" s="11"/>
       <c r="H611" s="11"/>
@@ -15214,7 +15214,7 @@
       <c r="X611" s="11"/>
       <c r="Y611" s="11"/>
     </row>
-    <row r="612" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="612" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D612" s="29"/>
       <c r="G612" s="11"/>
       <c r="H612" s="11"/>
@@ -15236,7 +15236,7 @@
       <c r="X612" s="11"/>
       <c r="Y612" s="11"/>
     </row>
-    <row r="613" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="613" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D613" s="29"/>
       <c r="G613" s="11"/>
       <c r="H613" s="11"/>
@@ -15258,7 +15258,7 @@
       <c r="X613" s="11"/>
       <c r="Y613" s="11"/>
     </row>
-    <row r="614" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="614" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D614" s="29"/>
       <c r="G614" s="11"/>
       <c r="H614" s="11"/>
@@ -15280,7 +15280,7 @@
       <c r="X614" s="11"/>
       <c r="Y614" s="11"/>
     </row>
-    <row r="615" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="615" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D615" s="29"/>
       <c r="G615" s="11"/>
       <c r="H615" s="11"/>
@@ -15302,7 +15302,7 @@
       <c r="X615" s="11"/>
       <c r="Y615" s="11"/>
     </row>
-    <row r="616" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="616" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D616" s="29"/>
       <c r="G616" s="11"/>
       <c r="H616" s="11"/>
@@ -15324,7 +15324,7 @@
       <c r="X616" s="11"/>
       <c r="Y616" s="11"/>
     </row>
-    <row r="617" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="617" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D617" s="29"/>
       <c r="G617" s="11"/>
       <c r="H617" s="11"/>
@@ -15346,7 +15346,7 @@
       <c r="X617" s="11"/>
       <c r="Y617" s="11"/>
     </row>
-    <row r="618" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="618" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D618" s="29"/>
       <c r="G618" s="11"/>
       <c r="H618" s="11"/>
@@ -15368,7 +15368,7 @@
       <c r="X618" s="11"/>
       <c r="Y618" s="11"/>
     </row>
-    <row r="619" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="619" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D619" s="29"/>
       <c r="G619" s="11"/>
       <c r="H619" s="11"/>
@@ -15390,7 +15390,7 @@
       <c r="X619" s="11"/>
       <c r="Y619" s="11"/>
     </row>
-    <row r="620" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="620" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D620" s="29"/>
       <c r="G620" s="11"/>
       <c r="H620" s="11"/>
@@ -15412,7 +15412,7 @@
       <c r="X620" s="11"/>
       <c r="Y620" s="11"/>
     </row>
-    <row r="621" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="621" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D621" s="29"/>
       <c r="G621" s="11"/>
       <c r="H621" s="11"/>
@@ -15434,7 +15434,7 @@
       <c r="X621" s="11"/>
       <c r="Y621" s="11"/>
     </row>
-    <row r="622" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="622" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D622" s="29"/>
       <c r="G622" s="11"/>
       <c r="H622" s="11"/>
@@ -15456,7 +15456,7 @@
       <c r="X622" s="11"/>
       <c r="Y622" s="11"/>
     </row>
-    <row r="623" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="623" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D623" s="29"/>
       <c r="G623" s="11"/>
       <c r="H623" s="11"/>
@@ -15478,7 +15478,7 @@
       <c r="X623" s="11"/>
       <c r="Y623" s="11"/>
     </row>
-    <row r="624" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="624" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D624" s="29"/>
       <c r="G624" s="11"/>
       <c r="H624" s="11"/>
@@ -15500,7 +15500,7 @@
       <c r="X624" s="11"/>
       <c r="Y624" s="11"/>
     </row>
-    <row r="625" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="625" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D625" s="29"/>
       <c r="G625" s="11"/>
       <c r="H625" s="11"/>
@@ -15522,7 +15522,7 @@
       <c r="X625" s="11"/>
       <c r="Y625" s="11"/>
     </row>
-    <row r="626" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="626" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D626" s="29"/>
       <c r="G626" s="11"/>
       <c r="H626" s="11"/>
@@ -15544,7 +15544,7 @@
       <c r="X626" s="11"/>
       <c r="Y626" s="11"/>
     </row>
-    <row r="627" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="627" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D627" s="29"/>
       <c r="G627" s="11"/>
       <c r="H627" s="11"/>
@@ -15566,7 +15566,7 @@
       <c r="X627" s="11"/>
       <c r="Y627" s="11"/>
     </row>
-    <row r="628" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="628" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D628" s="29"/>
       <c r="G628" s="11"/>
       <c r="H628" s="11"/>
@@ -15588,7 +15588,7 @@
       <c r="X628" s="11"/>
       <c r="Y628" s="11"/>
     </row>
-    <row r="629" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="629" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D629" s="29"/>
       <c r="G629" s="11"/>
       <c r="H629" s="11"/>
@@ -15610,7 +15610,7 @@
       <c r="X629" s="11"/>
       <c r="Y629" s="11"/>
     </row>
-    <row r="630" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="630" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D630" s="29"/>
       <c r="G630" s="11"/>
       <c r="H630" s="11"/>
@@ -15632,7 +15632,7 @@
       <c r="X630" s="11"/>
       <c r="Y630" s="11"/>
     </row>
-    <row r="631" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="631" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D631" s="29"/>
       <c r="G631" s="11"/>
       <c r="H631" s="11"/>
@@ -15654,7 +15654,7 @@
       <c r="X631" s="11"/>
       <c r="Y631" s="11"/>
     </row>
-    <row r="632" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="632" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D632" s="29"/>
       <c r="G632" s="11"/>
       <c r="H632" s="11"/>
@@ -15676,7 +15676,7 @@
       <c r="X632" s="11"/>
       <c r="Y632" s="11"/>
     </row>
-    <row r="633" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="633" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D633" s="29"/>
       <c r="G633" s="11"/>
       <c r="H633" s="11"/>
@@ -15698,7 +15698,7 @@
       <c r="X633" s="11"/>
       <c r="Y633" s="11"/>
     </row>
-    <row r="634" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="634" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D634" s="29"/>
       <c r="G634" s="11"/>
       <c r="H634" s="11"/>
@@ -15720,7 +15720,7 @@
       <c r="X634" s="11"/>
       <c r="Y634" s="11"/>
     </row>
-    <row r="635" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="635" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D635" s="29"/>
       <c r="G635" s="11"/>
       <c r="H635" s="11"/>
@@ -15742,7 +15742,7 @@
       <c r="X635" s="11"/>
       <c r="Y635" s="11"/>
     </row>
-    <row r="636" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="636" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D636" s="29"/>
       <c r="G636" s="11"/>
       <c r="H636" s="11"/>
@@ -15764,7 +15764,7 @@
       <c r="X636" s="11"/>
       <c r="Y636" s="11"/>
     </row>
-    <row r="637" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="637" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D637" s="29"/>
       <c r="G637" s="11"/>
       <c r="H637" s="11"/>
@@ -15786,7 +15786,7 @@
       <c r="X637" s="11"/>
       <c r="Y637" s="11"/>
     </row>
-    <row r="638" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="638" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D638" s="29"/>
       <c r="G638" s="11"/>
       <c r="H638" s="11"/>
@@ -15808,7 +15808,7 @@
       <c r="X638" s="11"/>
       <c r="Y638" s="11"/>
     </row>
-    <row r="639" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="639" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D639" s="29"/>
       <c r="G639" s="11"/>
       <c r="H639" s="11"/>
@@ -15830,7 +15830,7 @@
       <c r="X639" s="11"/>
       <c r="Y639" s="11"/>
     </row>
-    <row r="640" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="640" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D640" s="29"/>
       <c r="G640" s="11"/>
       <c r="H640" s="11"/>
@@ -15852,7 +15852,7 @@
       <c r="X640" s="11"/>
       <c r="Y640" s="11"/>
     </row>
-    <row r="641" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="641" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D641" s="29"/>
       <c r="G641" s="11"/>
       <c r="H641" s="11"/>
@@ -15874,7 +15874,7 @@
       <c r="X641" s="11"/>
       <c r="Y641" s="11"/>
     </row>
-    <row r="642" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="642" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D642" s="29"/>
       <c r="G642" s="11"/>
       <c r="H642" s="11"/>
@@ -15896,7 +15896,7 @@
       <c r="X642" s="11"/>
       <c r="Y642" s="11"/>
     </row>
-    <row r="643" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="643" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D643" s="29"/>
       <c r="G643" s="11"/>
       <c r="H643" s="11"/>
@@ -15918,7 +15918,7 @@
       <c r="X643" s="11"/>
       <c r="Y643" s="11"/>
     </row>
-    <row r="644" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="644" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D644" s="29"/>
       <c r="G644" s="11"/>
       <c r="H644" s="11"/>
@@ -15940,7 +15940,7 @@
       <c r="X644" s="11"/>
       <c r="Y644" s="11"/>
     </row>
-    <row r="645" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="645" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D645" s="29"/>
       <c r="G645" s="11"/>
       <c r="H645" s="11"/>
@@ -15962,7 +15962,7 @@
       <c r="X645" s="11"/>
       <c r="Y645" s="11"/>
     </row>
-    <row r="646" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="646" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D646" s="29"/>
       <c r="G646" s="11"/>
       <c r="H646" s="11"/>
@@ -15984,7 +15984,7 @@
       <c r="X646" s="11"/>
       <c r="Y646" s="11"/>
     </row>
-    <row r="647" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="647" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D647" s="29"/>
       <c r="G647" s="11"/>
       <c r="H647" s="11"/>
@@ -16006,7 +16006,7 @@
       <c r="X647" s="11"/>
       <c r="Y647" s="11"/>
     </row>
-    <row r="648" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="648" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D648" s="29"/>
       <c r="G648" s="11"/>
       <c r="H648" s="11"/>
@@ -16028,7 +16028,7 @@
       <c r="X648" s="11"/>
       <c r="Y648" s="11"/>
     </row>
-    <row r="649" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="649" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D649" s="29"/>
       <c r="G649" s="11"/>
       <c r="H649" s="11"/>
@@ -16050,7 +16050,7 @@
       <c r="X649" s="11"/>
       <c r="Y649" s="11"/>
     </row>
-    <row r="650" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="650" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D650" s="29"/>
       <c r="G650" s="11"/>
       <c r="H650" s="11"/>
@@ -16072,7 +16072,7 @@
       <c r="X650" s="11"/>
       <c r="Y650" s="11"/>
     </row>
-    <row r="651" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="651" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D651" s="29"/>
       <c r="G651" s="11"/>
       <c r="H651" s="11"/>
@@ -16094,7 +16094,7 @@
       <c r="X651" s="11"/>
       <c r="Y651" s="11"/>
     </row>
-    <row r="652" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="652" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D652" s="29"/>
       <c r="G652" s="11"/>
       <c r="H652" s="11"/>
@@ -16116,7 +16116,7 @@
       <c r="X652" s="11"/>
       <c r="Y652" s="11"/>
     </row>
-    <row r="653" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="653" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D653" s="29"/>
       <c r="G653" s="11"/>
       <c r="H653" s="11"/>
@@ -16138,7 +16138,7 @@
       <c r="X653" s="11"/>
       <c r="Y653" s="11"/>
     </row>
-    <row r="654" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="654" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D654" s="29"/>
       <c r="G654" s="11"/>
       <c r="H654" s="11"/>
@@ -16160,7 +16160,7 @@
       <c r="X654" s="11"/>
       <c r="Y654" s="11"/>
     </row>
-    <row r="655" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="655" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D655" s="29"/>
       <c r="G655" s="11"/>
       <c r="H655" s="11"/>
@@ -16182,7 +16182,7 @@
       <c r="X655" s="11"/>
       <c r="Y655" s="11"/>
     </row>
-    <row r="656" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="656" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D656" s="29"/>
       <c r="G656" s="11"/>
       <c r="H656" s="11"/>
@@ -16204,7 +16204,7 @@
       <c r="X656" s="11"/>
       <c r="Y656" s="11"/>
     </row>
-    <row r="657" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="657" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D657" s="29"/>
       <c r="G657" s="11"/>
       <c r="H657" s="11"/>
@@ -16226,7 +16226,7 @@
       <c r="X657" s="11"/>
       <c r="Y657" s="11"/>
     </row>
-    <row r="658" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="658" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D658" s="29"/>
       <c r="G658" s="11"/>
       <c r="H658" s="11"/>
@@ -16248,7 +16248,7 @@
       <c r="X658" s="11"/>
       <c r="Y658" s="11"/>
     </row>
-    <row r="659" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="659" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D659" s="29"/>
       <c r="G659" s="11"/>
       <c r="H659" s="11"/>
@@ -16270,7 +16270,7 @@
       <c r="X659" s="11"/>
       <c r="Y659" s="11"/>
     </row>
-    <row r="660" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="660" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D660" s="29"/>
       <c r="G660" s="11"/>
       <c r="H660" s="11"/>
@@ -16292,7 +16292,7 @@
       <c r="X660" s="11"/>
       <c r="Y660" s="11"/>
     </row>
-    <row r="661" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="661" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D661" s="29"/>
       <c r="G661" s="11"/>
       <c r="H661" s="11"/>
@@ -16314,7 +16314,7 @@
       <c r="X661" s="11"/>
       <c r="Y661" s="11"/>
     </row>
-    <row r="662" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="662" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D662" s="29"/>
       <c r="G662" s="11"/>
       <c r="H662" s="11"/>
@@ -16336,7 +16336,7 @@
       <c r="X662" s="11"/>
       <c r="Y662" s="11"/>
     </row>
-    <row r="663" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="663" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D663" s="29"/>
       <c r="G663" s="11"/>
       <c r="H663" s="11"/>
@@ -16358,7 +16358,7 @@
       <c r="X663" s="11"/>
       <c r="Y663" s="11"/>
     </row>
-    <row r="664" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="664" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D664" s="29"/>
       <c r="G664" s="11"/>
       <c r="H664" s="11"/>
@@ -16380,7 +16380,7 @@
       <c r="X664" s="11"/>
       <c r="Y664" s="11"/>
     </row>
-    <row r="665" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="665" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D665" s="29"/>
       <c r="G665" s="11"/>
       <c r="H665" s="11"/>
@@ -16402,7 +16402,7 @@
       <c r="X665" s="11"/>
       <c r="Y665" s="11"/>
     </row>
-    <row r="666" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="666" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D666" s="29"/>
       <c r="G666" s="11"/>
       <c r="H666" s="11"/>
@@ -16424,7 +16424,7 @@
       <c r="X666" s="11"/>
       <c r="Y666" s="11"/>
     </row>
-    <row r="667" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="667" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D667" s="29"/>
       <c r="G667" s="11"/>
       <c r="H667" s="11"/>
@@ -16446,7 +16446,7 @@
       <c r="X667" s="11"/>
       <c r="Y667" s="11"/>
     </row>
-    <row r="668" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="668" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D668" s="29"/>
       <c r="G668" s="11"/>
       <c r="H668" s="11"/>
@@ -16468,7 +16468,7 @@
       <c r="X668" s="11"/>
       <c r="Y668" s="11"/>
     </row>
-    <row r="669" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="669" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D669" s="29"/>
       <c r="G669" s="11"/>
       <c r="H669" s="11"/>
@@ -16490,7 +16490,7 @@
       <c r="X669" s="11"/>
       <c r="Y669" s="11"/>
     </row>
-    <row r="670" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="670" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D670" s="29"/>
       <c r="G670" s="11"/>
       <c r="H670" s="11"/>
@@ -16512,7 +16512,7 @@
       <c r="X670" s="11"/>
       <c r="Y670" s="11"/>
     </row>
-    <row r="671" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="671" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D671" s="29"/>
       <c r="G671" s="11"/>
       <c r="H671" s="11"/>
@@ -16534,7 +16534,7 @@
       <c r="X671" s="11"/>
       <c r="Y671" s="11"/>
     </row>
-    <row r="672" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="672" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D672" s="29"/>
       <c r="G672" s="11"/>
       <c r="H672" s="11"/>
@@ -16556,7 +16556,7 @@
       <c r="X672" s="11"/>
       <c r="Y672" s="11"/>
     </row>
-    <row r="673" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="673" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D673" s="29"/>
       <c r="G673" s="11"/>
       <c r="H673" s="11"/>
@@ -16578,7 +16578,7 @@
       <c r="X673" s="11"/>
       <c r="Y673" s="11"/>
     </row>
-    <row r="674" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="674" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D674" s="29"/>
       <c r="G674" s="11"/>
       <c r="H674" s="11"/>
@@ -16600,7 +16600,7 @@
       <c r="X674" s="11"/>
       <c r="Y674" s="11"/>
     </row>
-    <row r="675" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="675" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D675" s="29"/>
       <c r="G675" s="11"/>
       <c r="H675" s="11"/>
@@ -16622,7 +16622,7 @@
       <c r="X675" s="11"/>
       <c r="Y675" s="11"/>
     </row>
-    <row r="676" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="676" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D676" s="29"/>
       <c r="G676" s="11"/>
       <c r="H676" s="11"/>
@@ -16644,7 +16644,7 @@
       <c r="X676" s="11"/>
       <c r="Y676" s="11"/>
     </row>
-    <row r="677" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="677" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D677" s="29"/>
       <c r="G677" s="11"/>
       <c r="H677" s="11"/>
@@ -16666,7 +16666,7 @@
       <c r="X677" s="11"/>
       <c r="Y677" s="11"/>
     </row>
-    <row r="678" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="678" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D678" s="29"/>
       <c r="G678" s="11"/>
       <c r="H678" s="11"/>
@@ -16688,7 +16688,7 @@
       <c r="X678" s="11"/>
       <c r="Y678" s="11"/>
     </row>
-    <row r="679" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="679" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D679" s="29"/>
       <c r="G679" s="11"/>
       <c r="H679" s="11"/>
@@ -16710,7 +16710,7 @@
       <c r="X679" s="11"/>
       <c r="Y679" s="11"/>
     </row>
-    <row r="680" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="680" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D680" s="29"/>
       <c r="G680" s="11"/>
       <c r="H680" s="11"/>
@@ -16732,7 +16732,7 @@
       <c r="X680" s="11"/>
       <c r="Y680" s="11"/>
     </row>
-    <row r="681" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="681" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D681" s="29"/>
       <c r="G681" s="11"/>
       <c r="H681" s="11"/>
@@ -16754,7 +16754,7 @@
       <c r="X681" s="11"/>
       <c r="Y681" s="11"/>
     </row>
-    <row r="682" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="682" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D682" s="29"/>
       <c r="G682" s="11"/>
       <c r="H682" s="11"/>
@@ -16776,7 +16776,7 @@
       <c r="X682" s="11"/>
       <c r="Y682" s="11"/>
     </row>
-    <row r="683" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="683" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D683" s="29"/>
       <c r="G683" s="11"/>
       <c r="H683" s="11"/>
@@ -16798,7 +16798,7 @@
       <c r="X683" s="11"/>
       <c r="Y683" s="11"/>
     </row>
-    <row r="684" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="684" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D684" s="29"/>
       <c r="G684" s="11"/>
       <c r="H684" s="11"/>
@@ -16820,7 +16820,7 @@
       <c r="X684" s="11"/>
       <c r="Y684" s="11"/>
     </row>
-    <row r="685" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="685" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D685" s="29"/>
       <c r="G685" s="11"/>
       <c r="H685" s="11"/>
@@ -16842,7 +16842,7 @@
       <c r="X685" s="11"/>
       <c r="Y685" s="11"/>
     </row>
-    <row r="686" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="686" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D686" s="29"/>
       <c r="G686" s="11"/>
       <c r="H686" s="11"/>
@@ -16864,7 +16864,7 @@
       <c r="X686" s="11"/>
       <c r="Y686" s="11"/>
     </row>
-    <row r="687" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="687" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D687" s="29"/>
       <c r="G687" s="11"/>
       <c r="H687" s="11"/>
@@ -16886,7 +16886,7 @@
       <c r="X687" s="11"/>
       <c r="Y687" s="11"/>
     </row>
-    <row r="688" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="688" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D688" s="29"/>
       <c r="G688" s="11"/>
       <c r="H688" s="11"/>
@@ -16908,7 +16908,7 @@
       <c r="X688" s="11"/>
       <c r="Y688" s="11"/>
     </row>
-    <row r="689" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="689" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D689" s="29"/>
       <c r="G689" s="11"/>
       <c r="H689" s="11"/>
@@ -16930,7 +16930,7 @@
       <c r="X689" s="11"/>
       <c r="Y689" s="11"/>
     </row>
-    <row r="690" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="690" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D690" s="29"/>
       <c r="G690" s="11"/>
       <c r="H690" s="11"/>
@@ -16952,7 +16952,7 @@
       <c r="X690" s="11"/>
       <c r="Y690" s="11"/>
     </row>
-    <row r="691" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="691" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D691" s="29"/>
       <c r="G691" s="11"/>
       <c r="H691" s="11"/>
@@ -16974,7 +16974,7 @@
       <c r="X691" s="11"/>
       <c r="Y691" s="11"/>
     </row>
-    <row r="692" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="692" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D692" s="29"/>
       <c r="G692" s="11"/>
       <c r="H692" s="11"/>
@@ -16996,7 +16996,7 @@
       <c r="X692" s="11"/>
       <c r="Y692" s="11"/>
     </row>
-    <row r="693" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="693" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D693" s="29"/>
       <c r="G693" s="11"/>
       <c r="H693" s="11"/>
@@ -17018,7 +17018,7 @@
       <c r="X693" s="11"/>
       <c r="Y693" s="11"/>
     </row>
-    <row r="694" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="694" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D694" s="29"/>
       <c r="G694" s="11"/>
       <c r="H694" s="11"/>
@@ -17040,7 +17040,7 @@
       <c r="X694" s="11"/>
       <c r="Y694" s="11"/>
     </row>
-    <row r="695" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="695" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D695" s="29"/>
       <c r="G695" s="11"/>
       <c r="H695" s="11"/>
@@ -17062,7 +17062,7 @@
       <c r="X695" s="11"/>
       <c r="Y695" s="11"/>
     </row>
-    <row r="696" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="696" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D696" s="29"/>
       <c r="G696" s="11"/>
       <c r="H696" s="11"/>
@@ -17084,7 +17084,7 @@
       <c r="X696" s="11"/>
       <c r="Y696" s="11"/>
     </row>
-    <row r="697" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="697" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D697" s="29"/>
       <c r="G697" s="11"/>
       <c r="H697" s="11"/>
@@ -17106,7 +17106,7 @@
       <c r="X697" s="11"/>
       <c r="Y697" s="11"/>
     </row>
-    <row r="698" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="698" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D698" s="29"/>
       <c r="G698" s="11"/>
       <c r="H698" s="11"/>
@@ -17128,7 +17128,7 @@
       <c r="X698" s="11"/>
       <c r="Y698" s="11"/>
     </row>
-    <row r="699" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="699" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D699" s="29"/>
       <c r="G699" s="11"/>
       <c r="H699" s="11"/>
@@ -17150,7 +17150,7 @@
       <c r="X699" s="11"/>
       <c r="Y699" s="11"/>
     </row>
-    <row r="700" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="700" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D700" s="29"/>
       <c r="G700" s="11"/>
       <c r="H700" s="11"/>
@@ -17172,7 +17172,7 @@
       <c r="X700" s="11"/>
       <c r="Y700" s="11"/>
     </row>
-    <row r="701" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="701" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D701" s="29"/>
       <c r="G701" s="11"/>
       <c r="H701" s="11"/>
@@ -17194,7 +17194,7 @@
       <c r="X701" s="11"/>
       <c r="Y701" s="11"/>
     </row>
-    <row r="702" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="702" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D702" s="29"/>
       <c r="G702" s="11"/>
       <c r="H702" s="11"/>
@@ -17216,7 +17216,7 @@
       <c r="X702" s="11"/>
       <c r="Y702" s="11"/>
     </row>
-    <row r="703" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="703" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D703" s="29"/>
       <c r="G703" s="11"/>
       <c r="H703" s="11"/>
@@ -17238,7 +17238,7 @@
       <c r="X703" s="11"/>
       <c r="Y703" s="11"/>
     </row>
-    <row r="704" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="704" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D704" s="29"/>
       <c r="G704" s="11"/>
       <c r="H704" s="11"/>
@@ -17260,7 +17260,7 @@
       <c r="X704" s="11"/>
       <c r="Y704" s="11"/>
     </row>
-    <row r="705" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="705" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D705" s="29"/>
       <c r="G705" s="11"/>
       <c r="H705" s="11"/>
@@ -17282,7 +17282,7 @@
       <c r="X705" s="11"/>
       <c r="Y705" s="11"/>
     </row>
-    <row r="706" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="706" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D706" s="29"/>
       <c r="G706" s="11"/>
       <c r="H706" s="11"/>
@@ -17304,7 +17304,7 @@
       <c r="X706" s="11"/>
       <c r="Y706" s="11"/>
     </row>
-    <row r="707" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="707" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D707" s="29"/>
       <c r="G707" s="11"/>
       <c r="H707" s="11"/>
@@ -17326,7 +17326,7 @@
       <c r="X707" s="11"/>
       <c r="Y707" s="11"/>
     </row>
-    <row r="708" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="708" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D708" s="29"/>
       <c r="G708" s="11"/>
       <c r="H708" s="11"/>
@@ -17348,7 +17348,7 @@
       <c r="X708" s="11"/>
       <c r="Y708" s="11"/>
     </row>
-    <row r="709" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="709" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D709" s="29"/>
       <c r="G709" s="11"/>
       <c r="H709" s="11"/>
@@ -17370,7 +17370,7 @@
       <c r="X709" s="11"/>
       <c r="Y709" s="11"/>
     </row>
-    <row r="710" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="710" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D710" s="29"/>
       <c r="G710" s="11"/>
       <c r="H710" s="11"/>
@@ -17392,7 +17392,7 @@
       <c r="X710" s="11"/>
       <c r="Y710" s="11"/>
     </row>
-    <row r="711" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="711" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D711" s="29"/>
       <c r="G711" s="11"/>
       <c r="H711" s="11"/>
@@ -17414,7 +17414,7 @@
       <c r="X711" s="11"/>
       <c r="Y711" s="11"/>
     </row>
-    <row r="712" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="712" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D712" s="29"/>
       <c r="G712" s="11"/>
       <c r="H712" s="11"/>
@@ -17436,7 +17436,7 @@
       <c r="X712" s="11"/>
       <c r="Y712" s="11"/>
     </row>
-    <row r="713" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="713" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D713" s="29"/>
       <c r="G713" s="11"/>
       <c r="H713" s="11"/>
@@ -17458,7 +17458,7 @@
       <c r="X713" s="11"/>
       <c r="Y713" s="11"/>
     </row>
-    <row r="714" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="714" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D714" s="29"/>
       <c r="G714" s="11"/>
       <c r="H714" s="11"/>
@@ -17480,7 +17480,7 @@
       <c r="X714" s="11"/>
       <c r="Y714" s="11"/>
     </row>
-    <row r="715" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="715" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D715" s="29"/>
       <c r="G715" s="11"/>
       <c r="H715" s="11"/>
@@ -17502,7 +17502,7 @@
       <c r="X715" s="11"/>
       <c r="Y715" s="11"/>
     </row>
-    <row r="716" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="716" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D716" s="29"/>
       <c r="G716" s="11"/>
       <c r="H716" s="11"/>
@@ -17524,7 +17524,7 @@
       <c r="X716" s="11"/>
       <c r="Y716" s="11"/>
     </row>
-    <row r="717" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="717" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D717" s="29"/>
       <c r="G717" s="11"/>
       <c r="H717" s="11"/>
@@ -17546,7 +17546,7 @@
       <c r="X717" s="11"/>
       <c r="Y717" s="11"/>
     </row>
-    <row r="718" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="718" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D718" s="29"/>
       <c r="G718" s="11"/>
       <c r="H718" s="11"/>
@@ -17568,7 +17568,7 @@
       <c r="X718" s="11"/>
       <c r="Y718" s="11"/>
     </row>
-    <row r="719" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="719" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D719" s="29"/>
       <c r="G719" s="11"/>
       <c r="H719" s="11"/>
@@ -17590,7 +17590,7 @@
       <c r="X719" s="11"/>
       <c r="Y719" s="11"/>
     </row>
-    <row r="720" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="720" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D720" s="29"/>
       <c r="G720" s="11"/>
       <c r="H720" s="11"/>
@@ -17612,7 +17612,7 @@
       <c r="X720" s="11"/>
       <c r="Y720" s="11"/>
     </row>
-    <row r="721" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="721" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D721" s="29"/>
       <c r="G721" s="11"/>
       <c r="H721" s="11"/>
@@ -17634,7 +17634,7 @@
       <c r="X721" s="11"/>
       <c r="Y721" s="11"/>
     </row>
-    <row r="722" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="722" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D722" s="29"/>
       <c r="G722" s="11"/>
       <c r="H722" s="11"/>
@@ -17656,7 +17656,7 @@
       <c r="X722" s="11"/>
       <c r="Y722" s="11"/>
     </row>
-    <row r="723" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="723" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D723" s="29"/>
       <c r="G723" s="11"/>
       <c r="H723" s="11"/>
@@ -17678,7 +17678,7 @@
       <c r="X723" s="11"/>
       <c r="Y723" s="11"/>
     </row>
-    <row r="724" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="724" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D724" s="29"/>
       <c r="G724" s="11"/>
       <c r="H724" s="11"/>
@@ -17700,7 +17700,7 @@
       <c r="X724" s="11"/>
       <c r="Y724" s="11"/>
     </row>
-    <row r="725" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="725" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D725" s="29"/>
       <c r="G725" s="11"/>
       <c r="H725" s="11"/>
@@ -17722,7 +17722,7 @@
       <c r="X725" s="11"/>
       <c r="Y725" s="11"/>
     </row>
-    <row r="726" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="726" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D726" s="29"/>
       <c r="G726" s="11"/>
       <c r="H726" s="11"/>
@@ -17744,7 +17744,7 @@
       <c r="X726" s="11"/>
       <c r="Y726" s="11"/>
     </row>
-    <row r="727" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="727" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D727" s="29"/>
       <c r="G727" s="11"/>
       <c r="H727" s="11"/>
@@ -17766,7 +17766,7 @@
       <c r="X727" s="11"/>
       <c r="Y727" s="11"/>
     </row>
-    <row r="728" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="728" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D728" s="29"/>
       <c r="G728" s="11"/>
       <c r="H728" s="11"/>
@@ -17788,7 +17788,7 @@
       <c r="X728" s="11"/>
       <c r="Y728" s="11"/>
     </row>
-    <row r="729" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="729" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D729" s="29"/>
       <c r="G729" s="11"/>
       <c r="H729" s="11"/>
@@ -17810,7 +17810,7 @@
       <c r="X729" s="11"/>
       <c r="Y729" s="11"/>
     </row>
-    <row r="730" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="730" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D730" s="29"/>
       <c r="G730" s="11"/>
       <c r="H730" s="11"/>
@@ -17832,7 +17832,7 @@
       <c r="X730" s="11"/>
       <c r="Y730" s="11"/>
     </row>
-    <row r="731" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="731" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D731" s="29"/>
       <c r="G731" s="11"/>
       <c r="H731" s="11"/>
@@ -17854,7 +17854,7 @@
       <c r="X731" s="11"/>
       <c r="Y731" s="11"/>
     </row>
-    <row r="732" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="732" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D732" s="29"/>
       <c r="G732" s="11"/>
       <c r="H732" s="11"/>
@@ -17876,7 +17876,7 @@
       <c r="X732" s="11"/>
       <c r="Y732" s="11"/>
     </row>
-    <row r="733" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="733" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D733" s="29"/>
       <c r="G733" s="11"/>
       <c r="H733" s="11"/>
@@ -17898,7 +17898,7 @@
       <c r="X733" s="11"/>
       <c r="Y733" s="11"/>
     </row>
-    <row r="734" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="734" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D734" s="29"/>
       <c r="G734" s="11"/>
       <c r="H734" s="11"/>
@@ -17920,7 +17920,7 @@
       <c r="X734" s="11"/>
       <c r="Y734" s="11"/>
     </row>
-    <row r="735" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="735" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D735" s="29"/>
       <c r="G735" s="11"/>
       <c r="H735" s="11"/>
@@ -17942,7 +17942,7 @@
       <c r="X735" s="11"/>
       <c r="Y735" s="11"/>
     </row>
-    <row r="736" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="736" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D736" s="29"/>
       <c r="G736" s="11"/>
       <c r="H736" s="11"/>
@@ -17964,7 +17964,7 @@
       <c r="X736" s="11"/>
       <c r="Y736" s="11"/>
     </row>
-    <row r="737" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="737" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D737" s="29"/>
       <c r="G737" s="11"/>
       <c r="H737" s="11"/>
@@ -17986,7 +17986,7 @@
       <c r="X737" s="11"/>
       <c r="Y737" s="11"/>
     </row>
-    <row r="738" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="738" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D738" s="29"/>
       <c r="G738" s="11"/>
       <c r="H738" s="11"/>
@@ -18008,7 +18008,7 @@
       <c r="X738" s="11"/>
       <c r="Y738" s="11"/>
     </row>
-    <row r="739" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="739" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D739" s="29"/>
       <c r="G739" s="11"/>
       <c r="H739" s="11"/>
@@ -18030,7 +18030,7 @@
       <c r="X739" s="11"/>
       <c r="Y739" s="11"/>
     </row>
-    <row r="740" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="740" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D740" s="29"/>
       <c r="G740" s="11"/>
       <c r="H740" s="11"/>
@@ -18052,7 +18052,7 @@
       <c r="X740" s="11"/>
       <c r="Y740" s="11"/>
     </row>
-    <row r="741" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="741" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D741" s="29"/>
       <c r="G741" s="11"/>
       <c r="H741" s="11"/>
@@ -18074,7 +18074,7 @@
       <c r="X741" s="11"/>
       <c r="Y741" s="11"/>
     </row>
-    <row r="742" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="742" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D742" s="29"/>
       <c r="G742" s="11"/>
       <c r="H742" s="11"/>
@@ -18096,7 +18096,7 @@
       <c r="X742" s="11"/>
       <c r="Y742" s="11"/>
     </row>
-    <row r="743" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="743" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D743" s="29"/>
       <c r="G743" s="11"/>
       <c r="H743" s="11"/>
@@ -18118,7 +18118,7 @@
       <c r="X743" s="11"/>
       <c r="Y743" s="11"/>
     </row>
-    <row r="744" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="744" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D744" s="29"/>
       <c r="G744" s="11"/>
       <c r="H744" s="11"/>
@@ -18140,7 +18140,7 @@
       <c r="X744" s="11"/>
       <c r="Y744" s="11"/>
     </row>
-    <row r="745" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="745" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D745" s="29"/>
       <c r="G745" s="11"/>
       <c r="H745" s="11"/>
@@ -18162,7 +18162,7 @@
       <c r="X745" s="11"/>
       <c r="Y745" s="11"/>
     </row>
-    <row r="746" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="746" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D746" s="29"/>
       <c r="G746" s="11"/>
       <c r="H746" s="11"/>
@@ -18184,7 +18184,7 @@
       <c r="X746" s="11"/>
       <c r="Y746" s="11"/>
     </row>
-    <row r="747" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="747" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D747" s="29"/>
       <c r="G747" s="11"/>
       <c r="H747" s="11"/>
@@ -18206,7 +18206,7 @@
       <c r="X747" s="11"/>
       <c r="Y747" s="11"/>
     </row>
-    <row r="748" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="748" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D748" s="29"/>
       <c r="G748" s="11"/>
       <c r="H748" s="11"/>
@@ -18228,7 +18228,7 @@
       <c r="X748" s="11"/>
       <c r="Y748" s="11"/>
     </row>
-    <row r="749" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="749" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D749" s="29"/>
       <c r="G749" s="11"/>
       <c r="H749" s="11"/>
@@ -18250,7 +18250,7 @@
       <c r="X749" s="11"/>
       <c r="Y749" s="11"/>
     </row>
-    <row r="750" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="750" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D750" s="29"/>
       <c r="G750" s="11"/>
       <c r="H750" s="11"/>
@@ -18272,7 +18272,7 @@
       <c r="X750" s="11"/>
       <c r="Y750" s="11"/>
     </row>
-    <row r="751" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="751" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D751" s="29"/>
       <c r="G751" s="11"/>
       <c r="H751" s="11"/>
@@ -18294,7 +18294,7 @@
       <c r="X751" s="11"/>
       <c r="Y751" s="11"/>
     </row>
-    <row r="752" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="752" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D752" s="29"/>
       <c r="G752" s="11"/>
       <c r="H752" s="11"/>
@@ -18316,7 +18316,7 @@
       <c r="X752" s="11"/>
       <c r="Y752" s="11"/>
     </row>
-    <row r="753" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="753" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D753" s="29"/>
       <c r="G753" s="11"/>
       <c r="H753" s="11"/>
@@ -18338,7 +18338,7 @@
       <c r="X753" s="11"/>
       <c r="Y753" s="11"/>
     </row>
-    <row r="754" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="754" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D754" s="29"/>
       <c r="G754" s="11"/>
       <c r="H754" s="11"/>
@@ -18360,7 +18360,7 @@
       <c r="X754" s="11"/>
       <c r="Y754" s="11"/>
     </row>
-    <row r="755" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="755" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D755" s="29"/>
       <c r="G755" s="11"/>
       <c r="H755" s="11"/>
@@ -18382,7 +18382,7 @@
       <c r="X755" s="11"/>
       <c r="Y755" s="11"/>
     </row>
-    <row r="756" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="756" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D756" s="29"/>
       <c r="G756" s="11"/>
       <c r="H756" s="11"/>
@@ -18404,7 +18404,7 @@
       <c r="X756" s="11"/>
       <c r="Y756" s="11"/>
     </row>
-    <row r="757" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="757" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D757" s="29"/>
       <c r="G757" s="11"/>
       <c r="H757" s="11"/>
@@ -18426,7 +18426,7 @@
       <c r="X757" s="11"/>
       <c r="Y757" s="11"/>
     </row>
-    <row r="758" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="758" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D758" s="29"/>
       <c r="G758" s="11"/>
       <c r="H758" s="11"/>
@@ -18448,7 +18448,7 @@
       <c r="X758" s="11"/>
       <c r="Y758" s="11"/>
     </row>
-    <row r="759" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="759" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D759" s="29"/>
       <c r="G759" s="11"/>
       <c r="H759" s="11"/>
@@ -18470,7 +18470,7 @@
       <c r="X759" s="11"/>
       <c r="Y759" s="11"/>
     </row>
-    <row r="760" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="760" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D760" s="29"/>
       <c r="G760" s="11"/>
       <c r="H760" s="11"/>
@@ -18492,7 +18492,7 @@
       <c r="X760" s="11"/>
       <c r="Y760" s="11"/>
     </row>
-    <row r="761" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="761" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D761" s="29"/>
       <c r="G761" s="11"/>
       <c r="H761" s="11"/>
@@ -18514,7 +18514,7 @@
       <c r="X761" s="11"/>
       <c r="Y761" s="11"/>
     </row>
-    <row r="762" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="762" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D762" s="29"/>
       <c r="G762" s="11"/>
       <c r="H762" s="11"/>
@@ -18536,7 +18536,7 @@
       <c r="X762" s="11"/>
       <c r="Y762" s="11"/>
     </row>
-    <row r="763" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="763" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D763" s="29"/>
       <c r="G763" s="11"/>
       <c r="H763" s="11"/>
@@ -18558,7 +18558,7 @@
       <c r="X763" s="11"/>
       <c r="Y763" s="11"/>
     </row>
-    <row r="764" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="764" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D764" s="29"/>
       <c r="G764" s="11"/>
       <c r="H764" s="11"/>
@@ -18580,7 +18580,7 @@
       <c r="X764" s="11"/>
       <c r="Y764" s="11"/>
     </row>
-    <row r="765" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="765" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D765" s="29"/>
       <c r="G765" s="11"/>
       <c r="H765" s="11"/>
@@ -18602,7 +18602,7 @@
       <c r="X765" s="11"/>
       <c r="Y765" s="11"/>
     </row>
-    <row r="766" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="766" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D766" s="29"/>
       <c r="G766" s="11"/>
       <c r="H766" s="11"/>
@@ -18624,7 +18624,7 @@
       <c r="X766" s="11"/>
       <c r="Y766" s="11"/>
     </row>
-    <row r="767" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="767" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D767" s="29"/>
       <c r="G767" s="11"/>
       <c r="H767" s="11"/>
@@ -18646,7 +18646,7 @@
       <c r="X767" s="11"/>
       <c r="Y767" s="11"/>
     </row>
-    <row r="768" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="768" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D768" s="29"/>
       <c r="G768" s="11"/>
       <c r="H768" s="11"/>
@@ -18668,7 +18668,7 @@
       <c r="X768" s="11"/>
       <c r="Y768" s="11"/>
     </row>
-    <row r="769" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="769" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D769" s="29"/>
       <c r="G769" s="11"/>
       <c r="H769" s="11"/>
@@ -18690,7 +18690,7 @@
       <c r="X769" s="11"/>
       <c r="Y769" s="11"/>
     </row>
-    <row r="770" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="770" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D770" s="29"/>
       <c r="G770" s="11"/>
       <c r="H770" s="11"/>
@@ -18712,7 +18712,7 @@
       <c r="X770" s="11"/>
       <c r="Y770" s="11"/>
     </row>
-    <row r="771" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="771" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D771" s="29"/>
       <c r="G771" s="11"/>
       <c r="H771" s="11"/>
@@ -18734,7 +18734,7 @@
       <c r="X771" s="11"/>
       <c r="Y771" s="11"/>
     </row>
-    <row r="772" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="772" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D772" s="29"/>
       <c r="G772" s="11"/>
       <c r="H772" s="11"/>
@@ -18756,7 +18756,7 @@
       <c r="X772" s="11"/>
       <c r="Y772" s="11"/>
     </row>
-    <row r="773" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="773" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D773" s="29"/>
       <c r="G773" s="11"/>
       <c r="H773" s="11"/>
@@ -18778,7 +18778,7 @@
       <c r="X773" s="11"/>
       <c r="Y773" s="11"/>
     </row>
-    <row r="774" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="774" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D774" s="29"/>
       <c r="G774" s="11"/>
       <c r="H774" s="11"/>
@@ -18800,7 +18800,7 @@
       <c r="X774" s="11"/>
       <c r="Y774" s="11"/>
     </row>
-    <row r="775" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="775" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D775" s="29"/>
       <c r="G775" s="11"/>
       <c r="H775" s="11"/>
@@ -18822,7 +18822,7 @@
       <c r="X775" s="11"/>
       <c r="Y775" s="11"/>
     </row>
-    <row r="776" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="776" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D776" s="29"/>
       <c r="G776" s="11"/>
       <c r="H776" s="11"/>
@@ -18844,7 +18844,7 @@
       <c r="X776" s="11"/>
       <c r="Y776" s="11"/>
     </row>
-    <row r="777" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="777" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D777" s="29"/>
       <c r="G777" s="11"/>
       <c r="H777" s="11"/>
@@ -18866,7 +18866,7 @@
       <c r="X777" s="11"/>
       <c r="Y777" s="11"/>
     </row>
-    <row r="778" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="778" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D778" s="29"/>
       <c r="G778" s="11"/>
       <c r="H778" s="11"/>
@@ -18888,7 +18888,7 @@
       <c r="X778" s="11"/>
       <c r="Y778" s="11"/>
     </row>
-    <row r="779" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="779" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D779" s="29"/>
       <c r="G779" s="11"/>
       <c r="H779" s="11"/>
@@ -18910,7 +18910,7 @@
       <c r="X779" s="11"/>
       <c r="Y779" s="11"/>
     </row>
-    <row r="780" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="780" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D780" s="29"/>
       <c r="G780" s="11"/>
       <c r="H780" s="11"/>
@@ -18932,7 +18932,7 @@
       <c r="X780" s="11"/>
       <c r="Y780" s="11"/>
     </row>
-    <row r="781" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="781" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D781" s="29"/>
       <c r="G781" s="11"/>
       <c r="H781" s="11"/>
@@ -18954,7 +18954,7 @@
       <c r="X781" s="11"/>
       <c r="Y781" s="11"/>
     </row>
-    <row r="782" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="782" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D782" s="29"/>
       <c r="G782" s="11"/>
       <c r="H782" s="11"/>
@@ -18976,7 +18976,7 @@
       <c r="X782" s="11"/>
       <c r="Y782" s="11"/>
     </row>
-    <row r="783" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="783" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D783" s="29"/>
       <c r="G783" s="11"/>
       <c r="H783" s="11"/>
@@ -18998,7 +18998,7 @@
       <c r="X783" s="11"/>
       <c r="Y783" s="11"/>
     </row>
-    <row r="784" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="784" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D784" s="29"/>
       <c r="G784" s="11"/>
       <c r="H784" s="11"/>
@@ -19020,7 +19020,7 @@
       <c r="X784" s="11"/>
       <c r="Y784" s="11"/>
     </row>
-    <row r="785" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="785" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D785" s="29"/>
       <c r="G785" s="11"/>
       <c r="H785" s="11"/>
@@ -19042,7 +19042,7 @@
       <c r="X785" s="11"/>
       <c r="Y785" s="11"/>
     </row>
-    <row r="786" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="786" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D786" s="29"/>
       <c r="G786" s="11"/>
       <c r="H786" s="11"/>
@@ -19064,7 +19064,7 @@
       <c r="X786" s="11"/>
       <c r="Y786" s="11"/>
     </row>
-    <row r="787" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="787" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D787" s="29"/>
       <c r="G787" s="11"/>
       <c r="H787" s="11"/>
@@ -19086,7 +19086,7 @@
       <c r="X787" s="11"/>
       <c r="Y787" s="11"/>
     </row>
-    <row r="788" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="788" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D788" s="29"/>
       <c r="G788" s="11"/>
       <c r="H788" s="11"/>
@@ -19108,7 +19108,7 @@
       <c r="X788" s="11"/>
       <c r="Y788" s="11"/>
     </row>
-    <row r="789" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="789" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D789" s="29"/>
       <c r="G789" s="11"/>
       <c r="H789" s="11"/>
@@ -19130,7 +19130,7 @@
       <c r="X789" s="11"/>
       <c r="Y789" s="11"/>
     </row>
-    <row r="790" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="790" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D790" s="29"/>
       <c r="G790" s="11"/>
       <c r="H790" s="11"/>
@@ -19152,7 +19152,7 @@
       <c r="X790" s="11"/>
       <c r="Y790" s="11"/>
     </row>
-    <row r="791" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="791" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D791" s="29"/>
       <c r="G791" s="11"/>
       <c r="H791" s="11"/>
@@ -19174,7 +19174,7 @@
       <c r="X791" s="11"/>
       <c r="Y791" s="11"/>
     </row>
-    <row r="792" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="792" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D792" s="29"/>
       <c r="G792" s="11"/>
       <c r="H792" s="11"/>
@@ -19196,7 +19196,7 @@
       <c r="X792" s="11"/>
       <c r="Y792" s="11"/>
     </row>
-    <row r="793" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="793" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D793" s="29"/>
       <c r="G793" s="11"/>
       <c r="H793" s="11"/>
@@ -19218,7 +19218,7 @@
       <c r="X793" s="11"/>
       <c r="Y793" s="11"/>
     </row>
-    <row r="794" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="794" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D794" s="29"/>
       <c r="G794" s="11"/>
       <c r="H794" s="11"/>
@@ -19240,7 +19240,7 @@
       <c r="X794" s="11"/>
       <c r="Y794" s="11"/>
     </row>
-    <row r="795" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="795" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D795" s="29"/>
       <c r="G795" s="11"/>
       <c r="H795" s="11"/>
@@ -19262,7 +19262,7 @@
       <c r="X795" s="11"/>
       <c r="Y795" s="11"/>
     </row>
-    <row r="796" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="796" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D796" s="29"/>
       <c r="G796" s="11"/>
       <c r="H796" s="11"/>
@@ -19284,7 +19284,7 @@
       <c r="X796" s="11"/>
       <c r="Y796" s="11"/>
     </row>
-    <row r="797" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="797" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D797" s="29"/>
       <c r="G797" s="11"/>
       <c r="H797" s="11"/>
@@ -19306,7 +19306,7 @@
       <c r="X797" s="11"/>
       <c r="Y797" s="11"/>
     </row>
-    <row r="798" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="798" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D798" s="29"/>
       <c r="G798" s="11"/>
       <c r="H798" s="11"/>
@@ -19328,7 +19328,7 @@
       <c r="X798" s="11"/>
       <c r="Y798" s="11"/>
     </row>
-    <row r="799" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="799" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D799" s="29"/>
       <c r="G799" s="11"/>
       <c r="H799" s="11"/>
@@ -19350,7 +19350,7 @@
       <c r="X799" s="11"/>
       <c r="Y799" s="11"/>
     </row>
-    <row r="800" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="800" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D800" s="29"/>
       <c r="G800" s="11"/>
       <c r="H800" s="11"/>
@@ -19372,7 +19372,7 @@
       <c r="X800" s="11"/>
       <c r="Y800" s="11"/>
     </row>
-    <row r="801" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="801" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D801" s="29"/>
       <c r="G801" s="11"/>
       <c r="H801" s="11"/>
@@ -19394,7 +19394,7 @@
       <c r="X801" s="11"/>
       <c r="Y801" s="11"/>
     </row>
-    <row r="802" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="802" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D802" s="29"/>
       <c r="G802" s="11"/>
       <c r="H802" s="11"/>
@@ -19416,7 +19416,7 @@
       <c r="X802" s="11"/>
       <c r="Y802" s="11"/>
     </row>
-    <row r="803" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="803" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D803" s="29"/>
       <c r="G803" s="11"/>
       <c r="H803" s="11"/>
@@ -19438,7 +19438,7 @@
       <c r="X803" s="11"/>
       <c r="Y803" s="11"/>
     </row>
-    <row r="804" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="804" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D804" s="29"/>
       <c r="G804" s="11"/>
       <c r="H804" s="11"/>
@@ -19460,7 +19460,7 @@
       <c r="X804" s="11"/>
       <c r="Y804" s="11"/>
     </row>
-    <row r="805" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="805" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D805" s="29"/>
       <c r="G805" s="11"/>
       <c r="H805" s="11"/>
@@ -19482,7 +19482,7 @@
       <c r="X805" s="11"/>
       <c r="Y805" s="11"/>
     </row>
-    <row r="806" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="806" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D806" s="29"/>
       <c r="G806" s="11"/>
       <c r="H806" s="11"/>
@@ -19504,7 +19504,7 @@
       <c r="X806" s="11"/>
       <c r="Y806" s="11"/>
     </row>
-    <row r="807" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="807" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D807" s="29"/>
       <c r="G807" s="11"/>
       <c r="H807" s="11"/>
@@ -19526,7 +19526,7 @@
       <c r="X807" s="11"/>
       <c r="Y807" s="11"/>
     </row>
-    <row r="808" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="808" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D808" s="29"/>
       <c r="G808" s="11"/>
       <c r="H808" s="11"/>
@@ -19548,7 +19548,7 @@
       <c r="X808" s="11"/>
       <c r="Y808" s="11"/>
     </row>
-    <row r="809" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="809" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D809" s="29"/>
       <c r="G809" s="11"/>
       <c r="H809" s="11"/>
@@ -19570,7 +19570,7 @@
       <c r="X809" s="11"/>
       <c r="Y809" s="11"/>
     </row>
-    <row r="810" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="810" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D810" s="29"/>
       <c r="G810" s="11"/>
       <c r="H810" s="11"/>
@@ -19592,7 +19592,7 @@
       <c r="X810" s="11"/>
       <c r="Y810" s="11"/>
     </row>
-    <row r="811" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="811" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D811" s="29"/>
       <c r="G811" s="11"/>
       <c r="H811" s="11"/>
@@ -19614,7 +19614,7 @@
       <c r="X811" s="11"/>
       <c r="Y811" s="11"/>
     </row>
-    <row r="812" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="812" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D812" s="29"/>
       <c r="G812" s="11"/>
       <c r="H812" s="11"/>
@@ -19636,7 +19636,7 @@
       <c r="X812" s="11"/>
       <c r="Y812" s="11"/>
     </row>
-    <row r="813" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="813" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D813" s="29"/>
       <c r="G813" s="11"/>
       <c r="H813" s="11"/>
@@ -19658,7 +19658,7 @@
       <c r="X813" s="11"/>
       <c r="Y813" s="11"/>
     </row>
-    <row r="814" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="814" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D814" s="29"/>
       <c r="G814" s="11"/>
       <c r="H814" s="11"/>
@@ -19680,7 +19680,7 @@
       <c r="X814" s="11"/>
       <c r="Y814" s="11"/>
     </row>
-    <row r="815" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="815" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D815" s="29"/>
       <c r="G815" s="11"/>
       <c r="H815" s="11"/>
@@ -19702,7 +19702,7 @@
       <c r="X815" s="11"/>
       <c r="Y815" s="11"/>
     </row>
-    <row r="816" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="816" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D816" s="29"/>
       <c r="G816" s="11"/>
       <c r="H816" s="11"/>
@@ -19724,7 +19724,7 @@
       <c r="X816" s="11"/>
       <c r="Y816" s="11"/>
     </row>
-    <row r="817" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="817" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D817" s="29"/>
       <c r="G817" s="11"/>
       <c r="H817" s="11"/>
@@ -19746,7 +19746,7 @@
       <c r="X817" s="11"/>
       <c r="Y817" s="11"/>
     </row>
-    <row r="818" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="818" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D818" s="29"/>
       <c r="G818" s="11"/>
       <c r="H818" s="11"/>
@@ -19768,7 +19768,7 @@
       <c r="X818" s="11"/>
       <c r="Y818" s="11"/>
     </row>
-    <row r="819" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="819" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D819" s="29"/>
       <c r="G819" s="11"/>
       <c r="H819" s="11"/>
@@ -19790,7 +19790,7 @@
       <c r="X819" s="11"/>
       <c r="Y819" s="11"/>
     </row>
-    <row r="820" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="820" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D820" s="29"/>
       <c r="G820" s="11"/>
       <c r="H820" s="11"/>
@@ -19812,7 +19812,7 @@
       <c r="X820" s="11"/>
       <c r="Y820" s="11"/>
     </row>
-    <row r="821" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="821" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D821" s="29"/>
       <c r="G821" s="11"/>
       <c r="H821" s="11"/>
@@ -19834,7 +19834,7 @@
       <c r="X821" s="11"/>
       <c r="Y821" s="11"/>
     </row>
-    <row r="822" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="822" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D822" s="29"/>
       <c r="G822" s="11"/>
       <c r="H822" s="11"/>
@@ -19856,7 +19856,7 @@
       <c r="X822" s="11"/>
       <c r="Y822" s="11"/>
     </row>
-    <row r="823" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="823" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D823" s="29"/>
       <c r="G823" s="11"/>
       <c r="H823" s="11"/>
@@ -19878,7 +19878,7 @@
       <c r="X823" s="11"/>
       <c r="Y823" s="11"/>
     </row>
-    <row r="824" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="824" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D824" s="29"/>
       <c r="G824" s="11"/>
       <c r="H824" s="11"/>
@@ -19900,7 +19900,7 @@
       <c r="X824" s="11"/>
       <c r="Y824" s="11"/>
     </row>
-    <row r="825" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="825" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D825" s="29"/>
       <c r="G825" s="11"/>
       <c r="H825" s="11"/>
@@ -19922,7 +19922,7 @@
       <c r="X825" s="11"/>
       <c r="Y825" s="11"/>
     </row>
-    <row r="826" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="826" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D826" s="29"/>
       <c r="G826" s="11"/>
       <c r="H826" s="11"/>
@@ -19944,7 +19944,7 @@
       <c r="X826" s="11"/>
       <c r="Y826" s="11"/>
     </row>
-    <row r="827" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="827" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D827" s="29"/>
       <c r="G827" s="11"/>
       <c r="H827" s="11"/>
@@ -19966,7 +19966,7 @@
       <c r="X827" s="11"/>
       <c r="Y827" s="11"/>
     </row>
-    <row r="828" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="828" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D828" s="29"/>
       <c r="G828" s="11"/>
       <c r="H828" s="11"/>
@@ -19988,7 +19988,7 @@
       <c r="X828" s="11"/>
       <c r="Y828" s="11"/>
     </row>
-    <row r="829" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="829" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D829" s="29"/>
       <c r="G829" s="11"/>
       <c r="H829" s="11"/>
@@ -20010,7 +20010,7 @@
       <c r="X829" s="11"/>
       <c r="Y829" s="11"/>
     </row>
-    <row r="830" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="830" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D830" s="29"/>
       <c r="G830" s="11"/>
       <c r="H830" s="11"/>
@@ -20032,7 +20032,7 @@
       <c r="X830" s="11"/>
       <c r="Y830" s="11"/>
     </row>
-    <row r="831" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="831" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D831" s="29"/>
       <c r="G831" s="11"/>
       <c r="H831" s="11"/>
@@ -20054,7 +20054,7 @@
       <c r="X831" s="11"/>
       <c r="Y831" s="11"/>
     </row>
-    <row r="832" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="832" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D832" s="29"/>
       <c r="G832" s="11"/>
       <c r="H832" s="11"/>
@@ -20076,7 +20076,7 @@
       <c r="X832" s="11"/>
       <c r="Y832" s="11"/>
     </row>
-    <row r="833" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="833" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D833" s="29"/>
       <c r="G833" s="11"/>
       <c r="H833" s="11"/>
@@ -20098,7 +20098,7 @@
       <c r="X833" s="11"/>
       <c r="Y833" s="11"/>
     </row>
-    <row r="834" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="834" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D834" s="29"/>
       <c r="G834" s="11"/>
       <c r="H834" s="11"/>
@@ -20120,7 +20120,7 @@
       <c r="X834" s="11"/>
       <c r="Y834" s="11"/>
     </row>
-    <row r="835" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="835" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D835" s="29"/>
       <c r="G835" s="11"/>
       <c r="H835" s="11"/>
@@ -20142,7 +20142,7 @@
       <c r="X835" s="11"/>
       <c r="Y835" s="11"/>
     </row>
-    <row r="836" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="836" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D836" s="29"/>
       <c r="G836" s="11"/>
       <c r="H836" s="11"/>
@@ -20164,7 +20164,7 @@
       <c r="X836" s="11"/>
       <c r="Y836" s="11"/>
     </row>
-    <row r="837" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="837" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D837" s="29"/>
       <c r="G837" s="11"/>
       <c r="H837" s="11"/>
@@ -20186,7 +20186,7 @@
       <c r="X837" s="11"/>
       <c r="Y837" s="11"/>
     </row>
-    <row r="838" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="838" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D838" s="29"/>
       <c r="G838" s="11"/>
       <c r="H838" s="11"/>
@@ -20208,7 +20208,7 @@
       <c r="X838" s="11"/>
       <c r="Y838" s="11"/>
     </row>
-    <row r="839" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="839" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D839" s="29"/>
       <c r="G839" s="11"/>
       <c r="H839" s="11"/>
@@ -20230,7 +20230,7 @@
       <c r="X839" s="11"/>
       <c r="Y839" s="11"/>
     </row>
-    <row r="840" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="840" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D840" s="29"/>
       <c r="G840" s="11"/>
       <c r="H840" s="11"/>
@@ -20252,7 +20252,7 @@
       <c r="X840" s="11"/>
       <c r="Y840" s="11"/>
     </row>
-    <row r="841" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="841" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D841" s="29"/>
       <c r="G841" s="11"/>
       <c r="H841" s="11"/>
@@ -20274,7 +20274,7 @@
       <c r="X841" s="11"/>
       <c r="Y841" s="11"/>
     </row>
-    <row r="842" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="842" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D842" s="29"/>
       <c r="G842" s="11"/>
       <c r="H842" s="11"/>
@@ -20296,7 +20296,7 @@
       <c r="X842" s="11"/>
       <c r="Y842" s="11"/>
     </row>
-    <row r="843" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="843" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D843" s="29"/>
       <c r="G843" s="11"/>
       <c r="H843" s="11"/>
@@ -20318,7 +20318,7 @@
       <c r="X843" s="11"/>
       <c r="Y843" s="11"/>
     </row>
-    <row r="844" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="844" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D844" s="29"/>
       <c r="G844" s="11"/>
       <c r="H844" s="11"/>
@@ -20340,7 +20340,7 @@
       <c r="X844" s="11"/>
       <c r="Y844" s="11"/>
     </row>
-    <row r="845" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="845" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D845" s="29"/>
       <c r="G845" s="11"/>
       <c r="H845" s="11"/>
@@ -20362,7 +20362,7 @@
       <c r="X845" s="11"/>
       <c r="Y845" s="11"/>
     </row>
-    <row r="846" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="846" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D846" s="29"/>
       <c r="G846" s="11"/>
       <c r="H846" s="11"/>
@@ -20384,7 +20384,7 @@
       <c r="X846" s="11"/>
       <c r="Y846" s="11"/>
     </row>
-    <row r="847" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="847" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D847" s="29"/>
       <c r="G847" s="11"/>
       <c r="H847" s="11"/>
@@ -20406,7 +20406,7 @@
       <c r="X847" s="11"/>
       <c r="Y847" s="11"/>
     </row>
-    <row r="848" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="848" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D848" s="29"/>
       <c r="G848" s="11"/>
       <c r="H848" s="11"/>
@@ -20428,7 +20428,7 @@
       <c r="X848" s="11"/>
       <c r="Y848" s="11"/>
     </row>
-    <row r="849" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="849" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D849" s="29"/>
       <c r="G849" s="11"/>
       <c r="H849" s="11"/>
@@ -20450,7 +20450,7 @@
       <c r="X849" s="11"/>
       <c r="Y849" s="11"/>
     </row>
-    <row r="850" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="850" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D850" s="29"/>
       <c r="G850" s="11"/>
       <c r="H850" s="11"/>
@@ -20472,7 +20472,7 @@
       <c r="X850" s="11"/>
       <c r="Y850" s="11"/>
     </row>
-    <row r="851" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="851" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D851" s="29"/>
       <c r="G851" s="11"/>
       <c r="H851" s="11"/>
@@ -20494,7 +20494,7 @@
       <c r="X851" s="11"/>
       <c r="Y851" s="11"/>
     </row>
-    <row r="852" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="852" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D852" s="29"/>
       <c r="G852" s="11"/>
       <c r="H852" s="11"/>
@@ -20516,7 +20516,7 @@
       <c r="X852" s="11"/>
       <c r="Y852" s="11"/>
     </row>
-    <row r="853" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="853" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D853" s="29"/>
       <c r="G853" s="11"/>
       <c r="H853" s="11"/>
@@ -20538,7 +20538,7 @@
       <c r="X853" s="11"/>
       <c r="Y853" s="11"/>
     </row>
-    <row r="854" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="854" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D854" s="29"/>
       <c r="G854" s="11"/>
       <c r="H854" s="11"/>
@@ -20560,7 +20560,7 @@
       <c r="X854" s="11"/>
       <c r="Y854" s="11"/>
     </row>
-    <row r="855" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="855" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D855" s="29"/>
       <c r="G855" s="11"/>
       <c r="H855" s="11"/>
@@ -20582,7 +20582,7 @@
       <c r="X855" s="11"/>
       <c r="Y855" s="11"/>
     </row>
-    <row r="856" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="856" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D856" s="29"/>
       <c r="G856" s="11"/>
       <c r="H856" s="11"/>
@@ -20604,7 +20604,7 @@
       <c r="X856" s="11"/>
       <c r="Y856" s="11"/>
     </row>
-    <row r="857" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="857" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D857" s="29"/>
       <c r="G857" s="11"/>
       <c r="H857" s="11"/>
@@ -20626,7 +20626,7 @@
       <c r="X857" s="11"/>
       <c r="Y857" s="11"/>
     </row>
-    <row r="858" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="858" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D858" s="29"/>
       <c r="G858" s="11"/>
       <c r="H858" s="11"/>
@@ -20648,7 +20648,7 @@
       <c r="X858" s="11"/>
       <c r="Y858" s="11"/>
     </row>
-    <row r="859" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="859" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D859" s="29"/>
       <c r="G859" s="11"/>
       <c r="H859" s="11"/>
@@ -20670,7 +20670,7 @@
       <c r="X859" s="11"/>
       <c r="Y859" s="11"/>
     </row>
-    <row r="860" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="860" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D860" s="29"/>
       <c r="G860" s="11"/>
       <c r="H860" s="11"/>
@@ -20692,7 +20692,7 @@
       <c r="X860" s="11"/>
       <c r="Y860" s="11"/>
     </row>
-    <row r="861" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="861" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D861" s="29"/>
       <c r="G861" s="11"/>
       <c r="H861" s="11"/>
@@ -20714,7 +20714,7 @@
       <c r="X861" s="11"/>
       <c r="Y861" s="11"/>
     </row>
-    <row r="862" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="862" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D862" s="29"/>
       <c r="G862" s="11"/>
       <c r="H862" s="11"/>
@@ -20736,7 +20736,7 @@
       <c r="X862" s="11"/>
       <c r="Y862" s="11"/>
     </row>
-    <row r="863" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="863" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D863" s="29"/>
       <c r="G863" s="11"/>
       <c r="H863" s="11"/>
@@ -20758,7 +20758,7 @@
       <c r="X863" s="11"/>
       <c r="Y863" s="11"/>
     </row>
-    <row r="864" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="864" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D864" s="29"/>
       <c r="G864" s="11"/>
       <c r="H864" s="11"/>
@@ -20780,7 +20780,7 @@
       <c r="X864" s="11"/>
       <c r="Y864" s="11"/>
     </row>
-    <row r="865" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="865" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D865" s="29"/>
       <c r="G865" s="11"/>
       <c r="H865" s="11"/>
@@ -20802,7 +20802,7 @@
       <c r="X865" s="11"/>
       <c r="Y865" s="11"/>
     </row>
-    <row r="866" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="866" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D866" s="29"/>
       <c r="G866" s="11"/>
       <c r="H866" s="11"/>
@@ -20824,7 +20824,7 @@
       <c r="X866" s="11"/>
       <c r="Y866" s="11"/>
     </row>
-    <row r="867" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="867" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D867" s="29"/>
       <c r="G867" s="11"/>
       <c r="H867" s="11"/>
@@ -20846,7 +20846,7 @@
       <c r="X867" s="11"/>
       <c r="Y867" s="11"/>
     </row>
-    <row r="868" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="868" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D868" s="29"/>
       <c r="G868" s="11"/>
       <c r="H868" s="11"/>
@@ -20868,7 +20868,7 @@
       <c r="X868" s="11"/>
       <c r="Y868" s="11"/>
     </row>
-    <row r="869" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="869" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D869" s="29"/>
       <c r="G869" s="11"/>
       <c r="H869" s="11"/>
@@ -20890,7 +20890,7 @@
       <c r="X869" s="11"/>
       <c r="Y869" s="11"/>
     </row>
-    <row r="870" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="870" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D870" s="29"/>
       <c r="G870" s="11"/>
       <c r="H870" s="11"/>
@@ -20912,7 +20912,7 @@
       <c r="X870" s="11"/>
       <c r="Y870" s="11"/>
     </row>
-    <row r="871" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="871" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D871" s="29"/>
       <c r="G871" s="11"/>
       <c r="H871" s="11"/>
@@ -20934,7 +20934,7 @@
       <c r="X871" s="11"/>
       <c r="Y871" s="11"/>
     </row>
-    <row r="872" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="872" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D872" s="29"/>
       <c r="G872" s="11"/>
       <c r="H872" s="11"/>
@@ -20956,7 +20956,7 @@
       <c r="X872" s="11"/>
       <c r="Y872" s="11"/>
     </row>
-    <row r="873" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="873" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D873" s="29"/>
       <c r="G873" s="11"/>
       <c r="H873" s="11"/>
@@ -20978,7 +20978,7 @@
       <c r="X873" s="11"/>
       <c r="Y873" s="11"/>
     </row>
-    <row r="874" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="874" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D874" s="29"/>
       <c r="G874" s="11"/>
       <c r="H874" s="11"/>
@@ -21000,7 +21000,7 @@
       <c r="X874" s="11"/>
       <c r="Y874" s="11"/>
     </row>
-    <row r="875" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="875" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D875" s="29"/>
       <c r="G875" s="11"/>
       <c r="H875" s="11"/>
@@ -21022,7 +21022,7 @@
       <c r="X875" s="11"/>
       <c r="Y875" s="11"/>
     </row>
-    <row r="876" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="876" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D876" s="29"/>
       <c r="G876" s="11"/>
       <c r="H876" s="11"/>
@@ -21044,7 +21044,7 @@
       <c r="X876" s="11"/>
       <c r="Y876" s="11"/>
     </row>
-    <row r="877" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="877" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D877" s="29"/>
       <c r="G877" s="11"/>
       <c r="H877" s="11"/>
@@ -21066,7 +21066,7 @@
       <c r="X877" s="11"/>
       <c r="Y877" s="11"/>
     </row>
-    <row r="878" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="878" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D878" s="29"/>
       <c r="G878" s="11"/>
       <c r="H878" s="11"/>
@@ -21088,7 +21088,7 @@
       <c r="X878" s="11"/>
       <c r="Y878" s="11"/>
     </row>
-    <row r="879" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="879" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D879" s="29"/>
       <c r="G879" s="11"/>
       <c r="H879" s="11"/>
@@ -21110,7 +21110,7 @@
       <c r="X879" s="11"/>
       <c r="Y879" s="11"/>
     </row>
-    <row r="880" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="880" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D880" s="29"/>
       <c r="G880" s="11"/>
       <c r="H880" s="11"/>
@@ -21132,7 +21132,7 @@
       <c r="X880" s="11"/>
       <c r="Y880" s="11"/>
     </row>
-    <row r="881" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="881" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D881" s="29"/>
       <c r="G881" s="11"/>
       <c r="H881" s="11"/>
@@ -21154,7 +21154,7 @@
       <c r="X881" s="11"/>
       <c r="Y881" s="11"/>
     </row>
-    <row r="882" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="882" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D882" s="29"/>
       <c r="G882" s="11"/>
       <c r="H882" s="11"/>
@@ -21176,7 +21176,7 @@
       <c r="X882" s="11"/>
       <c r="Y882" s="11"/>
     </row>
-    <row r="883" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="883" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D883" s="29"/>
       <c r="G883" s="11"/>
       <c r="H883" s="11"/>
@@ -21198,7 +21198,7 @@
       <c r="X883" s="11"/>
       <c r="Y883" s="11"/>
     </row>
-    <row r="884" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="884" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D884" s="29"/>
       <c r="G884" s="11"/>
       <c r="H884" s="11"/>
@@ -21220,7 +21220,7 @@
       <c r="X884" s="11"/>
       <c r="Y884" s="11"/>
     </row>
-    <row r="885" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="885" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D885" s="29"/>
       <c r="G885" s="11"/>
       <c r="H885" s="11"/>
@@ -21242,7 +21242,7 @@
       <c r="X885" s="11"/>
       <c r="Y885" s="11"/>
     </row>
-    <row r="886" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="886" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D886" s="29"/>
       <c r="G886" s="11"/>
       <c r="H886" s="11"/>
@@ -21264,7 +21264,7 @@
       <c r="X886" s="11"/>
       <c r="Y886" s="11"/>
     </row>
-    <row r="887" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="887" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D887" s="29"/>
       <c r="G887" s="11"/>
       <c r="H887" s="11"/>
@@ -21286,7 +21286,7 @@
       <c r="X887" s="11"/>
       <c r="Y887" s="11"/>
     </row>
-    <row r="888" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="888" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D888" s="29"/>
       <c r="G888" s="11"/>
       <c r="H888" s="11"/>
@@ -21308,7 +21308,7 @@
       <c r="X888" s="11"/>
       <c r="Y888" s="11"/>
     </row>
-    <row r="889" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="889" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D889" s="29"/>
       <c r="G889" s="11"/>
       <c r="H889" s="11"/>
@@ -21330,7 +21330,7 @@
       <c r="X889" s="11"/>
       <c r="Y889" s="11"/>
     </row>
-    <row r="890" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="890" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D890" s="29"/>
       <c r="G890" s="11"/>
       <c r="H890" s="11"/>
@@ -21352,7 +21352,7 @@
       <c r="X890" s="11"/>
       <c r="Y890" s="11"/>
     </row>
-    <row r="891" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="891" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D891" s="29"/>
       <c r="G891" s="11"/>
       <c r="H891" s="11"/>
@@ -21374,7 +21374,7 @@
       <c r="X891" s="11"/>
       <c r="Y891" s="11"/>
     </row>
-    <row r="892" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="892" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D892" s="29"/>
       <c r="G892" s="11"/>
       <c r="H892" s="11"/>
@@ -21396,7 +21396,7 @@
       <c r="X892" s="11"/>
       <c r="Y892" s="11"/>
     </row>
-    <row r="893" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="893" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D893" s="29"/>
       <c r="G893" s="11"/>
       <c r="H893" s="11"/>
@@ -21418,7 +21418,7 @@
       <c r="X893" s="11"/>
       <c r="Y893" s="11"/>
     </row>
-    <row r="894" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="894" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D894" s="29"/>
       <c r="G894" s="11"/>
       <c r="H894" s="11"/>
@@ -21440,7 +21440,7 @@
       <c r="X894" s="11"/>
       <c r="Y894" s="11"/>
     </row>
-    <row r="895" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="895" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D895" s="29"/>
       <c r="G895" s="11"/>
       <c r="H895" s="11"/>
@@ -21462,7 +21462,7 @@
       <c r="X895" s="11"/>
       <c r="Y895" s="11"/>
     </row>
-    <row r="896" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="896" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D896" s="29"/>
       <c r="G896" s="11"/>
       <c r="H896" s="11"/>
@@ -21484,7 +21484,7 @@
       <c r="X896" s="11"/>
       <c r="Y896" s="11"/>
     </row>
-    <row r="897" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="897" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D897" s="29"/>
       <c r="G897" s="11"/>
       <c r="H897" s="11"/>
@@ -21506,7 +21506,7 @@
       <c r="X897" s="11"/>
       <c r="Y897" s="11"/>
     </row>
-    <row r="898" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="898" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D898" s="29"/>
       <c r="G898" s="11"/>
       <c r="H898" s="11"/>
@@ -21528,7 +21528,7 @@
       <c r="X898" s="11"/>
       <c r="Y898" s="11"/>
     </row>
-    <row r="899" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="899" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D899" s="29"/>
       <c r="G899" s="11"/>
       <c r="H899" s="11"/>
@@ -21550,7 +21550,7 @@
       <c r="X899" s="11"/>
       <c r="Y899" s="11"/>
     </row>
-    <row r="900" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="900" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D900" s="29"/>
       <c r="G900" s="11"/>
       <c r="H900" s="11"/>
@@ -21572,7 +21572,7 @@
       <c r="X900" s="11"/>
       <c r="Y900" s="11"/>
     </row>
-    <row r="901" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="901" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D901" s="29"/>
       <c r="G901" s="11"/>
       <c r="H901" s="11"/>
@@ -21594,7 +21594,7 @@
       <c r="X901" s="11"/>
       <c r="Y901" s="11"/>
     </row>
-    <row r="902" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="902" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D902" s="29"/>
       <c r="G902" s="11"/>
       <c r="H902" s="11"/>
@@ -21616,7 +21616,7 @@
       <c r="X902" s="11"/>
       <c r="Y902" s="11"/>
     </row>
-    <row r="903" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="903" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D903" s="29"/>
       <c r="G903" s="11"/>
       <c r="H903" s="11"/>
@@ -21638,7 +21638,7 @@
       <c r="X903" s="11"/>
       <c r="Y903" s="11"/>
     </row>
-    <row r="904" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="904" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D904" s="29"/>
       <c r="G904" s="11"/>
       <c r="H904" s="11"/>
@@ -21660,7 +21660,7 @@
       <c r="X904" s="11"/>
       <c r="Y904" s="11"/>
     </row>
-    <row r="905" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="905" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D905" s="29"/>
       <c r="G905" s="11"/>
       <c r="H905" s="11"/>
@@ -21682,7 +21682,7 @@
       <c r="X905" s="11"/>
       <c r="Y905" s="11"/>
     </row>
-    <row r="906" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="906" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D906" s="29"/>
       <c r="G906" s="11"/>
       <c r="H906" s="11"/>
@@ -21704,7 +21704,7 @@
       <c r="X906" s="11"/>
       <c r="Y906" s="11"/>
     </row>
-    <row r="907" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="907" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D907" s="29"/>
       <c r="G907" s="11"/>
       <c r="H907" s="11"/>
@@ -21726,7 +21726,7 @@
       <c r="X907" s="11"/>
       <c r="Y907" s="11"/>
     </row>
-    <row r="908" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="908" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D908" s="29"/>
       <c r="G908" s="11"/>
       <c r="H908" s="11"/>
@@ -21748,7 +21748,7 @@
       <c r="X908" s="11"/>
       <c r="Y908" s="11"/>
     </row>
-    <row r="909" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="909" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D909" s="29"/>
       <c r="G909" s="11"/>
       <c r="H909" s="11"/>
@@ -21770,7 +21770,7 @@
       <c r="X909" s="11"/>
       <c r="Y909" s="11"/>
     </row>
-    <row r="910" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="910" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D910" s="29"/>
       <c r="G910" s="11"/>
       <c r="H910" s="11"/>
@@ -21792,7 +21792,7 @@
       <c r="X910" s="11"/>
       <c r="Y910" s="11"/>
     </row>
-    <row r="911" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="911" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D911" s="29"/>
       <c r="G911" s="11"/>
       <c r="H911" s="11"/>
@@ -21814,7 +21814,7 @@
       <c r="X911" s="11"/>
       <c r="Y911" s="11"/>
     </row>
-    <row r="912" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="912" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D912" s="29"/>
       <c r="G912" s="11"/>
       <c r="H912" s="11"/>
@@ -21836,7 +21836,7 @@
       <c r="X912" s="11"/>
       <c r="Y912" s="11"/>
     </row>
-    <row r="913" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="913" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D913" s="29"/>
       <c r="G913" s="11"/>
       <c r="H913" s="11"/>
@@ -21858,7 +21858,7 @@
       <c r="X913" s="11"/>
       <c r="Y913" s="11"/>
     </row>
-    <row r="914" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="914" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D914" s="29"/>
       <c r="G914" s="11"/>
       <c r="H914" s="11"/>
@@ -21880,7 +21880,7 @@
       <c r="X914" s="11"/>
       <c r="Y914" s="11"/>
     </row>
-    <row r="915" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="915" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D915" s="29"/>
       <c r="G915" s="11"/>
       <c r="H915" s="11"/>
@@ -21902,7 +21902,7 @@
       <c r="X915" s="11"/>
       <c r="Y915" s="11"/>
     </row>
-    <row r="916" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="916" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D916" s="29"/>
       <c r="G916" s="11"/>
       <c r="H916" s="11"/>
@@ -21924,7 +21924,7 @@
       <c r="X916" s="11"/>
       <c r="Y916" s="11"/>
     </row>
-    <row r="917" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="917" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D917" s="29"/>
       <c r="G917" s="11"/>
       <c r="H917" s="11"/>
@@ -21946,7 +21946,7 @@
       <c r="X917" s="11"/>
       <c r="Y917" s="11"/>
     </row>
-    <row r="918" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="918" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D918" s="29"/>
       <c r="G918" s="11"/>
       <c r="H918" s="11"/>
@@ -21968,7 +21968,7 @@
       <c r="X918" s="11"/>
       <c r="Y918" s="11"/>
     </row>
-    <row r="919" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="919" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D919" s="29"/>
       <c r="G919" s="11"/>
       <c r="H919" s="11"/>
@@ -21990,7 +21990,7 @@
       <c r="X919" s="11"/>
       <c r="Y919" s="11"/>
     </row>
-    <row r="920" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="920" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D920" s="29"/>
       <c r="G920" s="11"/>
       <c r="H920" s="11"/>
@@ -22012,7 +22012,7 @@
       <c r="X920" s="11"/>
       <c r="Y920" s="11"/>
     </row>
-    <row r="921" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="921" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D921" s="29"/>
       <c r="G921" s="11"/>
       <c r="H921" s="11"/>
@@ -22034,7 +22034,7 @@
       <c r="X921" s="11"/>
       <c r="Y921" s="11"/>
     </row>
-    <row r="922" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="922" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D922" s="29"/>
       <c r="G922" s="11"/>
       <c r="H922" s="11"/>
@@ -22056,7 +22056,7 @@
       <c r="X922" s="11"/>
       <c r="Y922" s="11"/>
     </row>
-    <row r="923" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="923" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D923" s="29"/>
       <c r="G923" s="11"/>
       <c r="H923" s="11"/>
@@ -22078,7 +22078,7 @@
       <c r="X923" s="11"/>
       <c r="Y923" s="11"/>
     </row>
-    <row r="924" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="924" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D924" s="29"/>
       <c r="G924" s="11"/>
       <c r="H924" s="11"/>
@@ -22100,7 +22100,7 @@
       <c r="X924" s="11"/>
       <c r="Y924" s="11"/>
     </row>
-    <row r="925" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="925" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D925" s="29"/>
       <c r="G925" s="11"/>
       <c r="H925" s="11"/>
@@ -22122,7 +22122,7 @@
       <c r="X925" s="11"/>
       <c r="Y925" s="11"/>
     </row>
-    <row r="926" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="926" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D926" s="29"/>
       <c r="G926" s="11"/>
       <c r="H926" s="11"/>
@@ -22144,7 +22144,7 @@
       <c r="X926" s="11"/>
       <c r="Y926" s="11"/>
     </row>
-    <row r="927" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="927" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D927" s="29"/>
       <c r="G927" s="11"/>
       <c r="H927" s="11"/>
@@ -22166,7 +22166,7 @@
       <c r="X927" s="11"/>
       <c r="Y927" s="11"/>
     </row>
-    <row r="928" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="928" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D928" s="29"/>
       <c r="G928" s="11"/>
       <c r="H928" s="11"/>
@@ -22188,7 +22188,7 @@
       <c r="X928" s="11"/>
       <c r="Y928" s="11"/>
     </row>
-    <row r="929" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="929" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D929" s="29"/>
       <c r="G929" s="11"/>
       <c r="H929" s="11"/>
@@ -22210,7 +22210,7 @@
       <c r="X929" s="11"/>
       <c r="Y929" s="11"/>
     </row>
-    <row r="930" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="930" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D930" s="29"/>
       <c r="G930" s="11"/>
       <c r="H930" s="11"/>
@@ -22232,7 +22232,7 @@
       <c r="X930" s="11"/>
       <c r="Y930" s="11"/>
     </row>
-    <row r="931" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="931" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D931" s="29"/>
       <c r="G931" s="11"/>
       <c r="H931" s="11"/>
@@ -22254,7 +22254,7 @@
       <c r="X931" s="11"/>
       <c r="Y931" s="11"/>
     </row>
-    <row r="932" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="932" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D932" s="29"/>
       <c r="G932" s="11"/>
       <c r="H932" s="11"/>
@@ -22276,7 +22276,7 @@
       <c r="X932" s="11"/>
       <c r="Y932" s="11"/>
     </row>
-    <row r="933" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="933" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D933" s="29"/>
       <c r="G933" s="11"/>
       <c r="H933" s="11"/>
@@ -22298,7 +22298,7 @@
       <c r="X933" s="11"/>
       <c r="Y933" s="11"/>
     </row>
-    <row r="934" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="934" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D934" s="29"/>
       <c r="G934" s="11"/>
       <c r="H934" s="11"/>
@@ -22320,7 +22320,7 @@
       <c r="X934" s="11"/>
       <c r="Y934" s="11"/>
     </row>
-    <row r="935" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="935" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D935" s="29"/>
       <c r="G935" s="11"/>
       <c r="H935" s="11"/>
@@ -22342,7 +22342,7 @@
       <c r="X935" s="11"/>
       <c r="Y935" s="11"/>
     </row>
-    <row r="936" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="936" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D936" s="29"/>
       <c r="G936" s="11"/>
       <c r="H936" s="11"/>
@@ -22364,7 +22364,7 @@
       <c r="X936" s="11"/>
       <c r="Y936" s="11"/>
     </row>
-    <row r="937" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="937" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D937" s="29"/>
       <c r="G937" s="11"/>
       <c r="H937" s="11"/>
@@ -22386,7 +22386,7 @@
       <c r="X937" s="11"/>
       <c r="Y937" s="11"/>
     </row>
-    <row r="938" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="938" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D938" s="29"/>
       <c r="G938" s="11"/>
       <c r="H938" s="11"/>
@@ -22408,7 +22408,7 @@
       <c r="X938" s="11"/>
       <c r="Y938" s="11"/>
     </row>
-    <row r="939" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="939" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D939" s="29"/>
       <c r="G939" s="11"/>
       <c r="H939" s="11"/>
@@ -22430,7 +22430,7 @@
       <c r="X939" s="11"/>
       <c r="Y939" s="11"/>
     </row>
-    <row r="940" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="940" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D940" s="29"/>
       <c r="G940" s="11"/>
       <c r="H940" s="11"/>
@@ -22452,7 +22452,7 @@
       <c r="X940" s="11"/>
       <c r="Y940" s="11"/>
     </row>
-    <row r="941" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="941" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D941" s="29"/>
       <c r="G941" s="11"/>
       <c r="H941" s="11"/>
@@ -22474,7 +22474,7 @@
       <c r="X941" s="11"/>
       <c r="Y941" s="11"/>
     </row>
-    <row r="942" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="942" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D942" s="29"/>
       <c r="G942" s="11"/>
       <c r="H942" s="11"/>
@@ -22496,7 +22496,7 @@
       <c r="X942" s="11"/>
       <c r="Y942" s="11"/>
     </row>
-    <row r="943" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="943" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D943" s="29"/>
       <c r="G943" s="11"/>
       <c r="H943" s="11"/>
@@ -22518,7 +22518,7 @@
       <c r="X943" s="11"/>
       <c r="Y943" s="11"/>
     </row>
-    <row r="944" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="944" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D944" s="29"/>
       <c r="G944" s="11"/>
       <c r="H944" s="11"/>
@@ -22540,7 +22540,7 @@
       <c r="X944" s="11"/>
       <c r="Y944" s="11"/>
     </row>
-    <row r="945" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="945" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D945" s="29"/>
       <c r="G945" s="11"/>
       <c r="H945" s="11"/>
@@ -22562,7 +22562,7 @@
       <c r="X945" s="11"/>
       <c r="Y945" s="11"/>
     </row>
-    <row r="946" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="946" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D946" s="29"/>
       <c r="G946" s="11"/>
       <c r="H946" s="11"/>
@@ -22584,7 +22584,7 @@
       <c r="X946" s="11"/>
       <c r="Y946" s="11"/>
     </row>
-    <row r="947" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="947" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D947" s="29"/>
       <c r="G947" s="11"/>
       <c r="H947" s="11"/>
@@ -22606,7 +22606,7 @@
       <c r="X947" s="11"/>
       <c r="Y947" s="11"/>
     </row>
-    <row r="948" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="948" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D948" s="29"/>
       <c r="G948" s="11"/>
       <c r="H948" s="11"/>
@@ -22628,7 +22628,7 @@
       <c r="X948" s="11"/>
       <c r="Y948" s="11"/>
     </row>
-    <row r="949" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="949" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D949" s="29"/>
       <c r="G949" s="11"/>
       <c r="H949" s="11"/>
@@ -22650,7 +22650,7 @@
       <c r="X949" s="11"/>
       <c r="Y949" s="11"/>
     </row>
-    <row r="950" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="950" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D950" s="29"/>
       <c r="G950" s="11"/>
       <c r="H950" s="11"/>
@@ -22672,7 +22672,7 @@
       <c r="X950" s="11"/>
       <c r="Y950" s="11"/>
     </row>
-    <row r="951" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="951" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D951" s="29"/>
       <c r="G951" s="11"/>
       <c r="H951" s="11"/>
@@ -22694,7 +22694,7 @@
       <c r="X951" s="11"/>
       <c r="Y951" s="11"/>
     </row>
-    <row r="952" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="952" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D952" s="29"/>
       <c r="G952" s="11"/>
       <c r="H952" s="11"/>
@@ -22716,7 +22716,7 @@
       <c r="X952" s="11"/>
       <c r="Y952" s="11"/>
     </row>
-    <row r="953" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="953" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D953" s="29"/>
       <c r="G953" s="11"/>
       <c r="H953" s="11"/>
@@ -22738,7 +22738,7 @@
       <c r="X953" s="11"/>
       <c r="Y953" s="11"/>
     </row>
-    <row r="954" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="954" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D954" s="29"/>
       <c r="G954" s="11"/>
       <c r="H954" s="11"/>
@@ -22760,7 +22760,7 @@
       <c r="X954" s="11"/>
       <c r="Y954" s="11"/>
     </row>
-    <row r="955" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="955" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D955" s="29"/>
       <c r="G955" s="11"/>
       <c r="H955" s="11"/>
@@ -22782,7 +22782,7 @@
       <c r="X955" s="11"/>
       <c r="Y955" s="11"/>
     </row>
-    <row r="956" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="956" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D956" s="29"/>
       <c r="G956" s="11"/>
       <c r="H956" s="11"/>
@@ -22804,7 +22804,7 @@
       <c r="X956" s="11"/>
       <c r="Y956" s="11"/>
     </row>
-    <row r="957" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="957" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D957" s="29"/>
       <c r="G957" s="11"/>
       <c r="H957" s="11"/>
@@ -22826,7 +22826,7 @@
       <c r="X957" s="11"/>
       <c r="Y957" s="11"/>
     </row>
-    <row r="958" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="958" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D958" s="29"/>
       <c r="G958" s="11"/>
       <c r="H958" s="11"/>
@@ -22848,7 +22848,7 @@
       <c r="X958" s="11"/>
       <c r="Y958" s="11"/>
     </row>
-    <row r="959" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="959" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D959" s="29"/>
       <c r="G959" s="11"/>
       <c r="H959" s="11"/>
@@ -22870,7 +22870,7 @@
       <c r="X959" s="11"/>
       <c r="Y959" s="11"/>
     </row>
-    <row r="960" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="960" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D960" s="29"/>
       <c r="G960" s="11"/>
       <c r="H960" s="11"/>
@@ -22892,7 +22892,7 @@
       <c r="X960" s="11"/>
       <c r="Y960" s="11"/>
     </row>
-    <row r="961" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="961" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D961" s="29"/>
       <c r="G961" s="11"/>
       <c r="H961" s="11"/>
@@ -22914,7 +22914,7 @@
       <c r="X961" s="11"/>
       <c r="Y961" s="11"/>
     </row>
-    <row r="962" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="962" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D962" s="29"/>
       <c r="G962" s="11"/>
       <c r="H962" s="11"/>
@@ -22936,7 +22936,7 @@
       <c r="X962" s="11"/>
       <c r="Y962" s="11"/>
     </row>
-    <row r="963" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="963" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D963" s="29"/>
       <c r="G963" s="11"/>
       <c r="H963" s="11"/>
@@ -22958,7 +22958,7 @@
       <c r="X963" s="11"/>
       <c r="Y963" s="11"/>
     </row>
-    <row r="964" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="964" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D964" s="29"/>
       <c r="G964" s="11"/>
       <c r="H964" s="11"/>
@@ -22980,7 +22980,7 @@
       <c r="X964" s="11"/>
       <c r="Y964" s="11"/>
     </row>
-    <row r="965" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="965" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D965" s="29"/>
       <c r="G965" s="11"/>
       <c r="H965" s="11"/>
@@ -23002,7 +23002,7 @@
       <c r="X965" s="11"/>
       <c r="Y965" s="11"/>
     </row>
-    <row r="966" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="966" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D966" s="29"/>
       <c r="G966" s="11"/>
       <c r="H966" s="11"/>
@@ -23024,7 +23024,7 @@
       <c r="X966" s="11"/>
       <c r="Y966" s="11"/>
     </row>
-    <row r="967" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="967" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D967" s="29"/>
       <c r="G967" s="11"/>
       <c r="H967" s="11"/>
@@ -23046,7 +23046,7 @@
       <c r="X967" s="11"/>
       <c r="Y967" s="11"/>
     </row>
-    <row r="968" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="968" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D968" s="29"/>
       <c r="G968" s="11"/>
       <c r="H968" s="11"/>
@@ -23068,7 +23068,7 @@
       <c r="X968" s="11"/>
       <c r="Y968" s="11"/>
     </row>
-    <row r="969" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="969" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D969" s="29"/>
       <c r="G969" s="11"/>
       <c r="H969" s="11"/>
@@ -23090,7 +23090,7 @@
       <c r="X969" s="11"/>
       <c r="Y969" s="11"/>
     </row>
-    <row r="970" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="970" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D970" s="29"/>
       <c r="G970" s="11"/>
       <c r="H970" s="11"/>
@@ -23112,7 +23112,7 @@
       <c r="X970" s="11"/>
       <c r="Y970" s="11"/>
     </row>
-    <row r="971" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="971" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D971" s="29"/>
       <c r="G971" s="11"/>
       <c r="H971" s="11"/>
@@ -23134,7 +23134,7 @@
       <c r="X971" s="11"/>
       <c r="Y971" s="11"/>
     </row>
-    <row r="972" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="972" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D972" s="29"/>
       <c r="G972" s="11"/>
       <c r="H972" s="11"/>
@@ -23156,7 +23156,7 @@
       <c r="X972" s="11"/>
       <c r="Y972" s="11"/>
     </row>
-    <row r="973" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="973" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D973" s="29"/>
       <c r="G973" s="11"/>
       <c r="H973" s="11"/>
@@ -23178,7 +23178,7 @@
       <c r="X973" s="11"/>
       <c r="Y973" s="11"/>
     </row>
-    <row r="974" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="974" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D974" s="29"/>
       <c r="G974" s="11"/>
       <c r="H974" s="11"/>
@@ -23200,7 +23200,7 @@
       <c r="X974" s="11"/>
       <c r="Y974" s="11"/>
     </row>
-    <row r="975" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="975" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D975" s="29"/>
       <c r="G975" s="11"/>
       <c r="H975" s="11"/>
@@ -23222,7 +23222,7 @@
       <c r="X975" s="11"/>
       <c r="Y975" s="11"/>
     </row>
-    <row r="976" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="976" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D976" s="29"/>
       <c r="G976" s="11"/>
       <c r="H976" s="11"/>
@@ -23244,7 +23244,7 @@
       <c r="X976" s="11"/>
       <c r="Y976" s="11"/>
     </row>
-    <row r="977" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="977" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D977" s="29"/>
       <c r="G977" s="11"/>
       <c r="H977" s="11"/>
@@ -23266,7 +23266,7 @@
       <c r="X977" s="11"/>
       <c r="Y977" s="11"/>
     </row>
-    <row r="978" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="978" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D978" s="29"/>
       <c r="G978" s="11"/>
       <c r="H978" s="11"/>
@@ -23288,7 +23288,7 @@
       <c r="X978" s="11"/>
       <c r="Y978" s="11"/>
     </row>
-    <row r="979" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="979" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D979" s="29"/>
       <c r="G979" s="11"/>
       <c r="H979" s="11"/>
@@ -23310,7 +23310,7 @@
       <c r="X979" s="11"/>
       <c r="Y979" s="11"/>
     </row>
-    <row r="980" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="980" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D980" s="29"/>
       <c r="G980" s="11"/>
       <c r="H980" s="11"/>
@@ -23332,7 +23332,7 @@
       <c r="X980" s="11"/>
       <c r="Y980" s="11"/>
     </row>
-    <row r="981" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="981" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D981" s="29"/>
       <c r="G981" s="11"/>
       <c r="H981" s="11"/>
@@ -23354,7 +23354,7 @@
       <c r="X981" s="11"/>
       <c r="Y981" s="11"/>
     </row>
-    <row r="982" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="982" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D982" s="29"/>
       <c r="G982" s="11"/>
       <c r="H982" s="11"/>
@@ -23376,7 +23376,7 @@
       <c r="X982" s="11"/>
       <c r="Y982" s="11"/>
     </row>
-    <row r="983" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="983" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D983" s="29"/>
       <c r="G983" s="11"/>
       <c r="H983" s="11"/>
@@ -23398,7 +23398,7 @@
       <c r="X983" s="11"/>
       <c r="Y983" s="11"/>
     </row>
-    <row r="984" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="984" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D984" s="29"/>
       <c r="G984" s="11"/>
       <c r="H984" s="11"/>
@@ -23420,7 +23420,7 @@
       <c r="X984" s="11"/>
       <c r="Y984" s="11"/>
     </row>
-    <row r="985" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="985" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D985" s="29"/>
       <c r="G985" s="11"/>
       <c r="H985" s="11"/>
@@ -23442,7 +23442,7 @@
       <c r="X985" s="11"/>
       <c r="Y985" s="11"/>
     </row>
-    <row r="986" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="986" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D986" s="29"/>
       <c r="G986" s="11"/>
       <c r="H986" s="11"/>
@@ -23464,7 +23464,7 @@
       <c r="X986" s="11"/>
       <c r="Y986" s="11"/>
     </row>
-    <row r="987" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="987" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D987" s="29"/>
       <c r="G987" s="11"/>
       <c r="H987" s="11"/>
@@ -23486,7 +23486,7 @@
       <c r="X987" s="11"/>
       <c r="Y987" s="11"/>
     </row>
-    <row r="988" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="988" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D988" s="29"/>
       <c r="G988" s="11"/>
       <c r="H988" s="11"/>
@@ -23508,7 +23508,7 @@
       <c r="X988" s="11"/>
       <c r="Y988" s="11"/>
     </row>
-    <row r="989" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="989" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D989" s="29"/>
       <c r="G989" s="11"/>
       <c r="H989" s="11"/>
@@ -23530,7 +23530,7 @@
       <c r="X989" s="11"/>
       <c r="Y989" s="11"/>
     </row>
-    <row r="990" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="990" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D990" s="29"/>
       <c r="G990" s="11"/>
       <c r="H990" s="11"/>
@@ -23552,7 +23552,7 @@
       <c r="X990" s="11"/>
       <c r="Y990" s="11"/>
     </row>
-    <row r="991" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="991" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D991" s="29"/>
       <c r="G991" s="11"/>
       <c r="H991" s="11"/>
@@ -23574,7 +23574,7 @@
       <c r="X991" s="11"/>
       <c r="Y991" s="11"/>
     </row>
-    <row r="992" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="992" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D992" s="29"/>
       <c r="G992" s="11"/>
       <c r="H992" s="11"/>
@@ -23596,7 +23596,7 @@
       <c r="X992" s="11"/>
       <c r="Y992" s="11"/>
     </row>
-    <row r="993" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="993" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D993" s="29"/>
       <c r="G993" s="11"/>
       <c r="H993" s="11"/>
@@ -23618,7 +23618,7 @@
       <c r="X993" s="11"/>
       <c r="Y993" s="11"/>
     </row>
-    <row r="994" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="994" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D994" s="29"/>
       <c r="G994" s="11"/>
       <c r="H994" s="11"/>
@@ -23640,7 +23640,7 @@
       <c r="X994" s="11"/>
       <c r="Y994" s="11"/>
     </row>
-    <row r="995" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="995" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D995" s="29"/>
       <c r="G995" s="11"/>
       <c r="H995" s="11"/>
@@ -23662,7 +23662,7 @@
       <c r="X995" s="11"/>
       <c r="Y995" s="11"/>
     </row>
-    <row r="996" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="996" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D996" s="29"/>
       <c r="G996" s="11"/>
       <c r="H996" s="11"/>
@@ -23684,7 +23684,7 @@
       <c r="X996" s="11"/>
       <c r="Y996" s="11"/>
     </row>
-    <row r="997" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="997" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D997" s="29"/>
       <c r="G997" s="11"/>
       <c r="H997" s="11"/>
@@ -23706,7 +23706,7 @@
       <c r="X997" s="11"/>
       <c r="Y997" s="11"/>
     </row>
-    <row r="998" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="998" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D998" s="29"/>
       <c r="G998" s="11"/>
       <c r="H998" s="11"/>
@@ -23728,7 +23728,7 @@
       <c r="X998" s="11"/>
       <c r="Y998" s="11"/>
     </row>
-    <row r="999" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="999" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D999" s="29"/>
       <c r="G999" s="11"/>
       <c r="H999" s="11"/>
@@ -23750,7 +23750,7 @@
       <c r="X999" s="11"/>
       <c r="Y999" s="11"/>
     </row>
-    <row r="1000" spans="4:25" x14ac:dyDescent="0.25">
+    <row r="1000" spans="4:25" x14ac:dyDescent="0.3">
       <c r="D1000" s="29"/>
       <c r="G1000" s="11"/>
       <c r="H1000" s="11"/>
@@ -23784,17 +23784,17 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" style="28" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.6640625" style="28" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="55" style="28" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.28515625" style="28" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.5703125" style="28" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.7109375" style="28" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.5703125" style="28" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.33203125" style="28" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.5546875" style="28" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.6640625" style="28" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.5546875" style="28" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="1" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -23814,7 +23814,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="25"/>
       <c r="B2" s="27"/>
       <c r="C2" s="25"/>
